--- a/Excel Files IPEDS/Trimmed/c2006_trimmed_file.xlsx
+++ b/Excel Files IPEDS/Trimmed/c2006_trimmed_file.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E399"/>
+  <dimension ref="A1:K399"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,6 +451,36 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>CRACE15</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>CRACE16</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>CRACE18</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>CRACE20</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>CRACE21</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>CRACE22</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
           <t>Year</t>
         </is>
       </c>
@@ -469,6 +499,24 @@
         <v>7</v>
       </c>
       <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -486,6 +534,24 @@
         <v>7</v>
       </c>
       <c r="E3" t="n">
+        <v>5</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
+        <v>5</v>
+      </c>
+      <c r="K3" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -503,6 +569,24 @@
         <v>9</v>
       </c>
       <c r="E4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
+        <v>2</v>
+      </c>
+      <c r="K4" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -520,6 +604,24 @@
         <v>7</v>
       </c>
       <c r="E5" t="n">
+        <v>5</v>
+      </c>
+      <c r="F5" t="n">
+        <v>3</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>5</v>
+      </c>
+      <c r="K5" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -537,6 +639,24 @@
         <v>9</v>
       </c>
       <c r="E6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" t="n">
+        <v>2</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -554,6 +674,24 @@
         <v>7</v>
       </c>
       <c r="E7" t="n">
+        <v>2</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -571,6 +709,24 @@
         <v>9</v>
       </c>
       <c r="E8" t="n">
+        <v>5</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
+        <v>2</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>2</v>
+      </c>
+      <c r="K8" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -588,6 +744,24 @@
         <v>7</v>
       </c>
       <c r="E9" t="n">
+        <v>4</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
+        <v>2</v>
+      </c>
+      <c r="K9" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -605,6 +779,24 @@
         <v>9</v>
       </c>
       <c r="E10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -622,6 +814,24 @@
         <v>7</v>
       </c>
       <c r="E11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
+        <v>1</v>
+      </c>
+      <c r="K11" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -639,6 +849,24 @@
         <v>9</v>
       </c>
       <c r="E12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1</v>
+      </c>
+      <c r="K12" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -656,6 +884,24 @@
         <v>7</v>
       </c>
       <c r="E13" t="n">
+        <v>4</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1</v>
+      </c>
+      <c r="K13" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -673,6 +919,24 @@
         <v>9</v>
       </c>
       <c r="E14" t="n">
+        <v>5</v>
+      </c>
+      <c r="F14" t="n">
+        <v>3</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
+        <v>4</v>
+      </c>
+      <c r="K14" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -690,6 +954,24 @@
         <v>7</v>
       </c>
       <c r="E15" t="n">
+        <v>14</v>
+      </c>
+      <c r="F15" t="n">
+        <v>4</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="n">
+        <v>11</v>
+      </c>
+      <c r="K15" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -707,6 +989,24 @@
         <v>9</v>
       </c>
       <c r="E16" t="n">
+        <v>3</v>
+      </c>
+      <c r="F16" t="n">
+        <v>1</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="n">
+        <v>1</v>
+      </c>
+      <c r="K16" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -724,6 +1024,24 @@
         <v>7</v>
       </c>
       <c r="E17" t="n">
+        <v>5</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="n">
+        <v>5</v>
+      </c>
+      <c r="K17" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -741,6 +1059,24 @@
         <v>7</v>
       </c>
       <c r="E18" t="n">
+        <v>4</v>
+      </c>
+      <c r="F18" t="n">
+        <v>1</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" t="n">
+        <v>5</v>
+      </c>
+      <c r="K18" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -758,6 +1094,24 @@
         <v>9</v>
       </c>
       <c r="E19" t="n">
+        <v>5</v>
+      </c>
+      <c r="F19" t="n">
+        <v>1</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1</v>
+      </c>
+      <c r="K19" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -775,6 +1129,24 @@
         <v>7</v>
       </c>
       <c r="E20" t="n">
+        <v>3</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" t="n">
+        <v>2</v>
+      </c>
+      <c r="K20" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -792,6 +1164,24 @@
         <v>9</v>
       </c>
       <c r="E21" t="n">
+        <v>19</v>
+      </c>
+      <c r="F21" t="n">
+        <v>2</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" t="n">
+        <v>7</v>
+      </c>
+      <c r="K21" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -809,6 +1199,24 @@
         <v>7</v>
       </c>
       <c r="E22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -826,6 +1234,24 @@
         <v>7</v>
       </c>
       <c r="E23" t="n">
+        <v>2</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" t="n">
+        <v>2</v>
+      </c>
+      <c r="K23" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -843,6 +1269,24 @@
         <v>7</v>
       </c>
       <c r="E24" t="n">
+        <v>5</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" t="n">
+        <v>2</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" t="n">
+        <v>1</v>
+      </c>
+      <c r="K24" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -860,6 +1304,24 @@
         <v>7</v>
       </c>
       <c r="E25" t="n">
+        <v>4</v>
+      </c>
+      <c r="F25" t="n">
+        <v>2</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" t="n">
+        <v>2</v>
+      </c>
+      <c r="J25" t="n">
+        <v>1</v>
+      </c>
+      <c r="K25" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -877,6 +1339,24 @@
         <v>7</v>
       </c>
       <c r="E26" t="n">
+        <v>5</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" t="n">
+        <v>1</v>
+      </c>
+      <c r="J26" t="n">
+        <v>3</v>
+      </c>
+      <c r="K26" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -894,6 +1374,24 @@
         <v>7</v>
       </c>
       <c r="E27" t="n">
+        <v>2</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" t="n">
+        <v>1</v>
+      </c>
+      <c r="K27" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -911,6 +1409,24 @@
         <v>7</v>
       </c>
       <c r="E28" t="n">
+        <v>5</v>
+      </c>
+      <c r="F28" t="n">
+        <v>3</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" t="n">
+        <v>1</v>
+      </c>
+      <c r="I28" t="n">
+        <v>1</v>
+      </c>
+      <c r="J28" t="n">
+        <v>2</v>
+      </c>
+      <c r="K28" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -928,6 +1444,24 @@
         <v>7</v>
       </c>
       <c r="E29" t="n">
+        <v>28</v>
+      </c>
+      <c r="F29" t="n">
+        <v>7</v>
+      </c>
+      <c r="G29" t="n">
+        <v>1</v>
+      </c>
+      <c r="H29" t="n">
+        <v>2</v>
+      </c>
+      <c r="I29" t="n">
+        <v>4</v>
+      </c>
+      <c r="J29" t="n">
+        <v>22</v>
+      </c>
+      <c r="K29" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -945,6 +1479,24 @@
         <v>9</v>
       </c>
       <c r="E30" t="n">
+        <v>22</v>
+      </c>
+      <c r="F30" t="n">
+        <v>2</v>
+      </c>
+      <c r="G30" t="n">
+        <v>1</v>
+      </c>
+      <c r="H30" t="n">
+        <v>4</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" t="n">
+        <v>10</v>
+      </c>
+      <c r="K30" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -962,6 +1514,24 @@
         <v>7</v>
       </c>
       <c r="E31" t="n">
+        <v>9</v>
+      </c>
+      <c r="F31" t="n">
+        <v>6</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" t="n">
+        <v>1</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" t="n">
+        <v>10</v>
+      </c>
+      <c r="K31" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -979,6 +1549,24 @@
         <v>9</v>
       </c>
       <c r="E32" t="n">
+        <v>8</v>
+      </c>
+      <c r="F32" t="n">
+        <v>1</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" t="n">
+        <v>1</v>
+      </c>
+      <c r="I32" t="n">
+        <v>1</v>
+      </c>
+      <c r="J32" t="n">
+        <v>3</v>
+      </c>
+      <c r="K32" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -996,6 +1584,24 @@
         <v>7</v>
       </c>
       <c r="E33" t="n">
+        <v>10</v>
+      </c>
+      <c r="F33" t="n">
+        <v>4</v>
+      </c>
+      <c r="G33" t="n">
+        <v>1</v>
+      </c>
+      <c r="H33" t="n">
+        <v>3</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" t="n">
+        <v>5</v>
+      </c>
+      <c r="K33" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -1013,6 +1619,24 @@
         <v>9</v>
       </c>
       <c r="E34" t="n">
+        <v>6</v>
+      </c>
+      <c r="F34" t="n">
+        <v>1</v>
+      </c>
+      <c r="G34" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" t="n">
+        <v>2</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" t="n">
+        <v>1</v>
+      </c>
+      <c r="K34" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -1030,6 +1654,24 @@
         <v>7</v>
       </c>
       <c r="E35" t="n">
+        <v>14</v>
+      </c>
+      <c r="F35" t="n">
+        <v>2</v>
+      </c>
+      <c r="G35" t="n">
+        <v>1</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0</v>
+      </c>
+      <c r="J35" t="n">
+        <v>13</v>
+      </c>
+      <c r="K35" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -1047,6 +1689,24 @@
         <v>9</v>
       </c>
       <c r="E36" t="n">
+        <v>22</v>
+      </c>
+      <c r="F36" t="n">
+        <v>1</v>
+      </c>
+      <c r="G36" t="n">
+        <v>0</v>
+      </c>
+      <c r="H36" t="n">
+        <v>3</v>
+      </c>
+      <c r="I36" t="n">
+        <v>1</v>
+      </c>
+      <c r="J36" t="n">
+        <v>12</v>
+      </c>
+      <c r="K36" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -1064,6 +1724,24 @@
         <v>7</v>
       </c>
       <c r="E37" t="n">
+        <v>4</v>
+      </c>
+      <c r="F37" t="n">
+        <v>3</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0</v>
+      </c>
+      <c r="I37" t="n">
+        <v>2</v>
+      </c>
+      <c r="J37" t="n">
+        <v>2</v>
+      </c>
+      <c r="K37" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -1081,6 +1759,24 @@
         <v>9</v>
       </c>
       <c r="E38" t="n">
+        <v>5</v>
+      </c>
+      <c r="F38" t="n">
+        <v>0</v>
+      </c>
+      <c r="G38" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0</v>
+      </c>
+      <c r="I38" t="n">
+        <v>1</v>
+      </c>
+      <c r="J38" t="n">
+        <v>2</v>
+      </c>
+      <c r="K38" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -1098,6 +1794,24 @@
         <v>7</v>
       </c>
       <c r="E39" t="n">
+        <v>13</v>
+      </c>
+      <c r="F39" t="n">
+        <v>2</v>
+      </c>
+      <c r="G39" t="n">
+        <v>0</v>
+      </c>
+      <c r="H39" t="n">
+        <v>1</v>
+      </c>
+      <c r="I39" t="n">
+        <v>1</v>
+      </c>
+      <c r="J39" t="n">
+        <v>11</v>
+      </c>
+      <c r="K39" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -1115,6 +1829,24 @@
         <v>9</v>
       </c>
       <c r="E40" t="n">
+        <v>11</v>
+      </c>
+      <c r="F40" t="n">
+        <v>2</v>
+      </c>
+      <c r="G40" t="n">
+        <v>0</v>
+      </c>
+      <c r="H40" t="n">
+        <v>1</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0</v>
+      </c>
+      <c r="J40" t="n">
+        <v>10</v>
+      </c>
+      <c r="K40" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -1132,6 +1864,24 @@
         <v>7</v>
       </c>
       <c r="E41" t="n">
+        <v>9</v>
+      </c>
+      <c r="F41" t="n">
+        <v>1</v>
+      </c>
+      <c r="G41" t="n">
+        <v>0</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0</v>
+      </c>
+      <c r="J41" t="n">
+        <v>2</v>
+      </c>
+      <c r="K41" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -1149,6 +1899,24 @@
         <v>9</v>
       </c>
       <c r="E42" t="n">
+        <v>17</v>
+      </c>
+      <c r="F42" t="n">
+        <v>4</v>
+      </c>
+      <c r="G42" t="n">
+        <v>0</v>
+      </c>
+      <c r="H42" t="n">
+        <v>3</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0</v>
+      </c>
+      <c r="J42" t="n">
+        <v>16</v>
+      </c>
+      <c r="K42" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -1166,6 +1934,24 @@
         <v>7</v>
       </c>
       <c r="E43" t="n">
+        <v>10</v>
+      </c>
+      <c r="F43" t="n">
+        <v>2</v>
+      </c>
+      <c r="G43" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0</v>
+      </c>
+      <c r="J43" t="n">
+        <v>9</v>
+      </c>
+      <c r="K43" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -1183,6 +1969,24 @@
         <v>9</v>
       </c>
       <c r="E44" t="n">
+        <v>6</v>
+      </c>
+      <c r="F44" t="n">
+        <v>4</v>
+      </c>
+      <c r="G44" t="n">
+        <v>0</v>
+      </c>
+      <c r="H44" t="n">
+        <v>0</v>
+      </c>
+      <c r="I44" t="n">
+        <v>0</v>
+      </c>
+      <c r="J44" t="n">
+        <v>5</v>
+      </c>
+      <c r="K44" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -1200,6 +2004,24 @@
         <v>7</v>
       </c>
       <c r="E45" t="n">
+        <v>26</v>
+      </c>
+      <c r="F45" t="n">
+        <v>1</v>
+      </c>
+      <c r="G45" t="n">
+        <v>2</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0</v>
+      </c>
+      <c r="I45" t="n">
+        <v>3</v>
+      </c>
+      <c r="J45" t="n">
+        <v>17</v>
+      </c>
+      <c r="K45" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -1217,6 +2039,24 @@
         <v>7</v>
       </c>
       <c r="E46" t="n">
+        <v>4</v>
+      </c>
+      <c r="F46" t="n">
+        <v>1</v>
+      </c>
+      <c r="G46" t="n">
+        <v>0</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0</v>
+      </c>
+      <c r="I46" t="n">
+        <v>1</v>
+      </c>
+      <c r="J46" t="n">
+        <v>1</v>
+      </c>
+      <c r="K46" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -1234,6 +2074,24 @@
         <v>7</v>
       </c>
       <c r="E47" t="n">
+        <v>5</v>
+      </c>
+      <c r="F47" t="n">
+        <v>2</v>
+      </c>
+      <c r="G47" t="n">
+        <v>0</v>
+      </c>
+      <c r="H47" t="n">
+        <v>1</v>
+      </c>
+      <c r="I47" t="n">
+        <v>0</v>
+      </c>
+      <c r="J47" t="n">
+        <v>1</v>
+      </c>
+      <c r="K47" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -1251,6 +2109,24 @@
         <v>7</v>
       </c>
       <c r="E48" t="n">
+        <v>4</v>
+      </c>
+      <c r="F48" t="n">
+        <v>2</v>
+      </c>
+      <c r="G48" t="n">
+        <v>0</v>
+      </c>
+      <c r="H48" t="n">
+        <v>1</v>
+      </c>
+      <c r="I48" t="n">
+        <v>0</v>
+      </c>
+      <c r="J48" t="n">
+        <v>1</v>
+      </c>
+      <c r="K48" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -1268,6 +2144,24 @@
         <v>7</v>
       </c>
       <c r="E49" t="n">
+        <v>6</v>
+      </c>
+      <c r="F49" t="n">
+        <v>0</v>
+      </c>
+      <c r="G49" t="n">
+        <v>0</v>
+      </c>
+      <c r="H49" t="n">
+        <v>0</v>
+      </c>
+      <c r="I49" t="n">
+        <v>0</v>
+      </c>
+      <c r="J49" t="n">
+        <v>2</v>
+      </c>
+      <c r="K49" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -1285,6 +2179,24 @@
         <v>9</v>
       </c>
       <c r="E50" t="n">
+        <v>6</v>
+      </c>
+      <c r="F50" t="n">
+        <v>2</v>
+      </c>
+      <c r="G50" t="n">
+        <v>0</v>
+      </c>
+      <c r="H50" t="n">
+        <v>0</v>
+      </c>
+      <c r="I50" t="n">
+        <v>0</v>
+      </c>
+      <c r="J50" t="n">
+        <v>0</v>
+      </c>
+      <c r="K50" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -1302,6 +2214,24 @@
         <v>7</v>
       </c>
       <c r="E51" t="n">
+        <v>6</v>
+      </c>
+      <c r="F51" t="n">
+        <v>1</v>
+      </c>
+      <c r="G51" t="n">
+        <v>0</v>
+      </c>
+      <c r="H51" t="n">
+        <v>1</v>
+      </c>
+      <c r="I51" t="n">
+        <v>0</v>
+      </c>
+      <c r="J51" t="n">
+        <v>5</v>
+      </c>
+      <c r="K51" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -1319,6 +2249,24 @@
         <v>9</v>
       </c>
       <c r="E52" t="n">
+        <v>15</v>
+      </c>
+      <c r="F52" t="n">
+        <v>2</v>
+      </c>
+      <c r="G52" t="n">
+        <v>0</v>
+      </c>
+      <c r="H52" t="n">
+        <v>0</v>
+      </c>
+      <c r="I52" t="n">
+        <v>0</v>
+      </c>
+      <c r="J52" t="n">
+        <v>10</v>
+      </c>
+      <c r="K52" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -1336,6 +2284,24 @@
         <v>7</v>
       </c>
       <c r="E53" t="n">
+        <v>2</v>
+      </c>
+      <c r="F53" t="n">
+        <v>3</v>
+      </c>
+      <c r="G53" t="n">
+        <v>0</v>
+      </c>
+      <c r="H53" t="n">
+        <v>0</v>
+      </c>
+      <c r="I53" t="n">
+        <v>0</v>
+      </c>
+      <c r="J53" t="n">
+        <v>4</v>
+      </c>
+      <c r="K53" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -1353,6 +2319,24 @@
         <v>7</v>
       </c>
       <c r="E54" t="n">
+        <v>7</v>
+      </c>
+      <c r="F54" t="n">
+        <v>2</v>
+      </c>
+      <c r="G54" t="n">
+        <v>0</v>
+      </c>
+      <c r="H54" t="n">
+        <v>0</v>
+      </c>
+      <c r="I54" t="n">
+        <v>0</v>
+      </c>
+      <c r="J54" t="n">
+        <v>7</v>
+      </c>
+      <c r="K54" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -1370,6 +2354,24 @@
         <v>9</v>
       </c>
       <c r="E55" t="n">
+        <v>5</v>
+      </c>
+      <c r="F55" t="n">
+        <v>0</v>
+      </c>
+      <c r="G55" t="n">
+        <v>0</v>
+      </c>
+      <c r="H55" t="n">
+        <v>0</v>
+      </c>
+      <c r="I55" t="n">
+        <v>0</v>
+      </c>
+      <c r="J55" t="n">
+        <v>0</v>
+      </c>
+      <c r="K55" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -1387,6 +2389,24 @@
         <v>7</v>
       </c>
       <c r="E56" t="n">
+        <v>2</v>
+      </c>
+      <c r="F56" t="n">
+        <v>0</v>
+      </c>
+      <c r="G56" t="n">
+        <v>0</v>
+      </c>
+      <c r="H56" t="n">
+        <v>0</v>
+      </c>
+      <c r="I56" t="n">
+        <v>0</v>
+      </c>
+      <c r="J56" t="n">
+        <v>1</v>
+      </c>
+      <c r="K56" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -1404,6 +2424,24 @@
         <v>9</v>
       </c>
       <c r="E57" t="n">
+        <v>1</v>
+      </c>
+      <c r="F57" t="n">
+        <v>0</v>
+      </c>
+      <c r="G57" t="n">
+        <v>0</v>
+      </c>
+      <c r="H57" t="n">
+        <v>0</v>
+      </c>
+      <c r="I57" t="n">
+        <v>0</v>
+      </c>
+      <c r="J57" t="n">
+        <v>1</v>
+      </c>
+      <c r="K57" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -1421,6 +2459,24 @@
         <v>7</v>
       </c>
       <c r="E58" t="n">
+        <v>3</v>
+      </c>
+      <c r="F58" t="n">
+        <v>1</v>
+      </c>
+      <c r="G58" t="n">
+        <v>0</v>
+      </c>
+      <c r="H58" t="n">
+        <v>0</v>
+      </c>
+      <c r="I58" t="n">
+        <v>0</v>
+      </c>
+      <c r="J58" t="n">
+        <v>0</v>
+      </c>
+      <c r="K58" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -1438,6 +2494,24 @@
         <v>9</v>
       </c>
       <c r="E59" t="n">
+        <v>7</v>
+      </c>
+      <c r="F59" t="n">
+        <v>0</v>
+      </c>
+      <c r="G59" t="n">
+        <v>0</v>
+      </c>
+      <c r="H59" t="n">
+        <v>0</v>
+      </c>
+      <c r="I59" t="n">
+        <v>0</v>
+      </c>
+      <c r="J59" t="n">
+        <v>2</v>
+      </c>
+      <c r="K59" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -1455,6 +2529,24 @@
         <v>7</v>
       </c>
       <c r="E60" t="n">
+        <v>3</v>
+      </c>
+      <c r="F60" t="n">
+        <v>1</v>
+      </c>
+      <c r="G60" t="n">
+        <v>0</v>
+      </c>
+      <c r="H60" t="n">
+        <v>0</v>
+      </c>
+      <c r="I60" t="n">
+        <v>1</v>
+      </c>
+      <c r="J60" t="n">
+        <v>0</v>
+      </c>
+      <c r="K60" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -1472,6 +2564,24 @@
         <v>9</v>
       </c>
       <c r="E61" t="n">
+        <v>2</v>
+      </c>
+      <c r="F61" t="n">
+        <v>1</v>
+      </c>
+      <c r="G61" t="n">
+        <v>0</v>
+      </c>
+      <c r="H61" t="n">
+        <v>0</v>
+      </c>
+      <c r="I61" t="n">
+        <v>1</v>
+      </c>
+      <c r="J61" t="n">
+        <v>1</v>
+      </c>
+      <c r="K61" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -1489,6 +2599,24 @@
         <v>7</v>
       </c>
       <c r="E62" t="n">
+        <v>20</v>
+      </c>
+      <c r="F62" t="n">
+        <v>9</v>
+      </c>
+      <c r="G62" t="n">
+        <v>0</v>
+      </c>
+      <c r="H62" t="n">
+        <v>0</v>
+      </c>
+      <c r="I62" t="n">
+        <v>0</v>
+      </c>
+      <c r="J62" t="n">
+        <v>12</v>
+      </c>
+      <c r="K62" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -1506,6 +2634,24 @@
         <v>9</v>
       </c>
       <c r="E63" t="n">
+        <v>6</v>
+      </c>
+      <c r="F63" t="n">
+        <v>5</v>
+      </c>
+      <c r="G63" t="n">
+        <v>0</v>
+      </c>
+      <c r="H63" t="n">
+        <v>0</v>
+      </c>
+      <c r="I63" t="n">
+        <v>0</v>
+      </c>
+      <c r="J63" t="n">
+        <v>3</v>
+      </c>
+      <c r="K63" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -1523,6 +2669,24 @@
         <v>7</v>
       </c>
       <c r="E64" t="n">
+        <v>2</v>
+      </c>
+      <c r="F64" t="n">
+        <v>0</v>
+      </c>
+      <c r="G64" t="n">
+        <v>1</v>
+      </c>
+      <c r="H64" t="n">
+        <v>0</v>
+      </c>
+      <c r="I64" t="n">
+        <v>0</v>
+      </c>
+      <c r="J64" t="n">
+        <v>1</v>
+      </c>
+      <c r="K64" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -1540,6 +2704,24 @@
         <v>7</v>
       </c>
       <c r="E65" t="n">
+        <v>1</v>
+      </c>
+      <c r="F65" t="n">
+        <v>1</v>
+      </c>
+      <c r="G65" t="n">
+        <v>0</v>
+      </c>
+      <c r="H65" t="n">
+        <v>0</v>
+      </c>
+      <c r="I65" t="n">
+        <v>0</v>
+      </c>
+      <c r="J65" t="n">
+        <v>1</v>
+      </c>
+      <c r="K65" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -1557,6 +2739,24 @@
         <v>9</v>
       </c>
       <c r="E66" t="n">
+        <v>2</v>
+      </c>
+      <c r="F66" t="n">
+        <v>0</v>
+      </c>
+      <c r="G66" t="n">
+        <v>0</v>
+      </c>
+      <c r="H66" t="n">
+        <v>0</v>
+      </c>
+      <c r="I66" t="n">
+        <v>0</v>
+      </c>
+      <c r="J66" t="n">
+        <v>1</v>
+      </c>
+      <c r="K66" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -1574,6 +2774,24 @@
         <v>7</v>
       </c>
       <c r="E67" t="n">
+        <v>6</v>
+      </c>
+      <c r="F67" t="n">
+        <v>1</v>
+      </c>
+      <c r="G67" t="n">
+        <v>0</v>
+      </c>
+      <c r="H67" t="n">
+        <v>0</v>
+      </c>
+      <c r="I67" t="n">
+        <v>0</v>
+      </c>
+      <c r="J67" t="n">
+        <v>5</v>
+      </c>
+      <c r="K67" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -1591,6 +2809,24 @@
         <v>9</v>
       </c>
       <c r="E68" t="n">
+        <v>2</v>
+      </c>
+      <c r="F68" t="n">
+        <v>0</v>
+      </c>
+      <c r="G68" t="n">
+        <v>0</v>
+      </c>
+      <c r="H68" t="n">
+        <v>0</v>
+      </c>
+      <c r="I68" t="n">
+        <v>0</v>
+      </c>
+      <c r="J68" t="n">
+        <v>2</v>
+      </c>
+      <c r="K68" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -1608,6 +2844,24 @@
         <v>7</v>
       </c>
       <c r="E69" t="n">
+        <v>1</v>
+      </c>
+      <c r="F69" t="n">
+        <v>0</v>
+      </c>
+      <c r="G69" t="n">
+        <v>0</v>
+      </c>
+      <c r="H69" t="n">
+        <v>0</v>
+      </c>
+      <c r="I69" t="n">
+        <v>0</v>
+      </c>
+      <c r="J69" t="n">
+        <v>1</v>
+      </c>
+      <c r="K69" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -1625,6 +2879,24 @@
         <v>9</v>
       </c>
       <c r="E70" t="n">
+        <v>1</v>
+      </c>
+      <c r="F70" t="n">
+        <v>0</v>
+      </c>
+      <c r="G70" t="n">
+        <v>0</v>
+      </c>
+      <c r="H70" t="n">
+        <v>0</v>
+      </c>
+      <c r="I70" t="n">
+        <v>0</v>
+      </c>
+      <c r="J70" t="n">
+        <v>0</v>
+      </c>
+      <c r="K70" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -1642,6 +2914,24 @@
         <v>7</v>
       </c>
       <c r="E71" t="n">
+        <v>2</v>
+      </c>
+      <c r="F71" t="n">
+        <v>1</v>
+      </c>
+      <c r="G71" t="n">
+        <v>0</v>
+      </c>
+      <c r="H71" t="n">
+        <v>0</v>
+      </c>
+      <c r="I71" t="n">
+        <v>0</v>
+      </c>
+      <c r="J71" t="n">
+        <v>1</v>
+      </c>
+      <c r="K71" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -1659,6 +2949,24 @@
         <v>7</v>
       </c>
       <c r="E72" t="n">
+        <v>0</v>
+      </c>
+      <c r="F72" t="n">
+        <v>2</v>
+      </c>
+      <c r="G72" t="n">
+        <v>1</v>
+      </c>
+      <c r="H72" t="n">
+        <v>0</v>
+      </c>
+      <c r="I72" t="n">
+        <v>0</v>
+      </c>
+      <c r="J72" t="n">
+        <v>0</v>
+      </c>
+      <c r="K72" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -1676,6 +2984,24 @@
         <v>9</v>
       </c>
       <c r="E73" t="n">
+        <v>0</v>
+      </c>
+      <c r="F73" t="n">
+        <v>2</v>
+      </c>
+      <c r="G73" t="n">
+        <v>1</v>
+      </c>
+      <c r="H73" t="n">
+        <v>0</v>
+      </c>
+      <c r="I73" t="n">
+        <v>0</v>
+      </c>
+      <c r="J73" t="n">
+        <v>0</v>
+      </c>
+      <c r="K73" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -1693,6 +3019,24 @@
         <v>7</v>
       </c>
       <c r="E74" t="n">
+        <v>4</v>
+      </c>
+      <c r="F74" t="n">
+        <v>0</v>
+      </c>
+      <c r="G74" t="n">
+        <v>1</v>
+      </c>
+      <c r="H74" t="n">
+        <v>0</v>
+      </c>
+      <c r="I74" t="n">
+        <v>0</v>
+      </c>
+      <c r="J74" t="n">
+        <v>1</v>
+      </c>
+      <c r="K74" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -1710,6 +3054,24 @@
         <v>9</v>
       </c>
       <c r="E75" t="n">
+        <v>3</v>
+      </c>
+      <c r="F75" t="n">
+        <v>0</v>
+      </c>
+      <c r="G75" t="n">
+        <v>0</v>
+      </c>
+      <c r="H75" t="n">
+        <v>0</v>
+      </c>
+      <c r="I75" t="n">
+        <v>0</v>
+      </c>
+      <c r="J75" t="n">
+        <v>2</v>
+      </c>
+      <c r="K75" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -1727,6 +3089,24 @@
         <v>7</v>
       </c>
       <c r="E76" t="n">
+        <v>2</v>
+      </c>
+      <c r="F76" t="n">
+        <v>0</v>
+      </c>
+      <c r="G76" t="n">
+        <v>2</v>
+      </c>
+      <c r="H76" t="n">
+        <v>0</v>
+      </c>
+      <c r="I76" t="n">
+        <v>0</v>
+      </c>
+      <c r="J76" t="n">
+        <v>0</v>
+      </c>
+      <c r="K76" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -1744,6 +3124,24 @@
         <v>7</v>
       </c>
       <c r="E77" t="n">
+        <v>1</v>
+      </c>
+      <c r="F77" t="n">
+        <v>0</v>
+      </c>
+      <c r="G77" t="n">
+        <v>0</v>
+      </c>
+      <c r="H77" t="n">
+        <v>0</v>
+      </c>
+      <c r="I77" t="n">
+        <v>0</v>
+      </c>
+      <c r="J77" t="n">
+        <v>1</v>
+      </c>
+      <c r="K77" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -1761,6 +3159,24 @@
         <v>9</v>
       </c>
       <c r="E78" t="n">
+        <v>3</v>
+      </c>
+      <c r="F78" t="n">
+        <v>2</v>
+      </c>
+      <c r="G78" t="n">
+        <v>0</v>
+      </c>
+      <c r="H78" t="n">
+        <v>0</v>
+      </c>
+      <c r="I78" t="n">
+        <v>0</v>
+      </c>
+      <c r="J78" t="n">
+        <v>2</v>
+      </c>
+      <c r="K78" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -1778,6 +3194,24 @@
         <v>7</v>
       </c>
       <c r="E79" t="n">
+        <v>1</v>
+      </c>
+      <c r="F79" t="n">
+        <v>1</v>
+      </c>
+      <c r="G79" t="n">
+        <v>0</v>
+      </c>
+      <c r="H79" t="n">
+        <v>0</v>
+      </c>
+      <c r="I79" t="n">
+        <v>0</v>
+      </c>
+      <c r="J79" t="n">
+        <v>1</v>
+      </c>
+      <c r="K79" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -1795,6 +3229,24 @@
         <v>9</v>
       </c>
       <c r="E80" t="n">
+        <v>3</v>
+      </c>
+      <c r="F80" t="n">
+        <v>1</v>
+      </c>
+      <c r="G80" t="n">
+        <v>0</v>
+      </c>
+      <c r="H80" t="n">
+        <v>1</v>
+      </c>
+      <c r="I80" t="n">
+        <v>0</v>
+      </c>
+      <c r="J80" t="n">
+        <v>1</v>
+      </c>
+      <c r="K80" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -1812,6 +3264,24 @@
         <v>7</v>
       </c>
       <c r="E81" t="n">
+        <v>16</v>
+      </c>
+      <c r="F81" t="n">
+        <v>2</v>
+      </c>
+      <c r="G81" t="n">
+        <v>0</v>
+      </c>
+      <c r="H81" t="n">
+        <v>0</v>
+      </c>
+      <c r="I81" t="n">
+        <v>1</v>
+      </c>
+      <c r="J81" t="n">
+        <v>13</v>
+      </c>
+      <c r="K81" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -1829,6 +3299,24 @@
         <v>9</v>
       </c>
       <c r="E82" t="n">
+        <v>10</v>
+      </c>
+      <c r="F82" t="n">
+        <v>2</v>
+      </c>
+      <c r="G82" t="n">
+        <v>0</v>
+      </c>
+      <c r="H82" t="n">
+        <v>0</v>
+      </c>
+      <c r="I82" t="n">
+        <v>0</v>
+      </c>
+      <c r="J82" t="n">
+        <v>3</v>
+      </c>
+      <c r="K82" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -1846,6 +3334,24 @@
         <v>7</v>
       </c>
       <c r="E83" t="n">
+        <v>13</v>
+      </c>
+      <c r="F83" t="n">
+        <v>5</v>
+      </c>
+      <c r="G83" t="n">
+        <v>0</v>
+      </c>
+      <c r="H83" t="n">
+        <v>1</v>
+      </c>
+      <c r="I83" t="n">
+        <v>0</v>
+      </c>
+      <c r="J83" t="n">
+        <v>6</v>
+      </c>
+      <c r="K83" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -1863,6 +3369,24 @@
         <v>9</v>
       </c>
       <c r="E84" t="n">
+        <v>15</v>
+      </c>
+      <c r="F84" t="n">
+        <v>4</v>
+      </c>
+      <c r="G84" t="n">
+        <v>0</v>
+      </c>
+      <c r="H84" t="n">
+        <v>0</v>
+      </c>
+      <c r="I84" t="n">
+        <v>0</v>
+      </c>
+      <c r="J84" t="n">
+        <v>6</v>
+      </c>
+      <c r="K84" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -1880,6 +3404,24 @@
         <v>7</v>
       </c>
       <c r="E85" t="n">
+        <v>5</v>
+      </c>
+      <c r="F85" t="n">
+        <v>2</v>
+      </c>
+      <c r="G85" t="n">
+        <v>0</v>
+      </c>
+      <c r="H85" t="n">
+        <v>0</v>
+      </c>
+      <c r="I85" t="n">
+        <v>0</v>
+      </c>
+      <c r="J85" t="n">
+        <v>1</v>
+      </c>
+      <c r="K85" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -1897,6 +3439,24 @@
         <v>9</v>
       </c>
       <c r="E86" t="n">
+        <v>0</v>
+      </c>
+      <c r="F86" t="n">
+        <v>0</v>
+      </c>
+      <c r="G86" t="n">
+        <v>0</v>
+      </c>
+      <c r="H86" t="n">
+        <v>0</v>
+      </c>
+      <c r="I86" t="n">
+        <v>0</v>
+      </c>
+      <c r="J86" t="n">
+        <v>0</v>
+      </c>
+      <c r="K86" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -1914,6 +3474,24 @@
         <v>7</v>
       </c>
       <c r="E87" t="n">
+        <v>7</v>
+      </c>
+      <c r="F87" t="n">
+        <v>1</v>
+      </c>
+      <c r="G87" t="n">
+        <v>1</v>
+      </c>
+      <c r="H87" t="n">
+        <v>1</v>
+      </c>
+      <c r="I87" t="n">
+        <v>0</v>
+      </c>
+      <c r="J87" t="n">
+        <v>3</v>
+      </c>
+      <c r="K87" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -1931,6 +3509,24 @@
         <v>9</v>
       </c>
       <c r="E88" t="n">
+        <v>3</v>
+      </c>
+      <c r="F88" t="n">
+        <v>0</v>
+      </c>
+      <c r="G88" t="n">
+        <v>1</v>
+      </c>
+      <c r="H88" t="n">
+        <v>0</v>
+      </c>
+      <c r="I88" t="n">
+        <v>0</v>
+      </c>
+      <c r="J88" t="n">
+        <v>1</v>
+      </c>
+      <c r="K88" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -1948,6 +3544,24 @@
         <v>7</v>
       </c>
       <c r="E89" t="n">
+        <v>0</v>
+      </c>
+      <c r="F89" t="n">
+        <v>0</v>
+      </c>
+      <c r="G89" t="n">
+        <v>0</v>
+      </c>
+      <c r="H89" t="n">
+        <v>0</v>
+      </c>
+      <c r="I89" t="n">
+        <v>0</v>
+      </c>
+      <c r="J89" t="n">
+        <v>0</v>
+      </c>
+      <c r="K89" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -1965,6 +3579,24 @@
         <v>7</v>
       </c>
       <c r="E90" t="n">
+        <v>1</v>
+      </c>
+      <c r="F90" t="n">
+        <v>0</v>
+      </c>
+      <c r="G90" t="n">
+        <v>1</v>
+      </c>
+      <c r="H90" t="n">
+        <v>0</v>
+      </c>
+      <c r="I90" t="n">
+        <v>0</v>
+      </c>
+      <c r="J90" t="n">
+        <v>0</v>
+      </c>
+      <c r="K90" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -1982,6 +3614,24 @@
         <v>7</v>
       </c>
       <c r="E91" t="n">
+        <v>16</v>
+      </c>
+      <c r="F91" t="n">
+        <v>4</v>
+      </c>
+      <c r="G91" t="n">
+        <v>1</v>
+      </c>
+      <c r="H91" t="n">
+        <v>3</v>
+      </c>
+      <c r="I91" t="n">
+        <v>0</v>
+      </c>
+      <c r="J91" t="n">
+        <v>7</v>
+      </c>
+      <c r="K91" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -1999,6 +3649,24 @@
         <v>9</v>
       </c>
       <c r="E92" t="n">
+        <v>8</v>
+      </c>
+      <c r="F92" t="n">
+        <v>2</v>
+      </c>
+      <c r="G92" t="n">
+        <v>0</v>
+      </c>
+      <c r="H92" t="n">
+        <v>1</v>
+      </c>
+      <c r="I92" t="n">
+        <v>0</v>
+      </c>
+      <c r="J92" t="n">
+        <v>2</v>
+      </c>
+      <c r="K92" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -2016,6 +3684,24 @@
         <v>7</v>
       </c>
       <c r="E93" t="n">
+        <v>7</v>
+      </c>
+      <c r="F93" t="n">
+        <v>3</v>
+      </c>
+      <c r="G93" t="n">
+        <v>0</v>
+      </c>
+      <c r="H93" t="n">
+        <v>0</v>
+      </c>
+      <c r="I93" t="n">
+        <v>0</v>
+      </c>
+      <c r="J93" t="n">
+        <v>4</v>
+      </c>
+      <c r="K93" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -2033,6 +3719,24 @@
         <v>9</v>
       </c>
       <c r="E94" t="n">
+        <v>2</v>
+      </c>
+      <c r="F94" t="n">
+        <v>2</v>
+      </c>
+      <c r="G94" t="n">
+        <v>0</v>
+      </c>
+      <c r="H94" t="n">
+        <v>0</v>
+      </c>
+      <c r="I94" t="n">
+        <v>0</v>
+      </c>
+      <c r="J94" t="n">
+        <v>1</v>
+      </c>
+      <c r="K94" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -2050,6 +3754,24 @@
         <v>7</v>
       </c>
       <c r="E95" t="n">
+        <v>1</v>
+      </c>
+      <c r="F95" t="n">
+        <v>0</v>
+      </c>
+      <c r="G95" t="n">
+        <v>1</v>
+      </c>
+      <c r="H95" t="n">
+        <v>0</v>
+      </c>
+      <c r="I95" t="n">
+        <v>0</v>
+      </c>
+      <c r="J95" t="n">
+        <v>0</v>
+      </c>
+      <c r="K95" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -2067,6 +3789,24 @@
         <v>9</v>
       </c>
       <c r="E96" t="n">
+        <v>4</v>
+      </c>
+      <c r="F96" t="n">
+        <v>3</v>
+      </c>
+      <c r="G96" t="n">
+        <v>0</v>
+      </c>
+      <c r="H96" t="n">
+        <v>0</v>
+      </c>
+      <c r="I96" t="n">
+        <v>0</v>
+      </c>
+      <c r="J96" t="n">
+        <v>3</v>
+      </c>
+      <c r="K96" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -2084,6 +3824,24 @@
         <v>7</v>
       </c>
       <c r="E97" t="n">
+        <v>3</v>
+      </c>
+      <c r="F97" t="n">
+        <v>1</v>
+      </c>
+      <c r="G97" t="n">
+        <v>1</v>
+      </c>
+      <c r="H97" t="n">
+        <v>1</v>
+      </c>
+      <c r="I97" t="n">
+        <v>0</v>
+      </c>
+      <c r="J97" t="n">
+        <v>2</v>
+      </c>
+      <c r="K97" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -2101,6 +3859,24 @@
         <v>9</v>
       </c>
       <c r="E98" t="n">
+        <v>0</v>
+      </c>
+      <c r="F98" t="n">
+        <v>1</v>
+      </c>
+      <c r="G98" t="n">
+        <v>0</v>
+      </c>
+      <c r="H98" t="n">
+        <v>0</v>
+      </c>
+      <c r="I98" t="n">
+        <v>0</v>
+      </c>
+      <c r="J98" t="n">
+        <v>1</v>
+      </c>
+      <c r="K98" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -2118,6 +3894,24 @@
         <v>7</v>
       </c>
       <c r="E99" t="n">
+        <v>4</v>
+      </c>
+      <c r="F99" t="n">
+        <v>6</v>
+      </c>
+      <c r="G99" t="n">
+        <v>0</v>
+      </c>
+      <c r="H99" t="n">
+        <v>0</v>
+      </c>
+      <c r="I99" t="n">
+        <v>1</v>
+      </c>
+      <c r="J99" t="n">
+        <v>7</v>
+      </c>
+      <c r="K99" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -2135,6 +3929,24 @@
         <v>7</v>
       </c>
       <c r="E100" t="n">
+        <v>3</v>
+      </c>
+      <c r="F100" t="n">
+        <v>0</v>
+      </c>
+      <c r="G100" t="n">
+        <v>0</v>
+      </c>
+      <c r="H100" t="n">
+        <v>0</v>
+      </c>
+      <c r="I100" t="n">
+        <v>0</v>
+      </c>
+      <c r="J100" t="n">
+        <v>1</v>
+      </c>
+      <c r="K100" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -2152,6 +3964,24 @@
         <v>9</v>
       </c>
       <c r="E101" t="n">
+        <v>1</v>
+      </c>
+      <c r="F101" t="n">
+        <v>0</v>
+      </c>
+      <c r="G101" t="n">
+        <v>0</v>
+      </c>
+      <c r="H101" t="n">
+        <v>0</v>
+      </c>
+      <c r="I101" t="n">
+        <v>0</v>
+      </c>
+      <c r="J101" t="n">
+        <v>0</v>
+      </c>
+      <c r="K101" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -2169,6 +3999,24 @@
         <v>7</v>
       </c>
       <c r="E102" t="n">
+        <v>13</v>
+      </c>
+      <c r="F102" t="n">
+        <v>4</v>
+      </c>
+      <c r="G102" t="n">
+        <v>0</v>
+      </c>
+      <c r="H102" t="n">
+        <v>2</v>
+      </c>
+      <c r="I102" t="n">
+        <v>0</v>
+      </c>
+      <c r="J102" t="n">
+        <v>9</v>
+      </c>
+      <c r="K102" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -2186,6 +4034,24 @@
         <v>9</v>
       </c>
       <c r="E103" t="n">
+        <v>16</v>
+      </c>
+      <c r="F103" t="n">
+        <v>2</v>
+      </c>
+      <c r="G103" t="n">
+        <v>0</v>
+      </c>
+      <c r="H103" t="n">
+        <v>2</v>
+      </c>
+      <c r="I103" t="n">
+        <v>1</v>
+      </c>
+      <c r="J103" t="n">
+        <v>4</v>
+      </c>
+      <c r="K103" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -2203,6 +4069,24 @@
         <v>7</v>
       </c>
       <c r="E104" t="n">
+        <v>2</v>
+      </c>
+      <c r="F104" t="n">
+        <v>0</v>
+      </c>
+      <c r="G104" t="n">
+        <v>0</v>
+      </c>
+      <c r="H104" t="n">
+        <v>1</v>
+      </c>
+      <c r="I104" t="n">
+        <v>0</v>
+      </c>
+      <c r="J104" t="n">
+        <v>1</v>
+      </c>
+      <c r="K104" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -2220,6 +4104,24 @@
         <v>7</v>
       </c>
       <c r="E105" t="n">
+        <v>0</v>
+      </c>
+      <c r="F105" t="n">
+        <v>0</v>
+      </c>
+      <c r="G105" t="n">
+        <v>0</v>
+      </c>
+      <c r="H105" t="n">
+        <v>0</v>
+      </c>
+      <c r="I105" t="n">
+        <v>0</v>
+      </c>
+      <c r="J105" t="n">
+        <v>0</v>
+      </c>
+      <c r="K105" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -2237,6 +4139,24 @@
         <v>7</v>
       </c>
       <c r="E106" t="n">
+        <v>10</v>
+      </c>
+      <c r="F106" t="n">
+        <v>2</v>
+      </c>
+      <c r="G106" t="n">
+        <v>1</v>
+      </c>
+      <c r="H106" t="n">
+        <v>0</v>
+      </c>
+      <c r="I106" t="n">
+        <v>0</v>
+      </c>
+      <c r="J106" t="n">
+        <v>5</v>
+      </c>
+      <c r="K106" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -2254,6 +4174,24 @@
         <v>9</v>
       </c>
       <c r="E107" t="n">
+        <v>5</v>
+      </c>
+      <c r="F107" t="n">
+        <v>2</v>
+      </c>
+      <c r="G107" t="n">
+        <v>0</v>
+      </c>
+      <c r="H107" t="n">
+        <v>0</v>
+      </c>
+      <c r="I107" t="n">
+        <v>0</v>
+      </c>
+      <c r="J107" t="n">
+        <v>0</v>
+      </c>
+      <c r="K107" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -2271,6 +4209,24 @@
         <v>7</v>
       </c>
       <c r="E108" t="n">
+        <v>29</v>
+      </c>
+      <c r="F108" t="n">
+        <v>8</v>
+      </c>
+      <c r="G108" t="n">
+        <v>0</v>
+      </c>
+      <c r="H108" t="n">
+        <v>1</v>
+      </c>
+      <c r="I108" t="n">
+        <v>1</v>
+      </c>
+      <c r="J108" t="n">
+        <v>20</v>
+      </c>
+      <c r="K108" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -2288,6 +4244,24 @@
         <v>9</v>
       </c>
       <c r="E109" t="n">
+        <v>38</v>
+      </c>
+      <c r="F109" t="n">
+        <v>3</v>
+      </c>
+      <c r="G109" t="n">
+        <v>0</v>
+      </c>
+      <c r="H109" t="n">
+        <v>2</v>
+      </c>
+      <c r="I109" t="n">
+        <v>0</v>
+      </c>
+      <c r="J109" t="n">
+        <v>17</v>
+      </c>
+      <c r="K109" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -2305,6 +4279,24 @@
         <v>7</v>
       </c>
       <c r="E110" t="n">
+        <v>2</v>
+      </c>
+      <c r="F110" t="n">
+        <v>0</v>
+      </c>
+      <c r="G110" t="n">
+        <v>0</v>
+      </c>
+      <c r="H110" t="n">
+        <v>0</v>
+      </c>
+      <c r="I110" t="n">
+        <v>0</v>
+      </c>
+      <c r="J110" t="n">
+        <v>0</v>
+      </c>
+      <c r="K110" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -2322,6 +4314,24 @@
         <v>7</v>
       </c>
       <c r="E111" t="n">
+        <v>3</v>
+      </c>
+      <c r="F111" t="n">
+        <v>2</v>
+      </c>
+      <c r="G111" t="n">
+        <v>1</v>
+      </c>
+      <c r="H111" t="n">
+        <v>0</v>
+      </c>
+      <c r="I111" t="n">
+        <v>1</v>
+      </c>
+      <c r="J111" t="n">
+        <v>3</v>
+      </c>
+      <c r="K111" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -2339,6 +4349,24 @@
         <v>9</v>
       </c>
       <c r="E112" t="n">
+        <v>3</v>
+      </c>
+      <c r="F112" t="n">
+        <v>1</v>
+      </c>
+      <c r="G112" t="n">
+        <v>0</v>
+      </c>
+      <c r="H112" t="n">
+        <v>0</v>
+      </c>
+      <c r="I112" t="n">
+        <v>0</v>
+      </c>
+      <c r="J112" t="n">
+        <v>2</v>
+      </c>
+      <c r="K112" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -2356,6 +4384,24 @@
         <v>7</v>
       </c>
       <c r="E113" t="n">
+        <v>3</v>
+      </c>
+      <c r="F113" t="n">
+        <v>0</v>
+      </c>
+      <c r="G113" t="n">
+        <v>0</v>
+      </c>
+      <c r="H113" t="n">
+        <v>0</v>
+      </c>
+      <c r="I113" t="n">
+        <v>0</v>
+      </c>
+      <c r="J113" t="n">
+        <v>2</v>
+      </c>
+      <c r="K113" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -2373,6 +4419,24 @@
         <v>9</v>
       </c>
       <c r="E114" t="n">
+        <v>0</v>
+      </c>
+      <c r="F114" t="n">
+        <v>0</v>
+      </c>
+      <c r="G114" t="n">
+        <v>0</v>
+      </c>
+      <c r="H114" t="n">
+        <v>0</v>
+      </c>
+      <c r="I114" t="n">
+        <v>0</v>
+      </c>
+      <c r="J114" t="n">
+        <v>0</v>
+      </c>
+      <c r="K114" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -2390,6 +4454,24 @@
         <v>7</v>
       </c>
       <c r="E115" t="n">
+        <v>0</v>
+      </c>
+      <c r="F115" t="n">
+        <v>0</v>
+      </c>
+      <c r="G115" t="n">
+        <v>0</v>
+      </c>
+      <c r="H115" t="n">
+        <v>0</v>
+      </c>
+      <c r="I115" t="n">
+        <v>0</v>
+      </c>
+      <c r="J115" t="n">
+        <v>0</v>
+      </c>
+      <c r="K115" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -2407,6 +4489,24 @@
         <v>9</v>
       </c>
       <c r="E116" t="n">
+        <v>0</v>
+      </c>
+      <c r="F116" t="n">
+        <v>0</v>
+      </c>
+      <c r="G116" t="n">
+        <v>0</v>
+      </c>
+      <c r="H116" t="n">
+        <v>0</v>
+      </c>
+      <c r="I116" t="n">
+        <v>0</v>
+      </c>
+      <c r="J116" t="n">
+        <v>0</v>
+      </c>
+      <c r="K116" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -2424,6 +4524,24 @@
         <v>7</v>
       </c>
       <c r="E117" t="n">
+        <v>1</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0</v>
+      </c>
+      <c r="J117" t="n">
+        <v>1</v>
+      </c>
+      <c r="K117" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -2441,6 +4559,24 @@
         <v>7</v>
       </c>
       <c r="E118" t="n">
+        <v>2</v>
+      </c>
+      <c r="F118" t="n">
+        <v>0</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0</v>
+      </c>
+      <c r="J118" t="n">
+        <v>1</v>
+      </c>
+      <c r="K118" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -2458,6 +4594,24 @@
         <v>7</v>
       </c>
       <c r="E119" t="n">
+        <v>9</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0</v>
+      </c>
+      <c r="J119" t="n">
+        <v>6</v>
+      </c>
+      <c r="K119" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -2475,6 +4629,24 @@
         <v>7</v>
       </c>
       <c r="E120" t="n">
+        <v>1</v>
+      </c>
+      <c r="F120" t="n">
+        <v>1</v>
+      </c>
+      <c r="G120" t="n">
+        <v>1</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0</v>
+      </c>
+      <c r="K120" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -2492,6 +4664,24 @@
         <v>7</v>
       </c>
       <c r="E121" t="n">
+        <v>7</v>
+      </c>
+      <c r="F121" t="n">
+        <v>3</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0</v>
+      </c>
+      <c r="J121" t="n">
+        <v>6</v>
+      </c>
+      <c r="K121" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -2509,6 +4699,24 @@
         <v>9</v>
       </c>
       <c r="E122" t="n">
+        <v>5</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0</v>
+      </c>
+      <c r="J122" t="n">
+        <v>1</v>
+      </c>
+      <c r="K122" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -2526,6 +4734,24 @@
         <v>7</v>
       </c>
       <c r="E123" t="n">
+        <v>11</v>
+      </c>
+      <c r="F123" t="n">
+        <v>2</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0</v>
+      </c>
+      <c r="J123" t="n">
+        <v>5</v>
+      </c>
+      <c r="K123" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -2543,6 +4769,24 @@
         <v>9</v>
       </c>
       <c r="E124" t="n">
+        <v>4</v>
+      </c>
+      <c r="F124" t="n">
+        <v>1</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0</v>
+      </c>
+      <c r="J124" t="n">
+        <v>2</v>
+      </c>
+      <c r="K124" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -2560,6 +4804,24 @@
         <v>7</v>
       </c>
       <c r="E125" t="n">
+        <v>0</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0</v>
+      </c>
+      <c r="K125" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -2577,6 +4839,24 @@
         <v>9</v>
       </c>
       <c r="E126" t="n">
+        <v>0</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0</v>
+      </c>
+      <c r="K126" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -2594,6 +4874,24 @@
         <v>7</v>
       </c>
       <c r="E127" t="n">
+        <v>0</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0</v>
+      </c>
+      <c r="K127" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -2611,6 +4909,24 @@
         <v>9</v>
       </c>
       <c r="E128" t="n">
+        <v>0</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0</v>
+      </c>
+      <c r="K128" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -2628,6 +4944,24 @@
         <v>7</v>
       </c>
       <c r="E129" t="n">
+        <v>2</v>
+      </c>
+      <c r="F129" t="n">
+        <v>2</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0</v>
+      </c>
+      <c r="J129" t="n">
+        <v>2</v>
+      </c>
+      <c r="K129" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -2645,6 +4979,24 @@
         <v>9</v>
       </c>
       <c r="E130" t="n">
+        <v>6</v>
+      </c>
+      <c r="F130" t="n">
+        <v>1</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0</v>
+      </c>
+      <c r="J130" t="n">
+        <v>1</v>
+      </c>
+      <c r="K130" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -2662,6 +5014,24 @@
         <v>7</v>
       </c>
       <c r="E131" t="n">
+        <v>7</v>
+      </c>
+      <c r="F131" t="n">
+        <v>4</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0</v>
+      </c>
+      <c r="J131" t="n">
+        <v>6</v>
+      </c>
+      <c r="K131" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -2679,6 +5049,24 @@
         <v>9</v>
       </c>
       <c r="E132" t="n">
+        <v>3</v>
+      </c>
+      <c r="F132" t="n">
+        <v>1</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0</v>
+      </c>
+      <c r="J132" t="n">
+        <v>2</v>
+      </c>
+      <c r="K132" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -2696,6 +5084,24 @@
         <v>7</v>
       </c>
       <c r="E133" t="n">
+        <v>2</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0</v>
+      </c>
+      <c r="K133" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -2713,6 +5119,24 @@
         <v>9</v>
       </c>
       <c r="E134" t="n">
+        <v>3</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0</v>
+      </c>
+      <c r="K134" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -2730,6 +5154,24 @@
         <v>7</v>
       </c>
       <c r="E135" t="n">
+        <v>2</v>
+      </c>
+      <c r="F135" t="n">
+        <v>1</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0</v>
+      </c>
+      <c r="J135" t="n">
+        <v>2</v>
+      </c>
+      <c r="K135" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -2747,6 +5189,24 @@
         <v>7</v>
       </c>
       <c r="E136" t="n">
+        <v>2</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0</v>
+      </c>
+      <c r="J136" t="n">
+        <v>1</v>
+      </c>
+      <c r="K136" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -2764,6 +5224,24 @@
         <v>7</v>
       </c>
       <c r="E137" t="n">
+        <v>10</v>
+      </c>
+      <c r="F137" t="n">
+        <v>2</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0</v>
+      </c>
+      <c r="J137" t="n">
+        <v>1</v>
+      </c>
+      <c r="K137" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -2781,6 +5259,24 @@
         <v>9</v>
       </c>
       <c r="E138" t="n">
+        <v>2</v>
+      </c>
+      <c r="F138" t="n">
+        <v>1</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0</v>
+      </c>
+      <c r="J138" t="n">
+        <v>2</v>
+      </c>
+      <c r="K138" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -2798,6 +5294,24 @@
         <v>7</v>
       </c>
       <c r="E139" t="n">
+        <v>6</v>
+      </c>
+      <c r="F139" t="n">
+        <v>1</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0</v>
+      </c>
+      <c r="J139" t="n">
+        <v>4</v>
+      </c>
+      <c r="K139" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -2815,6 +5329,24 @@
         <v>7</v>
       </c>
       <c r="E140" t="n">
+        <v>1</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0</v>
+      </c>
+      <c r="J140" t="n">
+        <v>1</v>
+      </c>
+      <c r="K140" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -2832,6 +5364,24 @@
         <v>9</v>
       </c>
       <c r="E141" t="n">
+        <v>3</v>
+      </c>
+      <c r="F141" t="n">
+        <v>2</v>
+      </c>
+      <c r="G141" t="n">
+        <v>1</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0</v>
+      </c>
+      <c r="J141" t="n">
+        <v>1</v>
+      </c>
+      <c r="K141" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -2849,6 +5399,24 @@
         <v>7</v>
       </c>
       <c r="E142" t="n">
+        <v>2</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0</v>
+      </c>
+      <c r="K142" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -2866,6 +5434,24 @@
         <v>7</v>
       </c>
       <c r="E143" t="n">
+        <v>4</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0</v>
+      </c>
+      <c r="J143" t="n">
+        <v>3</v>
+      </c>
+      <c r="K143" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -2883,6 +5469,24 @@
         <v>7</v>
       </c>
       <c r="E144" t="n">
+        <v>2</v>
+      </c>
+      <c r="F144" t="n">
+        <v>0</v>
+      </c>
+      <c r="G144" t="n">
+        <v>1</v>
+      </c>
+      <c r="H144" t="n">
+        <v>1</v>
+      </c>
+      <c r="I144" t="n">
+        <v>0</v>
+      </c>
+      <c r="J144" t="n">
+        <v>0</v>
+      </c>
+      <c r="K144" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -2900,6 +5504,24 @@
         <v>7</v>
       </c>
       <c r="E145" t="n">
+        <v>0</v>
+      </c>
+      <c r="F145" t="n">
+        <v>1</v>
+      </c>
+      <c r="G145" t="n">
+        <v>0</v>
+      </c>
+      <c r="H145" t="n">
+        <v>0</v>
+      </c>
+      <c r="I145" t="n">
+        <v>0</v>
+      </c>
+      <c r="J145" t="n">
+        <v>1</v>
+      </c>
+      <c r="K145" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -2917,6 +5539,24 @@
         <v>7</v>
       </c>
       <c r="E146" t="n">
+        <v>4</v>
+      </c>
+      <c r="F146" t="n">
+        <v>0</v>
+      </c>
+      <c r="G146" t="n">
+        <v>0</v>
+      </c>
+      <c r="H146" t="n">
+        <v>0</v>
+      </c>
+      <c r="I146" t="n">
+        <v>0</v>
+      </c>
+      <c r="J146" t="n">
+        <v>2</v>
+      </c>
+      <c r="K146" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -2934,6 +5574,24 @@
         <v>9</v>
       </c>
       <c r="E147" t="n">
+        <v>1</v>
+      </c>
+      <c r="F147" t="n">
+        <v>0</v>
+      </c>
+      <c r="G147" t="n">
+        <v>0</v>
+      </c>
+      <c r="H147" t="n">
+        <v>0</v>
+      </c>
+      <c r="I147" t="n">
+        <v>0</v>
+      </c>
+      <c r="J147" t="n">
+        <v>0</v>
+      </c>
+      <c r="K147" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -2951,6 +5609,24 @@
         <v>7</v>
       </c>
       <c r="E148" t="n">
+        <v>1</v>
+      </c>
+      <c r="F148" t="n">
+        <v>1</v>
+      </c>
+      <c r="G148" t="n">
+        <v>0</v>
+      </c>
+      <c r="H148" t="n">
+        <v>0</v>
+      </c>
+      <c r="I148" t="n">
+        <v>0</v>
+      </c>
+      <c r="J148" t="n">
+        <v>2</v>
+      </c>
+      <c r="K148" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -2968,6 +5644,24 @@
         <v>9</v>
       </c>
       <c r="E149" t="n">
+        <v>1</v>
+      </c>
+      <c r="F149" t="n">
+        <v>0</v>
+      </c>
+      <c r="G149" t="n">
+        <v>0</v>
+      </c>
+      <c r="H149" t="n">
+        <v>0</v>
+      </c>
+      <c r="I149" t="n">
+        <v>0</v>
+      </c>
+      <c r="J149" t="n">
+        <v>1</v>
+      </c>
+      <c r="K149" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -2985,6 +5679,24 @@
         <v>7</v>
       </c>
       <c r="E150" t="n">
+        <v>22</v>
+      </c>
+      <c r="F150" t="n">
+        <v>3</v>
+      </c>
+      <c r="G150" t="n">
+        <v>0</v>
+      </c>
+      <c r="H150" t="n">
+        <v>0</v>
+      </c>
+      <c r="I150" t="n">
+        <v>0</v>
+      </c>
+      <c r="J150" t="n">
+        <v>12</v>
+      </c>
+      <c r="K150" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -3002,6 +5714,24 @@
         <v>9</v>
       </c>
       <c r="E151" t="n">
+        <v>9</v>
+      </c>
+      <c r="F151" t="n">
+        <v>4</v>
+      </c>
+      <c r="G151" t="n">
+        <v>0</v>
+      </c>
+      <c r="H151" t="n">
+        <v>1</v>
+      </c>
+      <c r="I151" t="n">
+        <v>0</v>
+      </c>
+      <c r="J151" t="n">
+        <v>5</v>
+      </c>
+      <c r="K151" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -3019,6 +5749,24 @@
         <v>7</v>
       </c>
       <c r="E152" t="n">
+        <v>2</v>
+      </c>
+      <c r="F152" t="n">
+        <v>1</v>
+      </c>
+      <c r="G152" t="n">
+        <v>0</v>
+      </c>
+      <c r="H152" t="n">
+        <v>0</v>
+      </c>
+      <c r="I152" t="n">
+        <v>0</v>
+      </c>
+      <c r="J152" t="n">
+        <v>3</v>
+      </c>
+      <c r="K152" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -3036,6 +5784,24 @@
         <v>9</v>
       </c>
       <c r="E153" t="n">
+        <v>2</v>
+      </c>
+      <c r="F153" t="n">
+        <v>2</v>
+      </c>
+      <c r="G153" t="n">
+        <v>0</v>
+      </c>
+      <c r="H153" t="n">
+        <v>0</v>
+      </c>
+      <c r="I153" t="n">
+        <v>0</v>
+      </c>
+      <c r="J153" t="n">
+        <v>1</v>
+      </c>
+      <c r="K153" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -3053,6 +5819,24 @@
         <v>7</v>
       </c>
       <c r="E154" t="n">
+        <v>13</v>
+      </c>
+      <c r="F154" t="n">
+        <v>1</v>
+      </c>
+      <c r="G154" t="n">
+        <v>0</v>
+      </c>
+      <c r="H154" t="n">
+        <v>0</v>
+      </c>
+      <c r="I154" t="n">
+        <v>0</v>
+      </c>
+      <c r="J154" t="n">
+        <v>7</v>
+      </c>
+      <c r="K154" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -3070,6 +5854,24 @@
         <v>9</v>
       </c>
       <c r="E155" t="n">
+        <v>29</v>
+      </c>
+      <c r="F155" t="n">
+        <v>4</v>
+      </c>
+      <c r="G155" t="n">
+        <v>0</v>
+      </c>
+      <c r="H155" t="n">
+        <v>0</v>
+      </c>
+      <c r="I155" t="n">
+        <v>0</v>
+      </c>
+      <c r="J155" t="n">
+        <v>11</v>
+      </c>
+      <c r="K155" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -3087,6 +5889,24 @@
         <v>7</v>
       </c>
       <c r="E156" t="n">
+        <v>1</v>
+      </c>
+      <c r="F156" t="n">
+        <v>0</v>
+      </c>
+      <c r="G156" t="n">
+        <v>0</v>
+      </c>
+      <c r="H156" t="n">
+        <v>0</v>
+      </c>
+      <c r="I156" t="n">
+        <v>0</v>
+      </c>
+      <c r="J156" t="n">
+        <v>0</v>
+      </c>
+      <c r="K156" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -3104,6 +5924,24 @@
         <v>9</v>
       </c>
       <c r="E157" t="n">
+        <v>4</v>
+      </c>
+      <c r="F157" t="n">
+        <v>0</v>
+      </c>
+      <c r="G157" t="n">
+        <v>0</v>
+      </c>
+      <c r="H157" t="n">
+        <v>0</v>
+      </c>
+      <c r="I157" t="n">
+        <v>0</v>
+      </c>
+      <c r="J157" t="n">
+        <v>1</v>
+      </c>
+      <c r="K157" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -3121,6 +5959,24 @@
         <v>7</v>
       </c>
       <c r="E158" t="n">
+        <v>5</v>
+      </c>
+      <c r="F158" t="n">
+        <v>1</v>
+      </c>
+      <c r="G158" t="n">
+        <v>0</v>
+      </c>
+      <c r="H158" t="n">
+        <v>2</v>
+      </c>
+      <c r="I158" t="n">
+        <v>0</v>
+      </c>
+      <c r="J158" t="n">
+        <v>1</v>
+      </c>
+      <c r="K158" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -3138,6 +5994,24 @@
         <v>9</v>
       </c>
       <c r="E159" t="n">
+        <v>7</v>
+      </c>
+      <c r="F159" t="n">
+        <v>1</v>
+      </c>
+      <c r="G159" t="n">
+        <v>0</v>
+      </c>
+      <c r="H159" t="n">
+        <v>1</v>
+      </c>
+      <c r="I159" t="n">
+        <v>0</v>
+      </c>
+      <c r="J159" t="n">
+        <v>0</v>
+      </c>
+      <c r="K159" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -3155,6 +6029,24 @@
         <v>7</v>
       </c>
       <c r="E160" t="n">
+        <v>2</v>
+      </c>
+      <c r="F160" t="n">
+        <v>2</v>
+      </c>
+      <c r="G160" t="n">
+        <v>0</v>
+      </c>
+      <c r="H160" t="n">
+        <v>0</v>
+      </c>
+      <c r="I160" t="n">
+        <v>0</v>
+      </c>
+      <c r="J160" t="n">
+        <v>3</v>
+      </c>
+      <c r="K160" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -3172,6 +6064,24 @@
         <v>9</v>
       </c>
       <c r="E161" t="n">
+        <v>2</v>
+      </c>
+      <c r="F161" t="n">
+        <v>1</v>
+      </c>
+      <c r="G161" t="n">
+        <v>0</v>
+      </c>
+      <c r="H161" t="n">
+        <v>0</v>
+      </c>
+      <c r="I161" t="n">
+        <v>0</v>
+      </c>
+      <c r="J161" t="n">
+        <v>1</v>
+      </c>
+      <c r="K161" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -3189,6 +6099,24 @@
         <v>7</v>
       </c>
       <c r="E162" t="n">
+        <v>0</v>
+      </c>
+      <c r="F162" t="n">
+        <v>1</v>
+      </c>
+      <c r="G162" t="n">
+        <v>0</v>
+      </c>
+      <c r="H162" t="n">
+        <v>0</v>
+      </c>
+      <c r="I162" t="n">
+        <v>0</v>
+      </c>
+      <c r="J162" t="n">
+        <v>0</v>
+      </c>
+      <c r="K162" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -3206,6 +6134,24 @@
         <v>9</v>
       </c>
       <c r="E163" t="n">
+        <v>1</v>
+      </c>
+      <c r="F163" t="n">
+        <v>0</v>
+      </c>
+      <c r="G163" t="n">
+        <v>0</v>
+      </c>
+      <c r="H163" t="n">
+        <v>0</v>
+      </c>
+      <c r="I163" t="n">
+        <v>0</v>
+      </c>
+      <c r="J163" t="n">
+        <v>0</v>
+      </c>
+      <c r="K163" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -3223,6 +6169,24 @@
         <v>7</v>
       </c>
       <c r="E164" t="n">
+        <v>27</v>
+      </c>
+      <c r="F164" t="n">
+        <v>10</v>
+      </c>
+      <c r="G164" t="n">
+        <v>0</v>
+      </c>
+      <c r="H164" t="n">
+        <v>6</v>
+      </c>
+      <c r="I164" t="n">
+        <v>0</v>
+      </c>
+      <c r="J164" t="n">
+        <v>17</v>
+      </c>
+      <c r="K164" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -3240,6 +6204,24 @@
         <v>9</v>
       </c>
       <c r="E165" t="n">
+        <v>27</v>
+      </c>
+      <c r="F165" t="n">
+        <v>6</v>
+      </c>
+      <c r="G165" t="n">
+        <v>1</v>
+      </c>
+      <c r="H165" t="n">
+        <v>1</v>
+      </c>
+      <c r="I165" t="n">
+        <v>0</v>
+      </c>
+      <c r="J165" t="n">
+        <v>17</v>
+      </c>
+      <c r="K165" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -3257,6 +6239,24 @@
         <v>7</v>
       </c>
       <c r="E166" t="n">
+        <v>6</v>
+      </c>
+      <c r="F166" t="n">
+        <v>0</v>
+      </c>
+      <c r="G166" t="n">
+        <v>0</v>
+      </c>
+      <c r="H166" t="n">
+        <v>0</v>
+      </c>
+      <c r="I166" t="n">
+        <v>0</v>
+      </c>
+      <c r="J166" t="n">
+        <v>1</v>
+      </c>
+      <c r="K166" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -3274,6 +6274,24 @@
         <v>9</v>
       </c>
       <c r="E167" t="n">
+        <v>3</v>
+      </c>
+      <c r="F167" t="n">
+        <v>3</v>
+      </c>
+      <c r="G167" t="n">
+        <v>0</v>
+      </c>
+      <c r="H167" t="n">
+        <v>0</v>
+      </c>
+      <c r="I167" t="n">
+        <v>1</v>
+      </c>
+      <c r="J167" t="n">
+        <v>2</v>
+      </c>
+      <c r="K167" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -3291,6 +6309,24 @@
         <v>7</v>
       </c>
       <c r="E168" t="n">
+        <v>4</v>
+      </c>
+      <c r="F168" t="n">
+        <v>5</v>
+      </c>
+      <c r="G168" t="n">
+        <v>1</v>
+      </c>
+      <c r="H168" t="n">
+        <v>0</v>
+      </c>
+      <c r="I168" t="n">
+        <v>0</v>
+      </c>
+      <c r="J168" t="n">
+        <v>3</v>
+      </c>
+      <c r="K168" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -3308,6 +6344,24 @@
         <v>9</v>
       </c>
       <c r="E169" t="n">
+        <v>5</v>
+      </c>
+      <c r="F169" t="n">
+        <v>0</v>
+      </c>
+      <c r="G169" t="n">
+        <v>0</v>
+      </c>
+      <c r="H169" t="n">
+        <v>0</v>
+      </c>
+      <c r="I169" t="n">
+        <v>0</v>
+      </c>
+      <c r="J169" t="n">
+        <v>1</v>
+      </c>
+      <c r="K169" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -3325,6 +6379,24 @@
         <v>7</v>
       </c>
       <c r="E170" t="n">
+        <v>4</v>
+      </c>
+      <c r="F170" t="n">
+        <v>1</v>
+      </c>
+      <c r="G170" t="n">
+        <v>0</v>
+      </c>
+      <c r="H170" t="n">
+        <v>1</v>
+      </c>
+      <c r="I170" t="n">
+        <v>0</v>
+      </c>
+      <c r="J170" t="n">
+        <v>3</v>
+      </c>
+      <c r="K170" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -3342,6 +6414,24 @@
         <v>9</v>
       </c>
       <c r="E171" t="n">
+        <v>36</v>
+      </c>
+      <c r="F171" t="n">
+        <v>4</v>
+      </c>
+      <c r="G171" t="n">
+        <v>0</v>
+      </c>
+      <c r="H171" t="n">
+        <v>1</v>
+      </c>
+      <c r="I171" t="n">
+        <v>0</v>
+      </c>
+      <c r="J171" t="n">
+        <v>15</v>
+      </c>
+      <c r="K171" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -3359,6 +6449,24 @@
         <v>7</v>
       </c>
       <c r="E172" t="n">
+        <v>4</v>
+      </c>
+      <c r="F172" t="n">
+        <v>0</v>
+      </c>
+      <c r="G172" t="n">
+        <v>0</v>
+      </c>
+      <c r="H172" t="n">
+        <v>0</v>
+      </c>
+      <c r="I172" t="n">
+        <v>0</v>
+      </c>
+      <c r="J172" t="n">
+        <v>0</v>
+      </c>
+      <c r="K172" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -3376,6 +6484,24 @@
         <v>9</v>
       </c>
       <c r="E173" t="n">
+        <v>4</v>
+      </c>
+      <c r="F173" t="n">
+        <v>2</v>
+      </c>
+      <c r="G173" t="n">
+        <v>0</v>
+      </c>
+      <c r="H173" t="n">
+        <v>0</v>
+      </c>
+      <c r="I173" t="n">
+        <v>0</v>
+      </c>
+      <c r="J173" t="n">
+        <v>0</v>
+      </c>
+      <c r="K173" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -3393,6 +6519,24 @@
         <v>7</v>
       </c>
       <c r="E174" t="n">
+        <v>1</v>
+      </c>
+      <c r="F174" t="n">
+        <v>1</v>
+      </c>
+      <c r="G174" t="n">
+        <v>0</v>
+      </c>
+      <c r="H174" t="n">
+        <v>0</v>
+      </c>
+      <c r="I174" t="n">
+        <v>0</v>
+      </c>
+      <c r="J174" t="n">
+        <v>2</v>
+      </c>
+      <c r="K174" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -3410,6 +6554,24 @@
         <v>7</v>
       </c>
       <c r="E175" t="n">
+        <v>5</v>
+      </c>
+      <c r="F175" t="n">
+        <v>2</v>
+      </c>
+      <c r="G175" t="n">
+        <v>0</v>
+      </c>
+      <c r="H175" t="n">
+        <v>0</v>
+      </c>
+      <c r="I175" t="n">
+        <v>0</v>
+      </c>
+      <c r="J175" t="n">
+        <v>2</v>
+      </c>
+      <c r="K175" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -3427,6 +6589,24 @@
         <v>9</v>
       </c>
       <c r="E176" t="n">
+        <v>2</v>
+      </c>
+      <c r="F176" t="n">
+        <v>1</v>
+      </c>
+      <c r="G176" t="n">
+        <v>0</v>
+      </c>
+      <c r="H176" t="n">
+        <v>0</v>
+      </c>
+      <c r="I176" t="n">
+        <v>0</v>
+      </c>
+      <c r="J176" t="n">
+        <v>0</v>
+      </c>
+      <c r="K176" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -3444,6 +6624,24 @@
         <v>7</v>
       </c>
       <c r="E177" t="n">
+        <v>0</v>
+      </c>
+      <c r="F177" t="n">
+        <v>1</v>
+      </c>
+      <c r="G177" t="n">
+        <v>0</v>
+      </c>
+      <c r="H177" t="n">
+        <v>0</v>
+      </c>
+      <c r="I177" t="n">
+        <v>0</v>
+      </c>
+      <c r="J177" t="n">
+        <v>1</v>
+      </c>
+      <c r="K177" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -3461,6 +6659,24 @@
         <v>9</v>
       </c>
       <c r="E178" t="n">
+        <v>2</v>
+      </c>
+      <c r="F178" t="n">
+        <v>1</v>
+      </c>
+      <c r="G178" t="n">
+        <v>0</v>
+      </c>
+      <c r="H178" t="n">
+        <v>0</v>
+      </c>
+      <c r="I178" t="n">
+        <v>0</v>
+      </c>
+      <c r="J178" t="n">
+        <v>2</v>
+      </c>
+      <c r="K178" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -3478,6 +6694,24 @@
         <v>7</v>
       </c>
       <c r="E179" t="n">
+        <v>3</v>
+      </c>
+      <c r="F179" t="n">
+        <v>0</v>
+      </c>
+      <c r="G179" t="n">
+        <v>0</v>
+      </c>
+      <c r="H179" t="n">
+        <v>0</v>
+      </c>
+      <c r="I179" t="n">
+        <v>0</v>
+      </c>
+      <c r="J179" t="n">
+        <v>1</v>
+      </c>
+      <c r="K179" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -3495,6 +6729,24 @@
         <v>7</v>
       </c>
       <c r="E180" t="n">
+        <v>1</v>
+      </c>
+      <c r="F180" t="n">
+        <v>2</v>
+      </c>
+      <c r="G180" t="n">
+        <v>0</v>
+      </c>
+      <c r="H180" t="n">
+        <v>0</v>
+      </c>
+      <c r="I180" t="n">
+        <v>0</v>
+      </c>
+      <c r="J180" t="n">
+        <v>1</v>
+      </c>
+      <c r="K180" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -3512,6 +6764,24 @@
         <v>7</v>
       </c>
       <c r="E181" t="n">
+        <v>14</v>
+      </c>
+      <c r="F181" t="n">
+        <v>5</v>
+      </c>
+      <c r="G181" t="n">
+        <v>0</v>
+      </c>
+      <c r="H181" t="n">
+        <v>1</v>
+      </c>
+      <c r="I181" t="n">
+        <v>1</v>
+      </c>
+      <c r="J181" t="n">
+        <v>16</v>
+      </c>
+      <c r="K181" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -3529,6 +6799,24 @@
         <v>9</v>
       </c>
       <c r="E182" t="n">
+        <v>14</v>
+      </c>
+      <c r="F182" t="n">
+        <v>4</v>
+      </c>
+      <c r="G182" t="n">
+        <v>0</v>
+      </c>
+      <c r="H182" t="n">
+        <v>1</v>
+      </c>
+      <c r="I182" t="n">
+        <v>0</v>
+      </c>
+      <c r="J182" t="n">
+        <v>9</v>
+      </c>
+      <c r="K182" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -3546,6 +6834,24 @@
         <v>7</v>
       </c>
       <c r="E183" t="n">
+        <v>10</v>
+      </c>
+      <c r="F183" t="n">
+        <v>5</v>
+      </c>
+      <c r="G183" t="n">
+        <v>0</v>
+      </c>
+      <c r="H183" t="n">
+        <v>0</v>
+      </c>
+      <c r="I183" t="n">
+        <v>0</v>
+      </c>
+      <c r="J183" t="n">
+        <v>7</v>
+      </c>
+      <c r="K183" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -3563,6 +6869,24 @@
         <v>9</v>
       </c>
       <c r="E184" t="n">
+        <v>14</v>
+      </c>
+      <c r="F184" t="n">
+        <v>3</v>
+      </c>
+      <c r="G184" t="n">
+        <v>0</v>
+      </c>
+      <c r="H184" t="n">
+        <v>0</v>
+      </c>
+      <c r="I184" t="n">
+        <v>0</v>
+      </c>
+      <c r="J184" t="n">
+        <v>8</v>
+      </c>
+      <c r="K184" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -3580,6 +6904,24 @@
         <v>7</v>
       </c>
       <c r="E185" t="n">
+        <v>2</v>
+      </c>
+      <c r="F185" t="n">
+        <v>1</v>
+      </c>
+      <c r="G185" t="n">
+        <v>0</v>
+      </c>
+      <c r="H185" t="n">
+        <v>0</v>
+      </c>
+      <c r="I185" t="n">
+        <v>0</v>
+      </c>
+      <c r="J185" t="n">
+        <v>1</v>
+      </c>
+      <c r="K185" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -3597,6 +6939,24 @@
         <v>9</v>
       </c>
       <c r="E186" t="n">
+        <v>0</v>
+      </c>
+      <c r="F186" t="n">
+        <v>0</v>
+      </c>
+      <c r="G186" t="n">
+        <v>0</v>
+      </c>
+      <c r="H186" t="n">
+        <v>0</v>
+      </c>
+      <c r="I186" t="n">
+        <v>0</v>
+      </c>
+      <c r="J186" t="n">
+        <v>0</v>
+      </c>
+      <c r="K186" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -3614,6 +6974,24 @@
         <v>7</v>
       </c>
       <c r="E187" t="n">
+        <v>0</v>
+      </c>
+      <c r="F187" t="n">
+        <v>0</v>
+      </c>
+      <c r="G187" t="n">
+        <v>0</v>
+      </c>
+      <c r="H187" t="n">
+        <v>0</v>
+      </c>
+      <c r="I187" t="n">
+        <v>0</v>
+      </c>
+      <c r="J187" t="n">
+        <v>0</v>
+      </c>
+      <c r="K187" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -3631,6 +7009,24 @@
         <v>7</v>
       </c>
       <c r="E188" t="n">
+        <v>5</v>
+      </c>
+      <c r="F188" t="n">
+        <v>1</v>
+      </c>
+      <c r="G188" t="n">
+        <v>0</v>
+      </c>
+      <c r="H188" t="n">
+        <v>5</v>
+      </c>
+      <c r="I188" t="n">
+        <v>0</v>
+      </c>
+      <c r="J188" t="n">
+        <v>1</v>
+      </c>
+      <c r="K188" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -3648,6 +7044,24 @@
         <v>9</v>
       </c>
       <c r="E189" t="n">
+        <v>3</v>
+      </c>
+      <c r="F189" t="n">
+        <v>0</v>
+      </c>
+      <c r="G189" t="n">
+        <v>0</v>
+      </c>
+      <c r="H189" t="n">
+        <v>2</v>
+      </c>
+      <c r="I189" t="n">
+        <v>0</v>
+      </c>
+      <c r="J189" t="n">
+        <v>1</v>
+      </c>
+      <c r="K189" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -3665,6 +7079,24 @@
         <v>7</v>
       </c>
       <c r="E190" t="n">
+        <v>2</v>
+      </c>
+      <c r="F190" t="n">
+        <v>0</v>
+      </c>
+      <c r="G190" t="n">
+        <v>0</v>
+      </c>
+      <c r="H190" t="n">
+        <v>0</v>
+      </c>
+      <c r="I190" t="n">
+        <v>0</v>
+      </c>
+      <c r="J190" t="n">
+        <v>1</v>
+      </c>
+      <c r="K190" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -3682,6 +7114,24 @@
         <v>9</v>
       </c>
       <c r="E191" t="n">
+        <v>2</v>
+      </c>
+      <c r="F191" t="n">
+        <v>0</v>
+      </c>
+      <c r="G191" t="n">
+        <v>0</v>
+      </c>
+      <c r="H191" t="n">
+        <v>0</v>
+      </c>
+      <c r="I191" t="n">
+        <v>0</v>
+      </c>
+      <c r="J191" t="n">
+        <v>0</v>
+      </c>
+      <c r="K191" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -3699,6 +7149,24 @@
         <v>7</v>
       </c>
       <c r="E192" t="n">
+        <v>2</v>
+      </c>
+      <c r="F192" t="n">
+        <v>3</v>
+      </c>
+      <c r="G192" t="n">
+        <v>0</v>
+      </c>
+      <c r="H192" t="n">
+        <v>0</v>
+      </c>
+      <c r="I192" t="n">
+        <v>0</v>
+      </c>
+      <c r="J192" t="n">
+        <v>0</v>
+      </c>
+      <c r="K192" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -3716,6 +7184,24 @@
         <v>7</v>
       </c>
       <c r="E193" t="n">
+        <v>4</v>
+      </c>
+      <c r="F193" t="n">
+        <v>1</v>
+      </c>
+      <c r="G193" t="n">
+        <v>0</v>
+      </c>
+      <c r="H193" t="n">
+        <v>0</v>
+      </c>
+      <c r="I193" t="n">
+        <v>0</v>
+      </c>
+      <c r="J193" t="n">
+        <v>2</v>
+      </c>
+      <c r="K193" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -3733,6 +7219,24 @@
         <v>9</v>
       </c>
       <c r="E194" t="n">
+        <v>12</v>
+      </c>
+      <c r="F194" t="n">
+        <v>4</v>
+      </c>
+      <c r="G194" t="n">
+        <v>0</v>
+      </c>
+      <c r="H194" t="n">
+        <v>0</v>
+      </c>
+      <c r="I194" t="n">
+        <v>0</v>
+      </c>
+      <c r="J194" t="n">
+        <v>9</v>
+      </c>
+      <c r="K194" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -3750,6 +7254,24 @@
         <v>7</v>
       </c>
       <c r="E195" t="n">
+        <v>1</v>
+      </c>
+      <c r="F195" t="n">
+        <v>0</v>
+      </c>
+      <c r="G195" t="n">
+        <v>0</v>
+      </c>
+      <c r="H195" t="n">
+        <v>0</v>
+      </c>
+      <c r="I195" t="n">
+        <v>0</v>
+      </c>
+      <c r="J195" t="n">
+        <v>1</v>
+      </c>
+      <c r="K195" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -3767,6 +7289,24 @@
         <v>7</v>
       </c>
       <c r="E196" t="n">
+        <v>1</v>
+      </c>
+      <c r="F196" t="n">
+        <v>0</v>
+      </c>
+      <c r="G196" t="n">
+        <v>0</v>
+      </c>
+      <c r="H196" t="n">
+        <v>0</v>
+      </c>
+      <c r="I196" t="n">
+        <v>0</v>
+      </c>
+      <c r="J196" t="n">
+        <v>1</v>
+      </c>
+      <c r="K196" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -3784,6 +7324,24 @@
         <v>9</v>
       </c>
       <c r="E197" t="n">
+        <v>1</v>
+      </c>
+      <c r="F197" t="n">
+        <v>0</v>
+      </c>
+      <c r="G197" t="n">
+        <v>0</v>
+      </c>
+      <c r="H197" t="n">
+        <v>0</v>
+      </c>
+      <c r="I197" t="n">
+        <v>0</v>
+      </c>
+      <c r="J197" t="n">
+        <v>1</v>
+      </c>
+      <c r="K197" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -3801,6 +7359,24 @@
         <v>7</v>
       </c>
       <c r="E198" t="n">
+        <v>5</v>
+      </c>
+      <c r="F198" t="n">
+        <v>1</v>
+      </c>
+      <c r="G198" t="n">
+        <v>0</v>
+      </c>
+      <c r="H198" t="n">
+        <v>0</v>
+      </c>
+      <c r="I198" t="n">
+        <v>1</v>
+      </c>
+      <c r="J198" t="n">
+        <v>0</v>
+      </c>
+      <c r="K198" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -3818,6 +7394,24 @@
         <v>7</v>
       </c>
       <c r="E199" t="n">
+        <v>0</v>
+      </c>
+      <c r="F199" t="n">
+        <v>0</v>
+      </c>
+      <c r="G199" t="n">
+        <v>0</v>
+      </c>
+      <c r="H199" t="n">
+        <v>0</v>
+      </c>
+      <c r="I199" t="n">
+        <v>0</v>
+      </c>
+      <c r="J199" t="n">
+        <v>0</v>
+      </c>
+      <c r="K199" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -3835,6 +7429,24 @@
         <v>7</v>
       </c>
       <c r="E200" t="n">
+        <v>6</v>
+      </c>
+      <c r="F200" t="n">
+        <v>1</v>
+      </c>
+      <c r="G200" t="n">
+        <v>0</v>
+      </c>
+      <c r="H200" t="n">
+        <v>0</v>
+      </c>
+      <c r="I200" t="n">
+        <v>0</v>
+      </c>
+      <c r="J200" t="n">
+        <v>3</v>
+      </c>
+      <c r="K200" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -3852,6 +7464,24 @@
         <v>9</v>
       </c>
       <c r="E201" t="n">
+        <v>6</v>
+      </c>
+      <c r="F201" t="n">
+        <v>2</v>
+      </c>
+      <c r="G201" t="n">
+        <v>0</v>
+      </c>
+      <c r="H201" t="n">
+        <v>0</v>
+      </c>
+      <c r="I201" t="n">
+        <v>0</v>
+      </c>
+      <c r="J201" t="n">
+        <v>2</v>
+      </c>
+      <c r="K201" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -3869,6 +7499,24 @@
         <v>7</v>
       </c>
       <c r="E202" t="n">
+        <v>4</v>
+      </c>
+      <c r="F202" t="n">
+        <v>1</v>
+      </c>
+      <c r="G202" t="n">
+        <v>0</v>
+      </c>
+      <c r="H202" t="n">
+        <v>0</v>
+      </c>
+      <c r="I202" t="n">
+        <v>0</v>
+      </c>
+      <c r="J202" t="n">
+        <v>1</v>
+      </c>
+      <c r="K202" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -3886,6 +7534,24 @@
         <v>7</v>
       </c>
       <c r="E203" t="n">
+        <v>3</v>
+      </c>
+      <c r="F203" t="n">
+        <v>1</v>
+      </c>
+      <c r="G203" t="n">
+        <v>0</v>
+      </c>
+      <c r="H203" t="n">
+        <v>0</v>
+      </c>
+      <c r="I203" t="n">
+        <v>0</v>
+      </c>
+      <c r="J203" t="n">
+        <v>2</v>
+      </c>
+      <c r="K203" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -3903,6 +7569,24 @@
         <v>9</v>
       </c>
       <c r="E204" t="n">
+        <v>9</v>
+      </c>
+      <c r="F204" t="n">
+        <v>0</v>
+      </c>
+      <c r="G204" t="n">
+        <v>0</v>
+      </c>
+      <c r="H204" t="n">
+        <v>1</v>
+      </c>
+      <c r="I204" t="n">
+        <v>0</v>
+      </c>
+      <c r="J204" t="n">
+        <v>3</v>
+      </c>
+      <c r="K204" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -3920,6 +7604,24 @@
         <v>7</v>
       </c>
       <c r="E205" t="n">
+        <v>4</v>
+      </c>
+      <c r="F205" t="n">
+        <v>1</v>
+      </c>
+      <c r="G205" t="n">
+        <v>0</v>
+      </c>
+      <c r="H205" t="n">
+        <v>0</v>
+      </c>
+      <c r="I205" t="n">
+        <v>0</v>
+      </c>
+      <c r="J205" t="n">
+        <v>3</v>
+      </c>
+      <c r="K205" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -3937,6 +7639,24 @@
         <v>9</v>
       </c>
       <c r="E206" t="n">
+        <v>3</v>
+      </c>
+      <c r="F206" t="n">
+        <v>0</v>
+      </c>
+      <c r="G206" t="n">
+        <v>0</v>
+      </c>
+      <c r="H206" t="n">
+        <v>1</v>
+      </c>
+      <c r="I206" t="n">
+        <v>0</v>
+      </c>
+      <c r="J206" t="n">
+        <v>1</v>
+      </c>
+      <c r="K206" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -3954,6 +7674,24 @@
         <v>7</v>
       </c>
       <c r="E207" t="n">
+        <v>10</v>
+      </c>
+      <c r="F207" t="n">
+        <v>7</v>
+      </c>
+      <c r="G207" t="n">
+        <v>0</v>
+      </c>
+      <c r="H207" t="n">
+        <v>0</v>
+      </c>
+      <c r="I207" t="n">
+        <v>0</v>
+      </c>
+      <c r="J207" t="n">
+        <v>12</v>
+      </c>
+      <c r="K207" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -3971,6 +7709,24 @@
         <v>9</v>
       </c>
       <c r="E208" t="n">
+        <v>11</v>
+      </c>
+      <c r="F208" t="n">
+        <v>3</v>
+      </c>
+      <c r="G208" t="n">
+        <v>0</v>
+      </c>
+      <c r="H208" t="n">
+        <v>0</v>
+      </c>
+      <c r="I208" t="n">
+        <v>1</v>
+      </c>
+      <c r="J208" t="n">
+        <v>5</v>
+      </c>
+      <c r="K208" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -3988,6 +7744,24 @@
         <v>7</v>
       </c>
       <c r="E209" t="n">
+        <v>4</v>
+      </c>
+      <c r="F209" t="n">
+        <v>3</v>
+      </c>
+      <c r="G209" t="n">
+        <v>0</v>
+      </c>
+      <c r="H209" t="n">
+        <v>0</v>
+      </c>
+      <c r="I209" t="n">
+        <v>0</v>
+      </c>
+      <c r="J209" t="n">
+        <v>6</v>
+      </c>
+      <c r="K209" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -4005,6 +7779,24 @@
         <v>9</v>
       </c>
       <c r="E210" t="n">
+        <v>3</v>
+      </c>
+      <c r="F210" t="n">
+        <v>0</v>
+      </c>
+      <c r="G210" t="n">
+        <v>0</v>
+      </c>
+      <c r="H210" t="n">
+        <v>0</v>
+      </c>
+      <c r="I210" t="n">
+        <v>0</v>
+      </c>
+      <c r="J210" t="n">
+        <v>2</v>
+      </c>
+      <c r="K210" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -4022,6 +7814,24 @@
         <v>7</v>
       </c>
       <c r="E211" t="n">
+        <v>0</v>
+      </c>
+      <c r="F211" t="n">
+        <v>0</v>
+      </c>
+      <c r="G211" t="n">
+        <v>0</v>
+      </c>
+      <c r="H211" t="n">
+        <v>0</v>
+      </c>
+      <c r="I211" t="n">
+        <v>0</v>
+      </c>
+      <c r="J211" t="n">
+        <v>0</v>
+      </c>
+      <c r="K211" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -4039,6 +7849,24 @@
         <v>7</v>
       </c>
       <c r="E212" t="n">
+        <v>3</v>
+      </c>
+      <c r="F212" t="n">
+        <v>0</v>
+      </c>
+      <c r="G212" t="n">
+        <v>0</v>
+      </c>
+      <c r="H212" t="n">
+        <v>0</v>
+      </c>
+      <c r="I212" t="n">
+        <v>1</v>
+      </c>
+      <c r="J212" t="n">
+        <v>2</v>
+      </c>
+      <c r="K212" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -4056,6 +7884,24 @@
         <v>7</v>
       </c>
       <c r="E213" t="n">
+        <v>7</v>
+      </c>
+      <c r="F213" t="n">
+        <v>2</v>
+      </c>
+      <c r="G213" t="n">
+        <v>0</v>
+      </c>
+      <c r="H213" t="n">
+        <v>1</v>
+      </c>
+      <c r="I213" t="n">
+        <v>1</v>
+      </c>
+      <c r="J213" t="n">
+        <v>3</v>
+      </c>
+      <c r="K213" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -4073,6 +7919,24 @@
         <v>9</v>
       </c>
       <c r="E214" t="n">
+        <v>4</v>
+      </c>
+      <c r="F214" t="n">
+        <v>1</v>
+      </c>
+      <c r="G214" t="n">
+        <v>0</v>
+      </c>
+      <c r="H214" t="n">
+        <v>0</v>
+      </c>
+      <c r="I214" t="n">
+        <v>2</v>
+      </c>
+      <c r="J214" t="n">
+        <v>1</v>
+      </c>
+      <c r="K214" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -4090,6 +7954,24 @@
         <v>9</v>
       </c>
       <c r="E215" t="n">
+        <v>1</v>
+      </c>
+      <c r="F215" t="n">
+        <v>0</v>
+      </c>
+      <c r="G215" t="n">
+        <v>0</v>
+      </c>
+      <c r="H215" t="n">
+        <v>0</v>
+      </c>
+      <c r="I215" t="n">
+        <v>0</v>
+      </c>
+      <c r="J215" t="n">
+        <v>0</v>
+      </c>
+      <c r="K215" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -4107,6 +7989,24 @@
         <v>7</v>
       </c>
       <c r="E216" t="n">
+        <v>4</v>
+      </c>
+      <c r="F216" t="n">
+        <v>2</v>
+      </c>
+      <c r="G216" t="n">
+        <v>0</v>
+      </c>
+      <c r="H216" t="n">
+        <v>0</v>
+      </c>
+      <c r="I216" t="n">
+        <v>0</v>
+      </c>
+      <c r="J216" t="n">
+        <v>0</v>
+      </c>
+      <c r="K216" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -4124,6 +8024,24 @@
         <v>9</v>
       </c>
       <c r="E217" t="n">
+        <v>0</v>
+      </c>
+      <c r="F217" t="n">
+        <v>1</v>
+      </c>
+      <c r="G217" t="n">
+        <v>0</v>
+      </c>
+      <c r="H217" t="n">
+        <v>0</v>
+      </c>
+      <c r="I217" t="n">
+        <v>0</v>
+      </c>
+      <c r="J217" t="n">
+        <v>1</v>
+      </c>
+      <c r="K217" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -4141,6 +8059,24 @@
         <v>7</v>
       </c>
       <c r="E218" t="n">
+        <v>5</v>
+      </c>
+      <c r="F218" t="n">
+        <v>1</v>
+      </c>
+      <c r="G218" t="n">
+        <v>0</v>
+      </c>
+      <c r="H218" t="n">
+        <v>0</v>
+      </c>
+      <c r="I218" t="n">
+        <v>0</v>
+      </c>
+      <c r="J218" t="n">
+        <v>4</v>
+      </c>
+      <c r="K218" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -4158,6 +8094,24 @@
         <v>9</v>
       </c>
       <c r="E219" t="n">
+        <v>1</v>
+      </c>
+      <c r="F219" t="n">
+        <v>0</v>
+      </c>
+      <c r="G219" t="n">
+        <v>0</v>
+      </c>
+      <c r="H219" t="n">
+        <v>0</v>
+      </c>
+      <c r="I219" t="n">
+        <v>0</v>
+      </c>
+      <c r="J219" t="n">
+        <v>1</v>
+      </c>
+      <c r="K219" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -4175,6 +8129,24 @@
         <v>7</v>
       </c>
       <c r="E220" t="n">
+        <v>4</v>
+      </c>
+      <c r="F220" t="n">
+        <v>0</v>
+      </c>
+      <c r="G220" t="n">
+        <v>0</v>
+      </c>
+      <c r="H220" t="n">
+        <v>0</v>
+      </c>
+      <c r="I220" t="n">
+        <v>0</v>
+      </c>
+      <c r="J220" t="n">
+        <v>2</v>
+      </c>
+      <c r="K220" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -4192,6 +8164,24 @@
         <v>9</v>
       </c>
       <c r="E221" t="n">
+        <v>3</v>
+      </c>
+      <c r="F221" t="n">
+        <v>1</v>
+      </c>
+      <c r="G221" t="n">
+        <v>0</v>
+      </c>
+      <c r="H221" t="n">
+        <v>0</v>
+      </c>
+      <c r="I221" t="n">
+        <v>0</v>
+      </c>
+      <c r="J221" t="n">
+        <v>3</v>
+      </c>
+      <c r="K221" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -4209,6 +8199,24 @@
         <v>7</v>
       </c>
       <c r="E222" t="n">
+        <v>4</v>
+      </c>
+      <c r="F222" t="n">
+        <v>1</v>
+      </c>
+      <c r="G222" t="n">
+        <v>0</v>
+      </c>
+      <c r="H222" t="n">
+        <v>0</v>
+      </c>
+      <c r="I222" t="n">
+        <v>0</v>
+      </c>
+      <c r="J222" t="n">
+        <v>3</v>
+      </c>
+      <c r="K222" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -4226,6 +8234,24 @@
         <v>9</v>
       </c>
       <c r="E223" t="n">
+        <v>23</v>
+      </c>
+      <c r="F223" t="n">
+        <v>2</v>
+      </c>
+      <c r="G223" t="n">
+        <v>0</v>
+      </c>
+      <c r="H223" t="n">
+        <v>3</v>
+      </c>
+      <c r="I223" t="n">
+        <v>0</v>
+      </c>
+      <c r="J223" t="n">
+        <v>13</v>
+      </c>
+      <c r="K223" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -4243,6 +8269,24 @@
         <v>7</v>
       </c>
       <c r="E224" t="n">
+        <v>1</v>
+      </c>
+      <c r="F224" t="n">
+        <v>0</v>
+      </c>
+      <c r="G224" t="n">
+        <v>0</v>
+      </c>
+      <c r="H224" t="n">
+        <v>0</v>
+      </c>
+      <c r="I224" t="n">
+        <v>0</v>
+      </c>
+      <c r="J224" t="n">
+        <v>1</v>
+      </c>
+      <c r="K224" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -4260,6 +8304,24 @@
         <v>9</v>
       </c>
       <c r="E225" t="n">
+        <v>2</v>
+      </c>
+      <c r="F225" t="n">
+        <v>1</v>
+      </c>
+      <c r="G225" t="n">
+        <v>0</v>
+      </c>
+      <c r="H225" t="n">
+        <v>0</v>
+      </c>
+      <c r="I225" t="n">
+        <v>1</v>
+      </c>
+      <c r="J225" t="n">
+        <v>0</v>
+      </c>
+      <c r="K225" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -4277,6 +8339,24 @@
         <v>7</v>
       </c>
       <c r="E226" t="n">
+        <v>1</v>
+      </c>
+      <c r="F226" t="n">
+        <v>0</v>
+      </c>
+      <c r="G226" t="n">
+        <v>0</v>
+      </c>
+      <c r="H226" t="n">
+        <v>0</v>
+      </c>
+      <c r="I226" t="n">
+        <v>0</v>
+      </c>
+      <c r="J226" t="n">
+        <v>1</v>
+      </c>
+      <c r="K226" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -4294,6 +8374,24 @@
         <v>9</v>
       </c>
       <c r="E227" t="n">
+        <v>1</v>
+      </c>
+      <c r="F227" t="n">
+        <v>2</v>
+      </c>
+      <c r="G227" t="n">
+        <v>0</v>
+      </c>
+      <c r="H227" t="n">
+        <v>0</v>
+      </c>
+      <c r="I227" t="n">
+        <v>0</v>
+      </c>
+      <c r="J227" t="n">
+        <v>1</v>
+      </c>
+      <c r="K227" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -4311,6 +8409,24 @@
         <v>7</v>
       </c>
       <c r="E228" t="n">
+        <v>2</v>
+      </c>
+      <c r="F228" t="n">
+        <v>0</v>
+      </c>
+      <c r="G228" t="n">
+        <v>0</v>
+      </c>
+      <c r="H228" t="n">
+        <v>0</v>
+      </c>
+      <c r="I228" t="n">
+        <v>0</v>
+      </c>
+      <c r="J228" t="n">
+        <v>0</v>
+      </c>
+      <c r="K228" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -4328,6 +8444,24 @@
         <v>9</v>
       </c>
       <c r="E229" t="n">
+        <v>5</v>
+      </c>
+      <c r="F229" t="n">
+        <v>0</v>
+      </c>
+      <c r="G229" t="n">
+        <v>0</v>
+      </c>
+      <c r="H229" t="n">
+        <v>0</v>
+      </c>
+      <c r="I229" t="n">
+        <v>0</v>
+      </c>
+      <c r="J229" t="n">
+        <v>4</v>
+      </c>
+      <c r="K229" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -4345,6 +8479,24 @@
         <v>7</v>
       </c>
       <c r="E230" t="n">
+        <v>3</v>
+      </c>
+      <c r="F230" t="n">
+        <v>1</v>
+      </c>
+      <c r="G230" t="n">
+        <v>0</v>
+      </c>
+      <c r="H230" t="n">
+        <v>0</v>
+      </c>
+      <c r="I230" t="n">
+        <v>0</v>
+      </c>
+      <c r="J230" t="n">
+        <v>2</v>
+      </c>
+      <c r="K230" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -4362,6 +8514,24 @@
         <v>9</v>
       </c>
       <c r="E231" t="n">
+        <v>2</v>
+      </c>
+      <c r="F231" t="n">
+        <v>0</v>
+      </c>
+      <c r="G231" t="n">
+        <v>0</v>
+      </c>
+      <c r="H231" t="n">
+        <v>0</v>
+      </c>
+      <c r="I231" t="n">
+        <v>1</v>
+      </c>
+      <c r="J231" t="n">
+        <v>0</v>
+      </c>
+      <c r="K231" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -4379,6 +8549,24 @@
         <v>7</v>
       </c>
       <c r="E232" t="n">
+        <v>3</v>
+      </c>
+      <c r="F232" t="n">
+        <v>1</v>
+      </c>
+      <c r="G232" t="n">
+        <v>0</v>
+      </c>
+      <c r="H232" t="n">
+        <v>0</v>
+      </c>
+      <c r="I232" t="n">
+        <v>0</v>
+      </c>
+      <c r="J232" t="n">
+        <v>3</v>
+      </c>
+      <c r="K232" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -4396,6 +8584,24 @@
         <v>9</v>
       </c>
       <c r="E233" t="n">
+        <v>4</v>
+      </c>
+      <c r="F233" t="n">
+        <v>0</v>
+      </c>
+      <c r="G233" t="n">
+        <v>0</v>
+      </c>
+      <c r="H233" t="n">
+        <v>0</v>
+      </c>
+      <c r="I233" t="n">
+        <v>0</v>
+      </c>
+      <c r="J233" t="n">
+        <v>2</v>
+      </c>
+      <c r="K233" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -4413,6 +8619,24 @@
         <v>7</v>
       </c>
       <c r="E234" t="n">
+        <v>12</v>
+      </c>
+      <c r="F234" t="n">
+        <v>9</v>
+      </c>
+      <c r="G234" t="n">
+        <v>1</v>
+      </c>
+      <c r="H234" t="n">
+        <v>0</v>
+      </c>
+      <c r="I234" t="n">
+        <v>1</v>
+      </c>
+      <c r="J234" t="n">
+        <v>7</v>
+      </c>
+      <c r="K234" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -4430,6 +8654,24 @@
         <v>9</v>
       </c>
       <c r="E235" t="n">
+        <v>15</v>
+      </c>
+      <c r="F235" t="n">
+        <v>3</v>
+      </c>
+      <c r="G235" t="n">
+        <v>0</v>
+      </c>
+      <c r="H235" t="n">
+        <v>0</v>
+      </c>
+      <c r="I235" t="n">
+        <v>0</v>
+      </c>
+      <c r="J235" t="n">
+        <v>8</v>
+      </c>
+      <c r="K235" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -4447,6 +8689,24 @@
         <v>7</v>
       </c>
       <c r="E236" t="n">
+        <v>27</v>
+      </c>
+      <c r="F236" t="n">
+        <v>9</v>
+      </c>
+      <c r="G236" t="n">
+        <v>0</v>
+      </c>
+      <c r="H236" t="n">
+        <v>2</v>
+      </c>
+      <c r="I236" t="n">
+        <v>0</v>
+      </c>
+      <c r="J236" t="n">
+        <v>19</v>
+      </c>
+      <c r="K236" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -4464,6 +8724,24 @@
         <v>9</v>
       </c>
       <c r="E237" t="n">
+        <v>22</v>
+      </c>
+      <c r="F237" t="n">
+        <v>3</v>
+      </c>
+      <c r="G237" t="n">
+        <v>1</v>
+      </c>
+      <c r="H237" t="n">
+        <v>1</v>
+      </c>
+      <c r="I237" t="n">
+        <v>0</v>
+      </c>
+      <c r="J237" t="n">
+        <v>12</v>
+      </c>
+      <c r="K237" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -4481,6 +8759,24 @@
         <v>7</v>
       </c>
       <c r="E238" t="n">
+        <v>1</v>
+      </c>
+      <c r="F238" t="n">
+        <v>1</v>
+      </c>
+      <c r="G238" t="n">
+        <v>0</v>
+      </c>
+      <c r="H238" t="n">
+        <v>2</v>
+      </c>
+      <c r="I238" t="n">
+        <v>0</v>
+      </c>
+      <c r="J238" t="n">
+        <v>0</v>
+      </c>
+      <c r="K238" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -4498,6 +8794,24 @@
         <v>7</v>
       </c>
       <c r="E239" t="n">
+        <v>4</v>
+      </c>
+      <c r="F239" t="n">
+        <v>0</v>
+      </c>
+      <c r="G239" t="n">
+        <v>0</v>
+      </c>
+      <c r="H239" t="n">
+        <v>3</v>
+      </c>
+      <c r="I239" t="n">
+        <v>0</v>
+      </c>
+      <c r="J239" t="n">
+        <v>0</v>
+      </c>
+      <c r="K239" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -4515,6 +8829,24 @@
         <v>9</v>
       </c>
       <c r="E240" t="n">
+        <v>7</v>
+      </c>
+      <c r="F240" t="n">
+        <v>1</v>
+      </c>
+      <c r="G240" t="n">
+        <v>0</v>
+      </c>
+      <c r="H240" t="n">
+        <v>0</v>
+      </c>
+      <c r="I240" t="n">
+        <v>0</v>
+      </c>
+      <c r="J240" t="n">
+        <v>3</v>
+      </c>
+      <c r="K240" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -4532,6 +8864,24 @@
         <v>7</v>
       </c>
       <c r="E241" t="n">
+        <v>2</v>
+      </c>
+      <c r="F241" t="n">
+        <v>1</v>
+      </c>
+      <c r="G241" t="n">
+        <v>0</v>
+      </c>
+      <c r="H241" t="n">
+        <v>0</v>
+      </c>
+      <c r="I241" t="n">
+        <v>0</v>
+      </c>
+      <c r="J241" t="n">
+        <v>3</v>
+      </c>
+      <c r="K241" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -4549,6 +8899,24 @@
         <v>7</v>
       </c>
       <c r="E242" t="n">
+        <v>2</v>
+      </c>
+      <c r="F242" t="n">
+        <v>2</v>
+      </c>
+      <c r="G242" t="n">
+        <v>1</v>
+      </c>
+      <c r="H242" t="n">
+        <v>0</v>
+      </c>
+      <c r="I242" t="n">
+        <v>0</v>
+      </c>
+      <c r="J242" t="n">
+        <v>0</v>
+      </c>
+      <c r="K242" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -4566,6 +8934,24 @@
         <v>9</v>
       </c>
       <c r="E243" t="n">
+        <v>5</v>
+      </c>
+      <c r="F243" t="n">
+        <v>1</v>
+      </c>
+      <c r="G243" t="n">
+        <v>0</v>
+      </c>
+      <c r="H243" t="n">
+        <v>0</v>
+      </c>
+      <c r="I243" t="n">
+        <v>0</v>
+      </c>
+      <c r="J243" t="n">
+        <v>0</v>
+      </c>
+      <c r="K243" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -4583,6 +8969,24 @@
         <v>7</v>
       </c>
       <c r="E244" t="n">
+        <v>7</v>
+      </c>
+      <c r="F244" t="n">
+        <v>7</v>
+      </c>
+      <c r="G244" t="n">
+        <v>0</v>
+      </c>
+      <c r="H244" t="n">
+        <v>0</v>
+      </c>
+      <c r="I244" t="n">
+        <v>0</v>
+      </c>
+      <c r="J244" t="n">
+        <v>7</v>
+      </c>
+      <c r="K244" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -4600,6 +9004,24 @@
         <v>9</v>
       </c>
       <c r="E245" t="n">
+        <v>6</v>
+      </c>
+      <c r="F245" t="n">
+        <v>0</v>
+      </c>
+      <c r="G245" t="n">
+        <v>0</v>
+      </c>
+      <c r="H245" t="n">
+        <v>0</v>
+      </c>
+      <c r="I245" t="n">
+        <v>0</v>
+      </c>
+      <c r="J245" t="n">
+        <v>0</v>
+      </c>
+      <c r="K245" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -4617,6 +9039,24 @@
         <v>7</v>
       </c>
       <c r="E246" t="n">
+        <v>6</v>
+      </c>
+      <c r="F246" t="n">
+        <v>4</v>
+      </c>
+      <c r="G246" t="n">
+        <v>0</v>
+      </c>
+      <c r="H246" t="n">
+        <v>0</v>
+      </c>
+      <c r="I246" t="n">
+        <v>0</v>
+      </c>
+      <c r="J246" t="n">
+        <v>4</v>
+      </c>
+      <c r="K246" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -4634,6 +9074,24 @@
         <v>9</v>
       </c>
       <c r="E247" t="n">
+        <v>13</v>
+      </c>
+      <c r="F247" t="n">
+        <v>0</v>
+      </c>
+      <c r="G247" t="n">
+        <v>0</v>
+      </c>
+      <c r="H247" t="n">
+        <v>0</v>
+      </c>
+      <c r="I247" t="n">
+        <v>1</v>
+      </c>
+      <c r="J247" t="n">
+        <v>4</v>
+      </c>
+      <c r="K247" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -4651,6 +9109,24 @@
         <v>7</v>
       </c>
       <c r="E248" t="n">
+        <v>10</v>
+      </c>
+      <c r="F248" t="n">
+        <v>1</v>
+      </c>
+      <c r="G248" t="n">
+        <v>0</v>
+      </c>
+      <c r="H248" t="n">
+        <v>0</v>
+      </c>
+      <c r="I248" t="n">
+        <v>0</v>
+      </c>
+      <c r="J248" t="n">
+        <v>5</v>
+      </c>
+      <c r="K248" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -4668,6 +9144,24 @@
         <v>9</v>
       </c>
       <c r="E249" t="n">
+        <v>2</v>
+      </c>
+      <c r="F249" t="n">
+        <v>1</v>
+      </c>
+      <c r="G249" t="n">
+        <v>0</v>
+      </c>
+      <c r="H249" t="n">
+        <v>0</v>
+      </c>
+      <c r="I249" t="n">
+        <v>0</v>
+      </c>
+      <c r="J249" t="n">
+        <v>1</v>
+      </c>
+      <c r="K249" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -4685,6 +9179,24 @@
         <v>7</v>
       </c>
       <c r="E250" t="n">
+        <v>2</v>
+      </c>
+      <c r="F250" t="n">
+        <v>0</v>
+      </c>
+      <c r="G250" t="n">
+        <v>0</v>
+      </c>
+      <c r="H250" t="n">
+        <v>0</v>
+      </c>
+      <c r="I250" t="n">
+        <v>0</v>
+      </c>
+      <c r="J250" t="n">
+        <v>1</v>
+      </c>
+      <c r="K250" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -4702,6 +9214,24 @@
         <v>7</v>
       </c>
       <c r="E251" t="n">
+        <v>4</v>
+      </c>
+      <c r="F251" t="n">
+        <v>1</v>
+      </c>
+      <c r="G251" t="n">
+        <v>0</v>
+      </c>
+      <c r="H251" t="n">
+        <v>0</v>
+      </c>
+      <c r="I251" t="n">
+        <v>0</v>
+      </c>
+      <c r="J251" t="n">
+        <v>0</v>
+      </c>
+      <c r="K251" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -4719,6 +9249,24 @@
         <v>9</v>
       </c>
       <c r="E252" t="n">
+        <v>6</v>
+      </c>
+      <c r="F252" t="n">
+        <v>1</v>
+      </c>
+      <c r="G252" t="n">
+        <v>0</v>
+      </c>
+      <c r="H252" t="n">
+        <v>0</v>
+      </c>
+      <c r="I252" t="n">
+        <v>0</v>
+      </c>
+      <c r="J252" t="n">
+        <v>2</v>
+      </c>
+      <c r="K252" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -4736,6 +9284,24 @@
         <v>7</v>
       </c>
       <c r="E253" t="n">
+        <v>24</v>
+      </c>
+      <c r="F253" t="n">
+        <v>5</v>
+      </c>
+      <c r="G253" t="n">
+        <v>0</v>
+      </c>
+      <c r="H253" t="n">
+        <v>1</v>
+      </c>
+      <c r="I253" t="n">
+        <v>1</v>
+      </c>
+      <c r="J253" t="n">
+        <v>9</v>
+      </c>
+      <c r="K253" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -4753,6 +9319,24 @@
         <v>9</v>
       </c>
       <c r="E254" t="n">
+        <v>8</v>
+      </c>
+      <c r="F254" t="n">
+        <v>2</v>
+      </c>
+      <c r="G254" t="n">
+        <v>0</v>
+      </c>
+      <c r="H254" t="n">
+        <v>0</v>
+      </c>
+      <c r="I254" t="n">
+        <v>0</v>
+      </c>
+      <c r="J254" t="n">
+        <v>5</v>
+      </c>
+      <c r="K254" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -4770,6 +9354,24 @@
         <v>7</v>
       </c>
       <c r="E255" t="n">
+        <v>6</v>
+      </c>
+      <c r="F255" t="n">
+        <v>2</v>
+      </c>
+      <c r="G255" t="n">
+        <v>0</v>
+      </c>
+      <c r="H255" t="n">
+        <v>0</v>
+      </c>
+      <c r="I255" t="n">
+        <v>0</v>
+      </c>
+      <c r="J255" t="n">
+        <v>2</v>
+      </c>
+      <c r="K255" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -4787,6 +9389,24 @@
         <v>9</v>
       </c>
       <c r="E256" t="n">
+        <v>2</v>
+      </c>
+      <c r="F256" t="n">
+        <v>1</v>
+      </c>
+      <c r="G256" t="n">
+        <v>0</v>
+      </c>
+      <c r="H256" t="n">
+        <v>0</v>
+      </c>
+      <c r="I256" t="n">
+        <v>0</v>
+      </c>
+      <c r="J256" t="n">
+        <v>1</v>
+      </c>
+      <c r="K256" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -4804,6 +9424,24 @@
         <v>7</v>
       </c>
       <c r="E257" t="n">
+        <v>8</v>
+      </c>
+      <c r="F257" t="n">
+        <v>0</v>
+      </c>
+      <c r="G257" t="n">
+        <v>1</v>
+      </c>
+      <c r="H257" t="n">
+        <v>0</v>
+      </c>
+      <c r="I257" t="n">
+        <v>0</v>
+      </c>
+      <c r="J257" t="n">
+        <v>7</v>
+      </c>
+      <c r="K257" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -4821,6 +9459,24 @@
         <v>7</v>
       </c>
       <c r="E258" t="n">
+        <v>6</v>
+      </c>
+      <c r="F258" t="n">
+        <v>1</v>
+      </c>
+      <c r="G258" t="n">
+        <v>0</v>
+      </c>
+      <c r="H258" t="n">
+        <v>4</v>
+      </c>
+      <c r="I258" t="n">
+        <v>0</v>
+      </c>
+      <c r="J258" t="n">
+        <v>3</v>
+      </c>
+      <c r="K258" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -4838,6 +9494,24 @@
         <v>9</v>
       </c>
       <c r="E259" t="n">
+        <v>9</v>
+      </c>
+      <c r="F259" t="n">
+        <v>3</v>
+      </c>
+      <c r="G259" t="n">
+        <v>0</v>
+      </c>
+      <c r="H259" t="n">
+        <v>5</v>
+      </c>
+      <c r="I259" t="n">
+        <v>0</v>
+      </c>
+      <c r="J259" t="n">
+        <v>7</v>
+      </c>
+      <c r="K259" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -4855,6 +9529,24 @@
         <v>7</v>
       </c>
       <c r="E260" t="n">
+        <v>6</v>
+      </c>
+      <c r="F260" t="n">
+        <v>2</v>
+      </c>
+      <c r="G260" t="n">
+        <v>1</v>
+      </c>
+      <c r="H260" t="n">
+        <v>0</v>
+      </c>
+      <c r="I260" t="n">
+        <v>0</v>
+      </c>
+      <c r="J260" t="n">
+        <v>6</v>
+      </c>
+      <c r="K260" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -4872,6 +9564,24 @@
         <v>7</v>
       </c>
       <c r="E261" t="n">
+        <v>3</v>
+      </c>
+      <c r="F261" t="n">
+        <v>1</v>
+      </c>
+      <c r="G261" t="n">
+        <v>3</v>
+      </c>
+      <c r="H261" t="n">
+        <v>0</v>
+      </c>
+      <c r="I261" t="n">
+        <v>0</v>
+      </c>
+      <c r="J261" t="n">
+        <v>0</v>
+      </c>
+      <c r="K261" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -4889,6 +9599,24 @@
         <v>7</v>
       </c>
       <c r="E262" t="n">
+        <v>8</v>
+      </c>
+      <c r="F262" t="n">
+        <v>2</v>
+      </c>
+      <c r="G262" t="n">
+        <v>0</v>
+      </c>
+      <c r="H262" t="n">
+        <v>1</v>
+      </c>
+      <c r="I262" t="n">
+        <v>0</v>
+      </c>
+      <c r="J262" t="n">
+        <v>7</v>
+      </c>
+      <c r="K262" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -4906,6 +9634,24 @@
         <v>9</v>
       </c>
       <c r="E263" t="n">
+        <v>5</v>
+      </c>
+      <c r="F263" t="n">
+        <v>2</v>
+      </c>
+      <c r="G263" t="n">
+        <v>0</v>
+      </c>
+      <c r="H263" t="n">
+        <v>0</v>
+      </c>
+      <c r="I263" t="n">
+        <v>0</v>
+      </c>
+      <c r="J263" t="n">
+        <v>3</v>
+      </c>
+      <c r="K263" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -4923,6 +9669,24 @@
         <v>7</v>
       </c>
       <c r="E264" t="n">
+        <v>3</v>
+      </c>
+      <c r="F264" t="n">
+        <v>2</v>
+      </c>
+      <c r="G264" t="n">
+        <v>1</v>
+      </c>
+      <c r="H264" t="n">
+        <v>0</v>
+      </c>
+      <c r="I264" t="n">
+        <v>0</v>
+      </c>
+      <c r="J264" t="n">
+        <v>3</v>
+      </c>
+      <c r="K264" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -4940,6 +9704,24 @@
         <v>7</v>
       </c>
       <c r="E265" t="n">
+        <v>3</v>
+      </c>
+      <c r="F265" t="n">
+        <v>0</v>
+      </c>
+      <c r="G265" t="n">
+        <v>0</v>
+      </c>
+      <c r="H265" t="n">
+        <v>0</v>
+      </c>
+      <c r="I265" t="n">
+        <v>0</v>
+      </c>
+      <c r="J265" t="n">
+        <v>3</v>
+      </c>
+      <c r="K265" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -4957,6 +9739,24 @@
         <v>9</v>
       </c>
       <c r="E266" t="n">
+        <v>5</v>
+      </c>
+      <c r="F266" t="n">
+        <v>1</v>
+      </c>
+      <c r="G266" t="n">
+        <v>0</v>
+      </c>
+      <c r="H266" t="n">
+        <v>0</v>
+      </c>
+      <c r="I266" t="n">
+        <v>0</v>
+      </c>
+      <c r="J266" t="n">
+        <v>4</v>
+      </c>
+      <c r="K266" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -4974,6 +9774,24 @@
         <v>7</v>
       </c>
       <c r="E267" t="n">
+        <v>0</v>
+      </c>
+      <c r="F267" t="n">
+        <v>1</v>
+      </c>
+      <c r="G267" t="n">
+        <v>0</v>
+      </c>
+      <c r="H267" t="n">
+        <v>0</v>
+      </c>
+      <c r="I267" t="n">
+        <v>0</v>
+      </c>
+      <c r="J267" t="n">
+        <v>1</v>
+      </c>
+      <c r="K267" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -4991,6 +9809,24 @@
         <v>9</v>
       </c>
       <c r="E268" t="n">
+        <v>0</v>
+      </c>
+      <c r="F268" t="n">
+        <v>0</v>
+      </c>
+      <c r="G268" t="n">
+        <v>0</v>
+      </c>
+      <c r="H268" t="n">
+        <v>0</v>
+      </c>
+      <c r="I268" t="n">
+        <v>0</v>
+      </c>
+      <c r="J268" t="n">
+        <v>0</v>
+      </c>
+      <c r="K268" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -5008,6 +9844,24 @@
         <v>7</v>
       </c>
       <c r="E269" t="n">
+        <v>4</v>
+      </c>
+      <c r="F269" t="n">
+        <v>1</v>
+      </c>
+      <c r="G269" t="n">
+        <v>0</v>
+      </c>
+      <c r="H269" t="n">
+        <v>1</v>
+      </c>
+      <c r="I269" t="n">
+        <v>0</v>
+      </c>
+      <c r="J269" t="n">
+        <v>2</v>
+      </c>
+      <c r="K269" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -5025,6 +9879,24 @@
         <v>7</v>
       </c>
       <c r="E270" t="n">
+        <v>0</v>
+      </c>
+      <c r="F270" t="n">
+        <v>0</v>
+      </c>
+      <c r="G270" t="n">
+        <v>0</v>
+      </c>
+      <c r="H270" t="n">
+        <v>0</v>
+      </c>
+      <c r="I270" t="n">
+        <v>0</v>
+      </c>
+      <c r="J270" t="n">
+        <v>0</v>
+      </c>
+      <c r="K270" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -5042,6 +9914,24 @@
         <v>9</v>
       </c>
       <c r="E271" t="n">
+        <v>0</v>
+      </c>
+      <c r="F271" t="n">
+        <v>0</v>
+      </c>
+      <c r="G271" t="n">
+        <v>0</v>
+      </c>
+      <c r="H271" t="n">
+        <v>0</v>
+      </c>
+      <c r="I271" t="n">
+        <v>0</v>
+      </c>
+      <c r="J271" t="n">
+        <v>0</v>
+      </c>
+      <c r="K271" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -5059,6 +9949,24 @@
         <v>7</v>
       </c>
       <c r="E272" t="n">
+        <v>3</v>
+      </c>
+      <c r="F272" t="n">
+        <v>0</v>
+      </c>
+      <c r="G272" t="n">
+        <v>0</v>
+      </c>
+      <c r="H272" t="n">
+        <v>0</v>
+      </c>
+      <c r="I272" t="n">
+        <v>0</v>
+      </c>
+      <c r="J272" t="n">
+        <v>2</v>
+      </c>
+      <c r="K272" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -5076,6 +9984,24 @@
         <v>7</v>
       </c>
       <c r="E273" t="n">
+        <v>5</v>
+      </c>
+      <c r="F273" t="n">
+        <v>1</v>
+      </c>
+      <c r="G273" t="n">
+        <v>0</v>
+      </c>
+      <c r="H273" t="n">
+        <v>0</v>
+      </c>
+      <c r="I273" t="n">
+        <v>0</v>
+      </c>
+      <c r="J273" t="n">
+        <v>2</v>
+      </c>
+      <c r="K273" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -5093,6 +10019,24 @@
         <v>7</v>
       </c>
       <c r="E274" t="n">
+        <v>6</v>
+      </c>
+      <c r="F274" t="n">
+        <v>2</v>
+      </c>
+      <c r="G274" t="n">
+        <v>0</v>
+      </c>
+      <c r="H274" t="n">
+        <v>1</v>
+      </c>
+      <c r="I274" t="n">
+        <v>0</v>
+      </c>
+      <c r="J274" t="n">
+        <v>4</v>
+      </c>
+      <c r="K274" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -5110,6 +10054,24 @@
         <v>9</v>
       </c>
       <c r="E275" t="n">
+        <v>5</v>
+      </c>
+      <c r="F275" t="n">
+        <v>1</v>
+      </c>
+      <c r="G275" t="n">
+        <v>0</v>
+      </c>
+      <c r="H275" t="n">
+        <v>1</v>
+      </c>
+      <c r="I275" t="n">
+        <v>0</v>
+      </c>
+      <c r="J275" t="n">
+        <v>0</v>
+      </c>
+      <c r="K275" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -5127,6 +10089,24 @@
         <v>7</v>
       </c>
       <c r="E276" t="n">
+        <v>1</v>
+      </c>
+      <c r="F276" t="n">
+        <v>2</v>
+      </c>
+      <c r="G276" t="n">
+        <v>0</v>
+      </c>
+      <c r="H276" t="n">
+        <v>0</v>
+      </c>
+      <c r="I276" t="n">
+        <v>0</v>
+      </c>
+      <c r="J276" t="n">
+        <v>0</v>
+      </c>
+      <c r="K276" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -5144,6 +10124,24 @@
         <v>9</v>
       </c>
       <c r="E277" t="n">
+        <v>5</v>
+      </c>
+      <c r="F277" t="n">
+        <v>0</v>
+      </c>
+      <c r="G277" t="n">
+        <v>0</v>
+      </c>
+      <c r="H277" t="n">
+        <v>0</v>
+      </c>
+      <c r="I277" t="n">
+        <v>0</v>
+      </c>
+      <c r="J277" t="n">
+        <v>0</v>
+      </c>
+      <c r="K277" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -5161,6 +10159,24 @@
         <v>7</v>
       </c>
       <c r="E278" t="n">
+        <v>2</v>
+      </c>
+      <c r="F278" t="n">
+        <v>3</v>
+      </c>
+      <c r="G278" t="n">
+        <v>1</v>
+      </c>
+      <c r="H278" t="n">
+        <v>0</v>
+      </c>
+      <c r="I278" t="n">
+        <v>0</v>
+      </c>
+      <c r="J278" t="n">
+        <v>3</v>
+      </c>
+      <c r="K278" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -5178,6 +10194,24 @@
         <v>7</v>
       </c>
       <c r="E279" t="n">
+        <v>1</v>
+      </c>
+      <c r="F279" t="n">
+        <v>0</v>
+      </c>
+      <c r="G279" t="n">
+        <v>0</v>
+      </c>
+      <c r="H279" t="n">
+        <v>0</v>
+      </c>
+      <c r="I279" t="n">
+        <v>0</v>
+      </c>
+      <c r="J279" t="n">
+        <v>1</v>
+      </c>
+      <c r="K279" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -5195,6 +10229,24 @@
         <v>7</v>
       </c>
       <c r="E280" t="n">
+        <v>2</v>
+      </c>
+      <c r="F280" t="n">
+        <v>0</v>
+      </c>
+      <c r="G280" t="n">
+        <v>0</v>
+      </c>
+      <c r="H280" t="n">
+        <v>0</v>
+      </c>
+      <c r="I280" t="n">
+        <v>0</v>
+      </c>
+      <c r="J280" t="n">
+        <v>0</v>
+      </c>
+      <c r="K280" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -5212,6 +10264,24 @@
         <v>9</v>
       </c>
       <c r="E281" t="n">
+        <v>2</v>
+      </c>
+      <c r="F281" t="n">
+        <v>1</v>
+      </c>
+      <c r="G281" t="n">
+        <v>0</v>
+      </c>
+      <c r="H281" t="n">
+        <v>0</v>
+      </c>
+      <c r="I281" t="n">
+        <v>0</v>
+      </c>
+      <c r="J281" t="n">
+        <v>0</v>
+      </c>
+      <c r="K281" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -5229,6 +10299,24 @@
         <v>7</v>
       </c>
       <c r="E282" t="n">
+        <v>9</v>
+      </c>
+      <c r="F282" t="n">
+        <v>3</v>
+      </c>
+      <c r="G282" t="n">
+        <v>0</v>
+      </c>
+      <c r="H282" t="n">
+        <v>0</v>
+      </c>
+      <c r="I282" t="n">
+        <v>1</v>
+      </c>
+      <c r="J282" t="n">
+        <v>7</v>
+      </c>
+      <c r="K282" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -5246,6 +10334,24 @@
         <v>7</v>
       </c>
       <c r="E283" t="n">
+        <v>7</v>
+      </c>
+      <c r="F283" t="n">
+        <v>1</v>
+      </c>
+      <c r="G283" t="n">
+        <v>0</v>
+      </c>
+      <c r="H283" t="n">
+        <v>0</v>
+      </c>
+      <c r="I283" t="n">
+        <v>0</v>
+      </c>
+      <c r="J283" t="n">
+        <v>6</v>
+      </c>
+      <c r="K283" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -5263,6 +10369,24 @@
         <v>9</v>
       </c>
       <c r="E284" t="n">
+        <v>15</v>
+      </c>
+      <c r="F284" t="n">
+        <v>4</v>
+      </c>
+      <c r="G284" t="n">
+        <v>0</v>
+      </c>
+      <c r="H284" t="n">
+        <v>0</v>
+      </c>
+      <c r="I284" t="n">
+        <v>0</v>
+      </c>
+      <c r="J284" t="n">
+        <v>4</v>
+      </c>
+      <c r="K284" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -5280,6 +10404,24 @@
         <v>7</v>
       </c>
       <c r="E285" t="n">
+        <v>9</v>
+      </c>
+      <c r="F285" t="n">
+        <v>2</v>
+      </c>
+      <c r="G285" t="n">
+        <v>0</v>
+      </c>
+      <c r="H285" t="n">
+        <v>0</v>
+      </c>
+      <c r="I285" t="n">
+        <v>0</v>
+      </c>
+      <c r="J285" t="n">
+        <v>0</v>
+      </c>
+      <c r="K285" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -5297,6 +10439,24 @@
         <v>9</v>
       </c>
       <c r="E286" t="n">
+        <v>8</v>
+      </c>
+      <c r="F286" t="n">
+        <v>2</v>
+      </c>
+      <c r="G286" t="n">
+        <v>0</v>
+      </c>
+      <c r="H286" t="n">
+        <v>0</v>
+      </c>
+      <c r="I286" t="n">
+        <v>0</v>
+      </c>
+      <c r="J286" t="n">
+        <v>1</v>
+      </c>
+      <c r="K286" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -5314,6 +10474,24 @@
         <v>7</v>
       </c>
       <c r="E287" t="n">
+        <v>3</v>
+      </c>
+      <c r="F287" t="n">
+        <v>0</v>
+      </c>
+      <c r="G287" t="n">
+        <v>0</v>
+      </c>
+      <c r="H287" t="n">
+        <v>0</v>
+      </c>
+      <c r="I287" t="n">
+        <v>0</v>
+      </c>
+      <c r="J287" t="n">
+        <v>2</v>
+      </c>
+      <c r="K287" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -5331,6 +10509,24 @@
         <v>9</v>
       </c>
       <c r="E288" t="n">
+        <v>7</v>
+      </c>
+      <c r="F288" t="n">
+        <v>2</v>
+      </c>
+      <c r="G288" t="n">
+        <v>0</v>
+      </c>
+      <c r="H288" t="n">
+        <v>0</v>
+      </c>
+      <c r="I288" t="n">
+        <v>0</v>
+      </c>
+      <c r="J288" t="n">
+        <v>3</v>
+      </c>
+      <c r="K288" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -5348,6 +10544,24 @@
         <v>7</v>
       </c>
       <c r="E289" t="n">
+        <v>0</v>
+      </c>
+      <c r="F289" t="n">
+        <v>0</v>
+      </c>
+      <c r="G289" t="n">
+        <v>0</v>
+      </c>
+      <c r="H289" t="n">
+        <v>0</v>
+      </c>
+      <c r="I289" t="n">
+        <v>0</v>
+      </c>
+      <c r="J289" t="n">
+        <v>0</v>
+      </c>
+      <c r="K289" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -5365,6 +10579,24 @@
         <v>7</v>
       </c>
       <c r="E290" t="n">
+        <v>3</v>
+      </c>
+      <c r="F290" t="n">
+        <v>0</v>
+      </c>
+      <c r="G290" t="n">
+        <v>0</v>
+      </c>
+      <c r="H290" t="n">
+        <v>0</v>
+      </c>
+      <c r="I290" t="n">
+        <v>1</v>
+      </c>
+      <c r="J290" t="n">
+        <v>2</v>
+      </c>
+      <c r="K290" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -5382,6 +10614,24 @@
         <v>7</v>
       </c>
       <c r="E291" t="n">
+        <v>0</v>
+      </c>
+      <c r="F291" t="n">
+        <v>0</v>
+      </c>
+      <c r="G291" t="n">
+        <v>0</v>
+      </c>
+      <c r="H291" t="n">
+        <v>0</v>
+      </c>
+      <c r="I291" t="n">
+        <v>0</v>
+      </c>
+      <c r="J291" t="n">
+        <v>0</v>
+      </c>
+      <c r="K291" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -5399,6 +10649,24 @@
         <v>7</v>
       </c>
       <c r="E292" t="n">
+        <v>3</v>
+      </c>
+      <c r="F292" t="n">
+        <v>2</v>
+      </c>
+      <c r="G292" t="n">
+        <v>0</v>
+      </c>
+      <c r="H292" t="n">
+        <v>0</v>
+      </c>
+      <c r="I292" t="n">
+        <v>0</v>
+      </c>
+      <c r="J292" t="n">
+        <v>2</v>
+      </c>
+      <c r="K292" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -5416,6 +10684,24 @@
         <v>9</v>
       </c>
       <c r="E293" t="n">
+        <v>4</v>
+      </c>
+      <c r="F293" t="n">
+        <v>0</v>
+      </c>
+      <c r="G293" t="n">
+        <v>0</v>
+      </c>
+      <c r="H293" t="n">
+        <v>0</v>
+      </c>
+      <c r="I293" t="n">
+        <v>0</v>
+      </c>
+      <c r="J293" t="n">
+        <v>2</v>
+      </c>
+      <c r="K293" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -5433,6 +10719,24 @@
         <v>7</v>
       </c>
       <c r="E294" t="n">
+        <v>0</v>
+      </c>
+      <c r="F294" t="n">
+        <v>0</v>
+      </c>
+      <c r="G294" t="n">
+        <v>0</v>
+      </c>
+      <c r="H294" t="n">
+        <v>0</v>
+      </c>
+      <c r="I294" t="n">
+        <v>0</v>
+      </c>
+      <c r="J294" t="n">
+        <v>0</v>
+      </c>
+      <c r="K294" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -5450,6 +10754,24 @@
         <v>9</v>
       </c>
       <c r="E295" t="n">
+        <v>0</v>
+      </c>
+      <c r="F295" t="n">
+        <v>0</v>
+      </c>
+      <c r="G295" t="n">
+        <v>0</v>
+      </c>
+      <c r="H295" t="n">
+        <v>0</v>
+      </c>
+      <c r="I295" t="n">
+        <v>0</v>
+      </c>
+      <c r="J295" t="n">
+        <v>0</v>
+      </c>
+      <c r="K295" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -5467,6 +10789,24 @@
         <v>7</v>
       </c>
       <c r="E296" t="n">
+        <v>6</v>
+      </c>
+      <c r="F296" t="n">
+        <v>1</v>
+      </c>
+      <c r="G296" t="n">
+        <v>1</v>
+      </c>
+      <c r="H296" t="n">
+        <v>0</v>
+      </c>
+      <c r="I296" t="n">
+        <v>0</v>
+      </c>
+      <c r="J296" t="n">
+        <v>2</v>
+      </c>
+      <c r="K296" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -5484,6 +10824,24 @@
         <v>9</v>
       </c>
       <c r="E297" t="n">
+        <v>3</v>
+      </c>
+      <c r="F297" t="n">
+        <v>2</v>
+      </c>
+      <c r="G297" t="n">
+        <v>0</v>
+      </c>
+      <c r="H297" t="n">
+        <v>0</v>
+      </c>
+      <c r="I297" t="n">
+        <v>0</v>
+      </c>
+      <c r="J297" t="n">
+        <v>1</v>
+      </c>
+      <c r="K297" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -5501,6 +10859,24 @@
         <v>7</v>
       </c>
       <c r="E298" t="n">
+        <v>0</v>
+      </c>
+      <c r="F298" t="n">
+        <v>0</v>
+      </c>
+      <c r="G298" t="n">
+        <v>0</v>
+      </c>
+      <c r="H298" t="n">
+        <v>0</v>
+      </c>
+      <c r="I298" t="n">
+        <v>0</v>
+      </c>
+      <c r="J298" t="n">
+        <v>0</v>
+      </c>
+      <c r="K298" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -5518,6 +10894,24 @@
         <v>9</v>
       </c>
       <c r="E299" t="n">
+        <v>0</v>
+      </c>
+      <c r="F299" t="n">
+        <v>0</v>
+      </c>
+      <c r="G299" t="n">
+        <v>0</v>
+      </c>
+      <c r="H299" t="n">
+        <v>0</v>
+      </c>
+      <c r="I299" t="n">
+        <v>0</v>
+      </c>
+      <c r="J299" t="n">
+        <v>0</v>
+      </c>
+      <c r="K299" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -5535,6 +10929,24 @@
         <v>7</v>
       </c>
       <c r="E300" t="n">
+        <v>3</v>
+      </c>
+      <c r="F300" t="n">
+        <v>1</v>
+      </c>
+      <c r="G300" t="n">
+        <v>0</v>
+      </c>
+      <c r="H300" t="n">
+        <v>0</v>
+      </c>
+      <c r="I300" t="n">
+        <v>0</v>
+      </c>
+      <c r="J300" t="n">
+        <v>2</v>
+      </c>
+      <c r="K300" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -5552,6 +10964,24 @@
         <v>9</v>
       </c>
       <c r="E301" t="n">
+        <v>0</v>
+      </c>
+      <c r="F301" t="n">
+        <v>1</v>
+      </c>
+      <c r="G301" t="n">
+        <v>0</v>
+      </c>
+      <c r="H301" t="n">
+        <v>0</v>
+      </c>
+      <c r="I301" t="n">
+        <v>0</v>
+      </c>
+      <c r="J301" t="n">
+        <v>1</v>
+      </c>
+      <c r="K301" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -5569,6 +10999,24 @@
         <v>7</v>
       </c>
       <c r="E302" t="n">
+        <v>11</v>
+      </c>
+      <c r="F302" t="n">
+        <v>0</v>
+      </c>
+      <c r="G302" t="n">
+        <v>0</v>
+      </c>
+      <c r="H302" t="n">
+        <v>0</v>
+      </c>
+      <c r="I302" t="n">
+        <v>0</v>
+      </c>
+      <c r="J302" t="n">
+        <v>2</v>
+      </c>
+      <c r="K302" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -5586,6 +11034,24 @@
         <v>9</v>
       </c>
       <c r="E303" t="n">
+        <v>6</v>
+      </c>
+      <c r="F303" t="n">
+        <v>1</v>
+      </c>
+      <c r="G303" t="n">
+        <v>0</v>
+      </c>
+      <c r="H303" t="n">
+        <v>0</v>
+      </c>
+      <c r="I303" t="n">
+        <v>0</v>
+      </c>
+      <c r="J303" t="n">
+        <v>5</v>
+      </c>
+      <c r="K303" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -5603,6 +11069,24 @@
         <v>7</v>
       </c>
       <c r="E304" t="n">
+        <v>6</v>
+      </c>
+      <c r="F304" t="n">
+        <v>3</v>
+      </c>
+      <c r="G304" t="n">
+        <v>0</v>
+      </c>
+      <c r="H304" t="n">
+        <v>0</v>
+      </c>
+      <c r="I304" t="n">
+        <v>2</v>
+      </c>
+      <c r="J304" t="n">
+        <v>3</v>
+      </c>
+      <c r="K304" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -5620,6 +11104,24 @@
         <v>9</v>
       </c>
       <c r="E305" t="n">
+        <v>2</v>
+      </c>
+      <c r="F305" t="n">
+        <v>0</v>
+      </c>
+      <c r="G305" t="n">
+        <v>0</v>
+      </c>
+      <c r="H305" t="n">
+        <v>0</v>
+      </c>
+      <c r="I305" t="n">
+        <v>0</v>
+      </c>
+      <c r="J305" t="n">
+        <v>2</v>
+      </c>
+      <c r="K305" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -5637,6 +11139,24 @@
         <v>7</v>
       </c>
       <c r="E306" t="n">
+        <v>9</v>
+      </c>
+      <c r="F306" t="n">
+        <v>2</v>
+      </c>
+      <c r="G306" t="n">
+        <v>0</v>
+      </c>
+      <c r="H306" t="n">
+        <v>0</v>
+      </c>
+      <c r="I306" t="n">
+        <v>0</v>
+      </c>
+      <c r="J306" t="n">
+        <v>4</v>
+      </c>
+      <c r="K306" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -5654,6 +11174,24 @@
         <v>9</v>
       </c>
       <c r="E307" t="n">
+        <v>9</v>
+      </c>
+      <c r="F307" t="n">
+        <v>3</v>
+      </c>
+      <c r="G307" t="n">
+        <v>0</v>
+      </c>
+      <c r="H307" t="n">
+        <v>0</v>
+      </c>
+      <c r="I307" t="n">
+        <v>0</v>
+      </c>
+      <c r="J307" t="n">
+        <v>1</v>
+      </c>
+      <c r="K307" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -5671,6 +11209,24 @@
         <v>7</v>
       </c>
       <c r="E308" t="n">
+        <v>2</v>
+      </c>
+      <c r="F308" t="n">
+        <v>2</v>
+      </c>
+      <c r="G308" t="n">
+        <v>0</v>
+      </c>
+      <c r="H308" t="n">
+        <v>0</v>
+      </c>
+      <c r="I308" t="n">
+        <v>0</v>
+      </c>
+      <c r="J308" t="n">
+        <v>1</v>
+      </c>
+      <c r="K308" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -5688,6 +11244,24 @@
         <v>7</v>
       </c>
       <c r="E309" t="n">
+        <v>6</v>
+      </c>
+      <c r="F309" t="n">
+        <v>1</v>
+      </c>
+      <c r="G309" t="n">
+        <v>1</v>
+      </c>
+      <c r="H309" t="n">
+        <v>0</v>
+      </c>
+      <c r="I309" t="n">
+        <v>0</v>
+      </c>
+      <c r="J309" t="n">
+        <v>1</v>
+      </c>
+      <c r="K309" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -5705,6 +11279,24 @@
         <v>9</v>
       </c>
       <c r="E310" t="n">
+        <v>4</v>
+      </c>
+      <c r="F310" t="n">
+        <v>2</v>
+      </c>
+      <c r="G310" t="n">
+        <v>0</v>
+      </c>
+      <c r="H310" t="n">
+        <v>0</v>
+      </c>
+      <c r="I310" t="n">
+        <v>0</v>
+      </c>
+      <c r="J310" t="n">
+        <v>3</v>
+      </c>
+      <c r="K310" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -5722,6 +11314,24 @@
         <v>7</v>
       </c>
       <c r="E311" t="n">
+        <v>5</v>
+      </c>
+      <c r="F311" t="n">
+        <v>0</v>
+      </c>
+      <c r="G311" t="n">
+        <v>1</v>
+      </c>
+      <c r="H311" t="n">
+        <v>0</v>
+      </c>
+      <c r="I311" t="n">
+        <v>0</v>
+      </c>
+      <c r="J311" t="n">
+        <v>2</v>
+      </c>
+      <c r="K311" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -5739,6 +11349,24 @@
         <v>9</v>
       </c>
       <c r="E312" t="n">
+        <v>10</v>
+      </c>
+      <c r="F312" t="n">
+        <v>3</v>
+      </c>
+      <c r="G312" t="n">
+        <v>1</v>
+      </c>
+      <c r="H312" t="n">
+        <v>0</v>
+      </c>
+      <c r="I312" t="n">
+        <v>0</v>
+      </c>
+      <c r="J312" t="n">
+        <v>7</v>
+      </c>
+      <c r="K312" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -5756,6 +11384,24 @@
         <v>7</v>
       </c>
       <c r="E313" t="n">
+        <v>3</v>
+      </c>
+      <c r="F313" t="n">
+        <v>0</v>
+      </c>
+      <c r="G313" t="n">
+        <v>0</v>
+      </c>
+      <c r="H313" t="n">
+        <v>0</v>
+      </c>
+      <c r="I313" t="n">
+        <v>0</v>
+      </c>
+      <c r="J313" t="n">
+        <v>2</v>
+      </c>
+      <c r="K313" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -5773,6 +11419,24 @@
         <v>9</v>
       </c>
       <c r="E314" t="n">
+        <v>10</v>
+      </c>
+      <c r="F314" t="n">
+        <v>1</v>
+      </c>
+      <c r="G314" t="n">
+        <v>0</v>
+      </c>
+      <c r="H314" t="n">
+        <v>0</v>
+      </c>
+      <c r="I314" t="n">
+        <v>0</v>
+      </c>
+      <c r="J314" t="n">
+        <v>6</v>
+      </c>
+      <c r="K314" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -5790,6 +11454,24 @@
         <v>7</v>
       </c>
       <c r="E315" t="n">
+        <v>13</v>
+      </c>
+      <c r="F315" t="n">
+        <v>1</v>
+      </c>
+      <c r="G315" t="n">
+        <v>0</v>
+      </c>
+      <c r="H315" t="n">
+        <v>1</v>
+      </c>
+      <c r="I315" t="n">
+        <v>0</v>
+      </c>
+      <c r="J315" t="n">
+        <v>3</v>
+      </c>
+      <c r="K315" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -5807,6 +11489,24 @@
         <v>9</v>
       </c>
       <c r="E316" t="n">
+        <v>4</v>
+      </c>
+      <c r="F316" t="n">
+        <v>2</v>
+      </c>
+      <c r="G316" t="n">
+        <v>0</v>
+      </c>
+      <c r="H316" t="n">
+        <v>1</v>
+      </c>
+      <c r="I316" t="n">
+        <v>0</v>
+      </c>
+      <c r="J316" t="n">
+        <v>0</v>
+      </c>
+      <c r="K316" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -5824,6 +11524,24 @@
         <v>7</v>
       </c>
       <c r="E317" t="n">
+        <v>14</v>
+      </c>
+      <c r="F317" t="n">
+        <v>12</v>
+      </c>
+      <c r="G317" t="n">
+        <v>0</v>
+      </c>
+      <c r="H317" t="n">
+        <v>0</v>
+      </c>
+      <c r="I317" t="n">
+        <v>0</v>
+      </c>
+      <c r="J317" t="n">
+        <v>24</v>
+      </c>
+      <c r="K317" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -5841,6 +11559,24 @@
         <v>7</v>
       </c>
       <c r="E318" t="n">
+        <v>0</v>
+      </c>
+      <c r="F318" t="n">
+        <v>1</v>
+      </c>
+      <c r="G318" t="n">
+        <v>0</v>
+      </c>
+      <c r="H318" t="n">
+        <v>0</v>
+      </c>
+      <c r="I318" t="n">
+        <v>0</v>
+      </c>
+      <c r="J318" t="n">
+        <v>1</v>
+      </c>
+      <c r="K318" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -5858,6 +11594,24 @@
         <v>7</v>
       </c>
       <c r="E319" t="n">
+        <v>2</v>
+      </c>
+      <c r="F319" t="n">
+        <v>0</v>
+      </c>
+      <c r="G319" t="n">
+        <v>0</v>
+      </c>
+      <c r="H319" t="n">
+        <v>0</v>
+      </c>
+      <c r="I319" t="n">
+        <v>0</v>
+      </c>
+      <c r="J319" t="n">
+        <v>2</v>
+      </c>
+      <c r="K319" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -5875,6 +11629,24 @@
         <v>9</v>
       </c>
       <c r="E320" t="n">
+        <v>1</v>
+      </c>
+      <c r="F320" t="n">
+        <v>0</v>
+      </c>
+      <c r="G320" t="n">
+        <v>0</v>
+      </c>
+      <c r="H320" t="n">
+        <v>1</v>
+      </c>
+      <c r="I320" t="n">
+        <v>0</v>
+      </c>
+      <c r="J320" t="n">
+        <v>0</v>
+      </c>
+      <c r="K320" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -5892,6 +11664,24 @@
         <v>7</v>
       </c>
       <c r="E321" t="n">
+        <v>12</v>
+      </c>
+      <c r="F321" t="n">
+        <v>3</v>
+      </c>
+      <c r="G321" t="n">
+        <v>0</v>
+      </c>
+      <c r="H321" t="n">
+        <v>0</v>
+      </c>
+      <c r="I321" t="n">
+        <v>0</v>
+      </c>
+      <c r="J321" t="n">
+        <v>1</v>
+      </c>
+      <c r="K321" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -5909,6 +11699,24 @@
         <v>9</v>
       </c>
       <c r="E322" t="n">
+        <v>13</v>
+      </c>
+      <c r="F322" t="n">
+        <v>4</v>
+      </c>
+      <c r="G322" t="n">
+        <v>0</v>
+      </c>
+      <c r="H322" t="n">
+        <v>0</v>
+      </c>
+      <c r="I322" t="n">
+        <v>1</v>
+      </c>
+      <c r="J322" t="n">
+        <v>2</v>
+      </c>
+      <c r="K322" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -5926,6 +11734,24 @@
         <v>7</v>
       </c>
       <c r="E323" t="n">
+        <v>0</v>
+      </c>
+      <c r="F323" t="n">
+        <v>0</v>
+      </c>
+      <c r="G323" t="n">
+        <v>0</v>
+      </c>
+      <c r="H323" t="n">
+        <v>0</v>
+      </c>
+      <c r="I323" t="n">
+        <v>0</v>
+      </c>
+      <c r="J323" t="n">
+        <v>0</v>
+      </c>
+      <c r="K323" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -5943,6 +11769,24 @@
         <v>9</v>
       </c>
       <c r="E324" t="n">
+        <v>0</v>
+      </c>
+      <c r="F324" t="n">
+        <v>0</v>
+      </c>
+      <c r="G324" t="n">
+        <v>0</v>
+      </c>
+      <c r="H324" t="n">
+        <v>0</v>
+      </c>
+      <c r="I324" t="n">
+        <v>0</v>
+      </c>
+      <c r="J324" t="n">
+        <v>0</v>
+      </c>
+      <c r="K324" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -5960,6 +11804,24 @@
         <v>7</v>
       </c>
       <c r="E325" t="n">
+        <v>8</v>
+      </c>
+      <c r="F325" t="n">
+        <v>7</v>
+      </c>
+      <c r="G325" t="n">
+        <v>0</v>
+      </c>
+      <c r="H325" t="n">
+        <v>1</v>
+      </c>
+      <c r="I325" t="n">
+        <v>1</v>
+      </c>
+      <c r="J325" t="n">
+        <v>7</v>
+      </c>
+      <c r="K325" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -5977,6 +11839,24 @@
         <v>9</v>
       </c>
       <c r="E326" t="n">
+        <v>2</v>
+      </c>
+      <c r="F326" t="n">
+        <v>3</v>
+      </c>
+      <c r="G326" t="n">
+        <v>0</v>
+      </c>
+      <c r="H326" t="n">
+        <v>0</v>
+      </c>
+      <c r="I326" t="n">
+        <v>0</v>
+      </c>
+      <c r="J326" t="n">
+        <v>2</v>
+      </c>
+      <c r="K326" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -5994,6 +11874,24 @@
         <v>7</v>
       </c>
       <c r="E327" t="n">
+        <v>3</v>
+      </c>
+      <c r="F327" t="n">
+        <v>0</v>
+      </c>
+      <c r="G327" t="n">
+        <v>0</v>
+      </c>
+      <c r="H327" t="n">
+        <v>0</v>
+      </c>
+      <c r="I327" t="n">
+        <v>0</v>
+      </c>
+      <c r="J327" t="n">
+        <v>2</v>
+      </c>
+      <c r="K327" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -6011,6 +11909,24 @@
         <v>9</v>
       </c>
       <c r="E328" t="n">
+        <v>1</v>
+      </c>
+      <c r="F328" t="n">
+        <v>1</v>
+      </c>
+      <c r="G328" t="n">
+        <v>0</v>
+      </c>
+      <c r="H328" t="n">
+        <v>0</v>
+      </c>
+      <c r="I328" t="n">
+        <v>0</v>
+      </c>
+      <c r="J328" t="n">
+        <v>0</v>
+      </c>
+      <c r="K328" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -6028,6 +11944,24 @@
         <v>7</v>
       </c>
       <c r="E329" t="n">
+        <v>3</v>
+      </c>
+      <c r="F329" t="n">
+        <v>0</v>
+      </c>
+      <c r="G329" t="n">
+        <v>1</v>
+      </c>
+      <c r="H329" t="n">
+        <v>0</v>
+      </c>
+      <c r="I329" t="n">
+        <v>0</v>
+      </c>
+      <c r="J329" t="n">
+        <v>1</v>
+      </c>
+      <c r="K329" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -6045,6 +11979,24 @@
         <v>7</v>
       </c>
       <c r="E330" t="n">
+        <v>3</v>
+      </c>
+      <c r="F330" t="n">
+        <v>1</v>
+      </c>
+      <c r="G330" t="n">
+        <v>0</v>
+      </c>
+      <c r="H330" t="n">
+        <v>0</v>
+      </c>
+      <c r="I330" t="n">
+        <v>0</v>
+      </c>
+      <c r="J330" t="n">
+        <v>3</v>
+      </c>
+      <c r="K330" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -6062,6 +12014,24 @@
         <v>7</v>
       </c>
       <c r="E331" t="n">
+        <v>4</v>
+      </c>
+      <c r="F331" t="n">
+        <v>2</v>
+      </c>
+      <c r="G331" t="n">
+        <v>0</v>
+      </c>
+      <c r="H331" t="n">
+        <v>0</v>
+      </c>
+      <c r="I331" t="n">
+        <v>0</v>
+      </c>
+      <c r="J331" t="n">
+        <v>4</v>
+      </c>
+      <c r="K331" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -6079,6 +12049,24 @@
         <v>9</v>
       </c>
       <c r="E332" t="n">
+        <v>7</v>
+      </c>
+      <c r="F332" t="n">
+        <v>3</v>
+      </c>
+      <c r="G332" t="n">
+        <v>0</v>
+      </c>
+      <c r="H332" t="n">
+        <v>0</v>
+      </c>
+      <c r="I332" t="n">
+        <v>0</v>
+      </c>
+      <c r="J332" t="n">
+        <v>5</v>
+      </c>
+      <c r="K332" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -6096,6 +12084,24 @@
         <v>7</v>
       </c>
       <c r="E333" t="n">
+        <v>4</v>
+      </c>
+      <c r="F333" t="n">
+        <v>1</v>
+      </c>
+      <c r="G333" t="n">
+        <v>0</v>
+      </c>
+      <c r="H333" t="n">
+        <v>0</v>
+      </c>
+      <c r="I333" t="n">
+        <v>0</v>
+      </c>
+      <c r="J333" t="n">
+        <v>2</v>
+      </c>
+      <c r="K333" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -6113,6 +12119,24 @@
         <v>9</v>
       </c>
       <c r="E334" t="n">
+        <v>3</v>
+      </c>
+      <c r="F334" t="n">
+        <v>1</v>
+      </c>
+      <c r="G334" t="n">
+        <v>0</v>
+      </c>
+      <c r="H334" t="n">
+        <v>0</v>
+      </c>
+      <c r="I334" t="n">
+        <v>0</v>
+      </c>
+      <c r="J334" t="n">
+        <v>0</v>
+      </c>
+      <c r="K334" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -6130,6 +12154,24 @@
         <v>7</v>
       </c>
       <c r="E335" t="n">
+        <v>0</v>
+      </c>
+      <c r="F335" t="n">
+        <v>0</v>
+      </c>
+      <c r="G335" t="n">
+        <v>0</v>
+      </c>
+      <c r="H335" t="n">
+        <v>0</v>
+      </c>
+      <c r="I335" t="n">
+        <v>0</v>
+      </c>
+      <c r="J335" t="n">
+        <v>0</v>
+      </c>
+      <c r="K335" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -6147,6 +12189,24 @@
         <v>9</v>
       </c>
       <c r="E336" t="n">
+        <v>0</v>
+      </c>
+      <c r="F336" t="n">
+        <v>0</v>
+      </c>
+      <c r="G336" t="n">
+        <v>0</v>
+      </c>
+      <c r="H336" t="n">
+        <v>0</v>
+      </c>
+      <c r="I336" t="n">
+        <v>0</v>
+      </c>
+      <c r="J336" t="n">
+        <v>0</v>
+      </c>
+      <c r="K336" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -6164,6 +12224,24 @@
         <v>7</v>
       </c>
       <c r="E337" t="n">
+        <v>3</v>
+      </c>
+      <c r="F337" t="n">
+        <v>2</v>
+      </c>
+      <c r="G337" t="n">
+        <v>0</v>
+      </c>
+      <c r="H337" t="n">
+        <v>0</v>
+      </c>
+      <c r="I337" t="n">
+        <v>0</v>
+      </c>
+      <c r="J337" t="n">
+        <v>2</v>
+      </c>
+      <c r="K337" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -6181,6 +12259,24 @@
         <v>9</v>
       </c>
       <c r="E338" t="n">
+        <v>3</v>
+      </c>
+      <c r="F338" t="n">
+        <v>0</v>
+      </c>
+      <c r="G338" t="n">
+        <v>0</v>
+      </c>
+      <c r="H338" t="n">
+        <v>0</v>
+      </c>
+      <c r="I338" t="n">
+        <v>0</v>
+      </c>
+      <c r="J338" t="n">
+        <v>3</v>
+      </c>
+      <c r="K338" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -6198,6 +12294,24 @@
         <v>7</v>
       </c>
       <c r="E339" t="n">
+        <v>0</v>
+      </c>
+      <c r="F339" t="n">
+        <v>2</v>
+      </c>
+      <c r="G339" t="n">
+        <v>0</v>
+      </c>
+      <c r="H339" t="n">
+        <v>0</v>
+      </c>
+      <c r="I339" t="n">
+        <v>0</v>
+      </c>
+      <c r="J339" t="n">
+        <v>2</v>
+      </c>
+      <c r="K339" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -6215,6 +12329,24 @@
         <v>7</v>
       </c>
       <c r="E340" t="n">
+        <v>6</v>
+      </c>
+      <c r="F340" t="n">
+        <v>2</v>
+      </c>
+      <c r="G340" t="n">
+        <v>1</v>
+      </c>
+      <c r="H340" t="n">
+        <v>1</v>
+      </c>
+      <c r="I340" t="n">
+        <v>0</v>
+      </c>
+      <c r="J340" t="n">
+        <v>6</v>
+      </c>
+      <c r="K340" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -6232,6 +12364,24 @@
         <v>7</v>
       </c>
       <c r="E341" t="n">
+        <v>12</v>
+      </c>
+      <c r="F341" t="n">
+        <v>3</v>
+      </c>
+      <c r="G341" t="n">
+        <v>0</v>
+      </c>
+      <c r="H341" t="n">
+        <v>0</v>
+      </c>
+      <c r="I341" t="n">
+        <v>2</v>
+      </c>
+      <c r="J341" t="n">
+        <v>2</v>
+      </c>
+      <c r="K341" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -6249,6 +12399,24 @@
         <v>9</v>
       </c>
       <c r="E342" t="n">
+        <v>13</v>
+      </c>
+      <c r="F342" t="n">
+        <v>2</v>
+      </c>
+      <c r="G342" t="n">
+        <v>0</v>
+      </c>
+      <c r="H342" t="n">
+        <v>2</v>
+      </c>
+      <c r="I342" t="n">
+        <v>1</v>
+      </c>
+      <c r="J342" t="n">
+        <v>1</v>
+      </c>
+      <c r="K342" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -6266,6 +12434,24 @@
         <v>7</v>
       </c>
       <c r="E343" t="n">
+        <v>4</v>
+      </c>
+      <c r="F343" t="n">
+        <v>0</v>
+      </c>
+      <c r="G343" t="n">
+        <v>0</v>
+      </c>
+      <c r="H343" t="n">
+        <v>0</v>
+      </c>
+      <c r="I343" t="n">
+        <v>0</v>
+      </c>
+      <c r="J343" t="n">
+        <v>3</v>
+      </c>
+      <c r="K343" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -6283,6 +12469,24 @@
         <v>9</v>
       </c>
       <c r="E344" t="n">
+        <v>4</v>
+      </c>
+      <c r="F344" t="n">
+        <v>1</v>
+      </c>
+      <c r="G344" t="n">
+        <v>0</v>
+      </c>
+      <c r="H344" t="n">
+        <v>0</v>
+      </c>
+      <c r="I344" t="n">
+        <v>0</v>
+      </c>
+      <c r="J344" t="n">
+        <v>2</v>
+      </c>
+      <c r="K344" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -6300,6 +12504,24 @@
         <v>7</v>
       </c>
       <c r="E345" t="n">
+        <v>2</v>
+      </c>
+      <c r="F345" t="n">
+        <v>1</v>
+      </c>
+      <c r="G345" t="n">
+        <v>0</v>
+      </c>
+      <c r="H345" t="n">
+        <v>0</v>
+      </c>
+      <c r="I345" t="n">
+        <v>1</v>
+      </c>
+      <c r="J345" t="n">
+        <v>1</v>
+      </c>
+      <c r="K345" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -6317,6 +12539,24 @@
         <v>7</v>
       </c>
       <c r="E346" t="n">
+        <v>16</v>
+      </c>
+      <c r="F346" t="n">
+        <v>1</v>
+      </c>
+      <c r="G346" t="n">
+        <v>0</v>
+      </c>
+      <c r="H346" t="n">
+        <v>0</v>
+      </c>
+      <c r="I346" t="n">
+        <v>3</v>
+      </c>
+      <c r="J346" t="n">
+        <v>6</v>
+      </c>
+      <c r="K346" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -6334,6 +12574,24 @@
         <v>9</v>
       </c>
       <c r="E347" t="n">
+        <v>4</v>
+      </c>
+      <c r="F347" t="n">
+        <v>0</v>
+      </c>
+      <c r="G347" t="n">
+        <v>0</v>
+      </c>
+      <c r="H347" t="n">
+        <v>2</v>
+      </c>
+      <c r="I347" t="n">
+        <v>0</v>
+      </c>
+      <c r="J347" t="n">
+        <v>1</v>
+      </c>
+      <c r="K347" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -6351,6 +12609,24 @@
         <v>7</v>
       </c>
       <c r="E348" t="n">
+        <v>0</v>
+      </c>
+      <c r="F348" t="n">
+        <v>0</v>
+      </c>
+      <c r="G348" t="n">
+        <v>0</v>
+      </c>
+      <c r="H348" t="n">
+        <v>0</v>
+      </c>
+      <c r="I348" t="n">
+        <v>0</v>
+      </c>
+      <c r="J348" t="n">
+        <v>0</v>
+      </c>
+      <c r="K348" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -6368,6 +12644,24 @@
         <v>7</v>
       </c>
       <c r="E349" t="n">
+        <v>1</v>
+      </c>
+      <c r="F349" t="n">
+        <v>1</v>
+      </c>
+      <c r="G349" t="n">
+        <v>0</v>
+      </c>
+      <c r="H349" t="n">
+        <v>0</v>
+      </c>
+      <c r="I349" t="n">
+        <v>0</v>
+      </c>
+      <c r="J349" t="n">
+        <v>1</v>
+      </c>
+      <c r="K349" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -6385,6 +12679,24 @@
         <v>9</v>
       </c>
       <c r="E350" t="n">
+        <v>1</v>
+      </c>
+      <c r="F350" t="n">
+        <v>0</v>
+      </c>
+      <c r="G350" t="n">
+        <v>0</v>
+      </c>
+      <c r="H350" t="n">
+        <v>0</v>
+      </c>
+      <c r="I350" t="n">
+        <v>0</v>
+      </c>
+      <c r="J350" t="n">
+        <v>0</v>
+      </c>
+      <c r="K350" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -6402,6 +12714,24 @@
         <v>7</v>
       </c>
       <c r="E351" t="n">
+        <v>4</v>
+      </c>
+      <c r="F351" t="n">
+        <v>0</v>
+      </c>
+      <c r="G351" t="n">
+        <v>0</v>
+      </c>
+      <c r="H351" t="n">
+        <v>0</v>
+      </c>
+      <c r="I351" t="n">
+        <v>0</v>
+      </c>
+      <c r="J351" t="n">
+        <v>4</v>
+      </c>
+      <c r="K351" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -6419,6 +12749,24 @@
         <v>7</v>
       </c>
       <c r="E352" t="n">
+        <v>3</v>
+      </c>
+      <c r="F352" t="n">
+        <v>0</v>
+      </c>
+      <c r="G352" t="n">
+        <v>0</v>
+      </c>
+      <c r="H352" t="n">
+        <v>0</v>
+      </c>
+      <c r="I352" t="n">
+        <v>1</v>
+      </c>
+      <c r="J352" t="n">
+        <v>2</v>
+      </c>
+      <c r="K352" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -6436,6 +12784,24 @@
         <v>7</v>
       </c>
       <c r="E353" t="n">
+        <v>14</v>
+      </c>
+      <c r="F353" t="n">
+        <v>0</v>
+      </c>
+      <c r="G353" t="n">
+        <v>1</v>
+      </c>
+      <c r="H353" t="n">
+        <v>0</v>
+      </c>
+      <c r="I353" t="n">
+        <v>1</v>
+      </c>
+      <c r="J353" t="n">
+        <v>2</v>
+      </c>
+      <c r="K353" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -6453,6 +12819,24 @@
         <v>9</v>
       </c>
       <c r="E354" t="n">
+        <v>13</v>
+      </c>
+      <c r="F354" t="n">
+        <v>2</v>
+      </c>
+      <c r="G354" t="n">
+        <v>0</v>
+      </c>
+      <c r="H354" t="n">
+        <v>0</v>
+      </c>
+      <c r="I354" t="n">
+        <v>0</v>
+      </c>
+      <c r="J354" t="n">
+        <v>1</v>
+      </c>
+      <c r="K354" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -6470,6 +12854,24 @@
         <v>7</v>
       </c>
       <c r="E355" t="n">
+        <v>6</v>
+      </c>
+      <c r="F355" t="n">
+        <v>3</v>
+      </c>
+      <c r="G355" t="n">
+        <v>0</v>
+      </c>
+      <c r="H355" t="n">
+        <v>0</v>
+      </c>
+      <c r="I355" t="n">
+        <v>0</v>
+      </c>
+      <c r="J355" t="n">
+        <v>0</v>
+      </c>
+      <c r="K355" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -6487,6 +12889,24 @@
         <v>7</v>
       </c>
       <c r="E356" t="n">
+        <v>9</v>
+      </c>
+      <c r="F356" t="n">
+        <v>4</v>
+      </c>
+      <c r="G356" t="n">
+        <v>0</v>
+      </c>
+      <c r="H356" t="n">
+        <v>0</v>
+      </c>
+      <c r="I356" t="n">
+        <v>1</v>
+      </c>
+      <c r="J356" t="n">
+        <v>3</v>
+      </c>
+      <c r="K356" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -6504,6 +12924,24 @@
         <v>9</v>
       </c>
       <c r="E357" t="n">
+        <v>21</v>
+      </c>
+      <c r="F357" t="n">
+        <v>0</v>
+      </c>
+      <c r="G357" t="n">
+        <v>0</v>
+      </c>
+      <c r="H357" t="n">
+        <v>0</v>
+      </c>
+      <c r="I357" t="n">
+        <v>0</v>
+      </c>
+      <c r="J357" t="n">
+        <v>9</v>
+      </c>
+      <c r="K357" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -6521,6 +12959,24 @@
         <v>7</v>
       </c>
       <c r="E358" t="n">
+        <v>6</v>
+      </c>
+      <c r="F358" t="n">
+        <v>3</v>
+      </c>
+      <c r="G358" t="n">
+        <v>0</v>
+      </c>
+      <c r="H358" t="n">
+        <v>1</v>
+      </c>
+      <c r="I358" t="n">
+        <v>0</v>
+      </c>
+      <c r="J358" t="n">
+        <v>7</v>
+      </c>
+      <c r="K358" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -6538,6 +12994,24 @@
         <v>9</v>
       </c>
       <c r="E359" t="n">
+        <v>6</v>
+      </c>
+      <c r="F359" t="n">
+        <v>3</v>
+      </c>
+      <c r="G359" t="n">
+        <v>0</v>
+      </c>
+      <c r="H359" t="n">
+        <v>0</v>
+      </c>
+      <c r="I359" t="n">
+        <v>1</v>
+      </c>
+      <c r="J359" t="n">
+        <v>5</v>
+      </c>
+      <c r="K359" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -6555,6 +13029,24 @@
         <v>7</v>
       </c>
       <c r="E360" t="n">
+        <v>8</v>
+      </c>
+      <c r="F360" t="n">
+        <v>5</v>
+      </c>
+      <c r="G360" t="n">
+        <v>0</v>
+      </c>
+      <c r="H360" t="n">
+        <v>0</v>
+      </c>
+      <c r="I360" t="n">
+        <v>3</v>
+      </c>
+      <c r="J360" t="n">
+        <v>0</v>
+      </c>
+      <c r="K360" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -6572,6 +13064,24 @@
         <v>7</v>
       </c>
       <c r="E361" t="n">
+        <v>5</v>
+      </c>
+      <c r="F361" t="n">
+        <v>0</v>
+      </c>
+      <c r="G361" t="n">
+        <v>0</v>
+      </c>
+      <c r="H361" t="n">
+        <v>0</v>
+      </c>
+      <c r="I361" t="n">
+        <v>0</v>
+      </c>
+      <c r="J361" t="n">
+        <v>1</v>
+      </c>
+      <c r="K361" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -6589,6 +13099,24 @@
         <v>9</v>
       </c>
       <c r="E362" t="n">
+        <v>0</v>
+      </c>
+      <c r="F362" t="n">
+        <v>0</v>
+      </c>
+      <c r="G362" t="n">
+        <v>0</v>
+      </c>
+      <c r="H362" t="n">
+        <v>0</v>
+      </c>
+      <c r="I362" t="n">
+        <v>0</v>
+      </c>
+      <c r="J362" t="n">
+        <v>0</v>
+      </c>
+      <c r="K362" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -6606,6 +13134,24 @@
         <v>7</v>
       </c>
       <c r="E363" t="n">
+        <v>5</v>
+      </c>
+      <c r="F363" t="n">
+        <v>2</v>
+      </c>
+      <c r="G363" t="n">
+        <v>0</v>
+      </c>
+      <c r="H363" t="n">
+        <v>0</v>
+      </c>
+      <c r="I363" t="n">
+        <v>0</v>
+      </c>
+      <c r="J363" t="n">
+        <v>6</v>
+      </c>
+      <c r="K363" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -6623,6 +13169,24 @@
         <v>7</v>
       </c>
       <c r="E364" t="n">
+        <v>0</v>
+      </c>
+      <c r="F364" t="n">
+        <v>0</v>
+      </c>
+      <c r="G364" t="n">
+        <v>0</v>
+      </c>
+      <c r="H364" t="n">
+        <v>0</v>
+      </c>
+      <c r="I364" t="n">
+        <v>0</v>
+      </c>
+      <c r="J364" t="n">
+        <v>0</v>
+      </c>
+      <c r="K364" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -6640,6 +13204,24 @@
         <v>9</v>
       </c>
       <c r="E365" t="n">
+        <v>4</v>
+      </c>
+      <c r="F365" t="n">
+        <v>0</v>
+      </c>
+      <c r="G365" t="n">
+        <v>0</v>
+      </c>
+      <c r="H365" t="n">
+        <v>0</v>
+      </c>
+      <c r="I365" t="n">
+        <v>1</v>
+      </c>
+      <c r="J365" t="n">
+        <v>2</v>
+      </c>
+      <c r="K365" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -6657,6 +13239,24 @@
         <v>7</v>
       </c>
       <c r="E366" t="n">
+        <v>19</v>
+      </c>
+      <c r="F366" t="n">
+        <v>3</v>
+      </c>
+      <c r="G366" t="n">
+        <v>0</v>
+      </c>
+      <c r="H366" t="n">
+        <v>0</v>
+      </c>
+      <c r="I366" t="n">
+        <v>0</v>
+      </c>
+      <c r="J366" t="n">
+        <v>10</v>
+      </c>
+      <c r="K366" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -6674,6 +13274,24 @@
         <v>9</v>
       </c>
       <c r="E367" t="n">
+        <v>5</v>
+      </c>
+      <c r="F367" t="n">
+        <v>0</v>
+      </c>
+      <c r="G367" t="n">
+        <v>0</v>
+      </c>
+      <c r="H367" t="n">
+        <v>0</v>
+      </c>
+      <c r="I367" t="n">
+        <v>0</v>
+      </c>
+      <c r="J367" t="n">
+        <v>2</v>
+      </c>
+      <c r="K367" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -6691,6 +13309,24 @@
         <v>7</v>
       </c>
       <c r="E368" t="n">
+        <v>1</v>
+      </c>
+      <c r="F368" t="n">
+        <v>0</v>
+      </c>
+      <c r="G368" t="n">
+        <v>0</v>
+      </c>
+      <c r="H368" t="n">
+        <v>0</v>
+      </c>
+      <c r="I368" t="n">
+        <v>0</v>
+      </c>
+      <c r="J368" t="n">
+        <v>1</v>
+      </c>
+      <c r="K368" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -6708,6 +13344,24 @@
         <v>7</v>
       </c>
       <c r="E369" t="n">
+        <v>8</v>
+      </c>
+      <c r="F369" t="n">
+        <v>3</v>
+      </c>
+      <c r="G369" t="n">
+        <v>0</v>
+      </c>
+      <c r="H369" t="n">
+        <v>0</v>
+      </c>
+      <c r="I369" t="n">
+        <v>0</v>
+      </c>
+      <c r="J369" t="n">
+        <v>7</v>
+      </c>
+      <c r="K369" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -6725,6 +13379,24 @@
         <v>9</v>
       </c>
       <c r="E370" t="n">
+        <v>7</v>
+      </c>
+      <c r="F370" t="n">
+        <v>2</v>
+      </c>
+      <c r="G370" t="n">
+        <v>1</v>
+      </c>
+      <c r="H370" t="n">
+        <v>0</v>
+      </c>
+      <c r="I370" t="n">
+        <v>0</v>
+      </c>
+      <c r="J370" t="n">
+        <v>4</v>
+      </c>
+      <c r="K370" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -6742,6 +13414,24 @@
         <v>7</v>
       </c>
       <c r="E371" t="n">
+        <v>1</v>
+      </c>
+      <c r="F371" t="n">
+        <v>0</v>
+      </c>
+      <c r="G371" t="n">
+        <v>1</v>
+      </c>
+      <c r="H371" t="n">
+        <v>0</v>
+      </c>
+      <c r="I371" t="n">
+        <v>0</v>
+      </c>
+      <c r="J371" t="n">
+        <v>0</v>
+      </c>
+      <c r="K371" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -6759,6 +13449,24 @@
         <v>9</v>
       </c>
       <c r="E372" t="n">
+        <v>1</v>
+      </c>
+      <c r="F372" t="n">
+        <v>0</v>
+      </c>
+      <c r="G372" t="n">
+        <v>0</v>
+      </c>
+      <c r="H372" t="n">
+        <v>0</v>
+      </c>
+      <c r="I372" t="n">
+        <v>1</v>
+      </c>
+      <c r="J372" t="n">
+        <v>0</v>
+      </c>
+      <c r="K372" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -6776,6 +13484,24 @@
         <v>7</v>
       </c>
       <c r="E373" t="n">
+        <v>9</v>
+      </c>
+      <c r="F373" t="n">
+        <v>1</v>
+      </c>
+      <c r="G373" t="n">
+        <v>0</v>
+      </c>
+      <c r="H373" t="n">
+        <v>0</v>
+      </c>
+      <c r="I373" t="n">
+        <v>0</v>
+      </c>
+      <c r="J373" t="n">
+        <v>2</v>
+      </c>
+      <c r="K373" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -6793,6 +13519,24 @@
         <v>9</v>
       </c>
       <c r="E374" t="n">
+        <v>3</v>
+      </c>
+      <c r="F374" t="n">
+        <v>0</v>
+      </c>
+      <c r="G374" t="n">
+        <v>0</v>
+      </c>
+      <c r="H374" t="n">
+        <v>0</v>
+      </c>
+      <c r="I374" t="n">
+        <v>0</v>
+      </c>
+      <c r="J374" t="n">
+        <v>0</v>
+      </c>
+      <c r="K374" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -6810,6 +13554,24 @@
         <v>7</v>
       </c>
       <c r="E375" t="n">
+        <v>6</v>
+      </c>
+      <c r="F375" t="n">
+        <v>1</v>
+      </c>
+      <c r="G375" t="n">
+        <v>0</v>
+      </c>
+      <c r="H375" t="n">
+        <v>0</v>
+      </c>
+      <c r="I375" t="n">
+        <v>0</v>
+      </c>
+      <c r="J375" t="n">
+        <v>4</v>
+      </c>
+      <c r="K375" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -6827,6 +13589,24 @@
         <v>9</v>
       </c>
       <c r="E376" t="n">
+        <v>0</v>
+      </c>
+      <c r="F376" t="n">
+        <v>0</v>
+      </c>
+      <c r="G376" t="n">
+        <v>0</v>
+      </c>
+      <c r="H376" t="n">
+        <v>0</v>
+      </c>
+      <c r="I376" t="n">
+        <v>0</v>
+      </c>
+      <c r="J376" t="n">
+        <v>0</v>
+      </c>
+      <c r="K376" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -6844,6 +13624,24 @@
         <v>7</v>
       </c>
       <c r="E377" t="n">
+        <v>1</v>
+      </c>
+      <c r="F377" t="n">
+        <v>3</v>
+      </c>
+      <c r="G377" t="n">
+        <v>0</v>
+      </c>
+      <c r="H377" t="n">
+        <v>1</v>
+      </c>
+      <c r="I377" t="n">
+        <v>0</v>
+      </c>
+      <c r="J377" t="n">
+        <v>3</v>
+      </c>
+      <c r="K377" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -6861,6 +13659,24 @@
         <v>7</v>
       </c>
       <c r="E378" t="n">
+        <v>10</v>
+      </c>
+      <c r="F378" t="n">
+        <v>4</v>
+      </c>
+      <c r="G378" t="n">
+        <v>0</v>
+      </c>
+      <c r="H378" t="n">
+        <v>0</v>
+      </c>
+      <c r="I378" t="n">
+        <v>0</v>
+      </c>
+      <c r="J378" t="n">
+        <v>8</v>
+      </c>
+      <c r="K378" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -6878,6 +13694,24 @@
         <v>9</v>
       </c>
       <c r="E379" t="n">
+        <v>7</v>
+      </c>
+      <c r="F379" t="n">
+        <v>1</v>
+      </c>
+      <c r="G379" t="n">
+        <v>0</v>
+      </c>
+      <c r="H379" t="n">
+        <v>0</v>
+      </c>
+      <c r="I379" t="n">
+        <v>0</v>
+      </c>
+      <c r="J379" t="n">
+        <v>4</v>
+      </c>
+      <c r="K379" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -6895,6 +13729,24 @@
         <v>7</v>
       </c>
       <c r="E380" t="n">
+        <v>0</v>
+      </c>
+      <c r="F380" t="n">
+        <v>0</v>
+      </c>
+      <c r="G380" t="n">
+        <v>0</v>
+      </c>
+      <c r="H380" t="n">
+        <v>0</v>
+      </c>
+      <c r="I380" t="n">
+        <v>0</v>
+      </c>
+      <c r="J380" t="n">
+        <v>0</v>
+      </c>
+      <c r="K380" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -6912,6 +13764,24 @@
         <v>7</v>
       </c>
       <c r="E381" t="n">
+        <v>1</v>
+      </c>
+      <c r="F381" t="n">
+        <v>2</v>
+      </c>
+      <c r="G381" t="n">
+        <v>0</v>
+      </c>
+      <c r="H381" t="n">
+        <v>0</v>
+      </c>
+      <c r="I381" t="n">
+        <v>0</v>
+      </c>
+      <c r="J381" t="n">
+        <v>1</v>
+      </c>
+      <c r="K381" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -6929,6 +13799,24 @@
         <v>9</v>
       </c>
       <c r="E382" t="n">
+        <v>1</v>
+      </c>
+      <c r="F382" t="n">
+        <v>0</v>
+      </c>
+      <c r="G382" t="n">
+        <v>0</v>
+      </c>
+      <c r="H382" t="n">
+        <v>0</v>
+      </c>
+      <c r="I382" t="n">
+        <v>0</v>
+      </c>
+      <c r="J382" t="n">
+        <v>0</v>
+      </c>
+      <c r="K382" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -6946,6 +13834,24 @@
         <v>7</v>
       </c>
       <c r="E383" t="n">
+        <v>22</v>
+      </c>
+      <c r="F383" t="n">
+        <v>7</v>
+      </c>
+      <c r="G383" t="n">
+        <v>0</v>
+      </c>
+      <c r="H383" t="n">
+        <v>4</v>
+      </c>
+      <c r="I383" t="n">
+        <v>0</v>
+      </c>
+      <c r="J383" t="n">
+        <v>14</v>
+      </c>
+      <c r="K383" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -6963,6 +13869,24 @@
         <v>9</v>
       </c>
       <c r="E384" t="n">
+        <v>21</v>
+      </c>
+      <c r="F384" t="n">
+        <v>5</v>
+      </c>
+      <c r="G384" t="n">
+        <v>0</v>
+      </c>
+      <c r="H384" t="n">
+        <v>0</v>
+      </c>
+      <c r="I384" t="n">
+        <v>0</v>
+      </c>
+      <c r="J384" t="n">
+        <v>18</v>
+      </c>
+      <c r="K384" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -6980,6 +13904,24 @@
         <v>7</v>
       </c>
       <c r="E385" t="n">
+        <v>7</v>
+      </c>
+      <c r="F385" t="n">
+        <v>0</v>
+      </c>
+      <c r="G385" t="n">
+        <v>0</v>
+      </c>
+      <c r="H385" t="n">
+        <v>0</v>
+      </c>
+      <c r="I385" t="n">
+        <v>0</v>
+      </c>
+      <c r="J385" t="n">
+        <v>2</v>
+      </c>
+      <c r="K385" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -6997,6 +13939,24 @@
         <v>9</v>
       </c>
       <c r="E386" t="n">
+        <v>4</v>
+      </c>
+      <c r="F386" t="n">
+        <v>1</v>
+      </c>
+      <c r="G386" t="n">
+        <v>0</v>
+      </c>
+      <c r="H386" t="n">
+        <v>0</v>
+      </c>
+      <c r="I386" t="n">
+        <v>0</v>
+      </c>
+      <c r="J386" t="n">
+        <v>3</v>
+      </c>
+      <c r="K386" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -7014,6 +13974,24 @@
         <v>7</v>
       </c>
       <c r="E387" t="n">
+        <v>1</v>
+      </c>
+      <c r="F387" t="n">
+        <v>0</v>
+      </c>
+      <c r="G387" t="n">
+        <v>0</v>
+      </c>
+      <c r="H387" t="n">
+        <v>0</v>
+      </c>
+      <c r="I387" t="n">
+        <v>0</v>
+      </c>
+      <c r="J387" t="n">
+        <v>1</v>
+      </c>
+      <c r="K387" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -7031,6 +14009,24 @@
         <v>7</v>
       </c>
       <c r="E388" t="n">
+        <v>9</v>
+      </c>
+      <c r="F388" t="n">
+        <v>3</v>
+      </c>
+      <c r="G388" t="n">
+        <v>0</v>
+      </c>
+      <c r="H388" t="n">
+        <v>0</v>
+      </c>
+      <c r="I388" t="n">
+        <v>0</v>
+      </c>
+      <c r="J388" t="n">
+        <v>12</v>
+      </c>
+      <c r="K388" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -7048,6 +14044,24 @@
         <v>9</v>
       </c>
       <c r="E389" t="n">
+        <v>19</v>
+      </c>
+      <c r="F389" t="n">
+        <v>6</v>
+      </c>
+      <c r="G389" t="n">
+        <v>0</v>
+      </c>
+      <c r="H389" t="n">
+        <v>0</v>
+      </c>
+      <c r="I389" t="n">
+        <v>1</v>
+      </c>
+      <c r="J389" t="n">
+        <v>10</v>
+      </c>
+      <c r="K389" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -7065,6 +14079,24 @@
         <v>7</v>
       </c>
       <c r="E390" t="n">
+        <v>2</v>
+      </c>
+      <c r="F390" t="n">
+        <v>0</v>
+      </c>
+      <c r="G390" t="n">
+        <v>0</v>
+      </c>
+      <c r="H390" t="n">
+        <v>0</v>
+      </c>
+      <c r="I390" t="n">
+        <v>0</v>
+      </c>
+      <c r="J390" t="n">
+        <v>2</v>
+      </c>
+      <c r="K390" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -7082,6 +14114,24 @@
         <v>9</v>
       </c>
       <c r="E391" t="n">
+        <v>4</v>
+      </c>
+      <c r="F391" t="n">
+        <v>0</v>
+      </c>
+      <c r="G391" t="n">
+        <v>0</v>
+      </c>
+      <c r="H391" t="n">
+        <v>0</v>
+      </c>
+      <c r="I391" t="n">
+        <v>0</v>
+      </c>
+      <c r="J391" t="n">
+        <v>1</v>
+      </c>
+      <c r="K391" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -7099,6 +14149,24 @@
         <v>7</v>
       </c>
       <c r="E392" t="n">
+        <v>2</v>
+      </c>
+      <c r="F392" t="n">
+        <v>1</v>
+      </c>
+      <c r="G392" t="n">
+        <v>0</v>
+      </c>
+      <c r="H392" t="n">
+        <v>0</v>
+      </c>
+      <c r="I392" t="n">
+        <v>0</v>
+      </c>
+      <c r="J392" t="n">
+        <v>2</v>
+      </c>
+      <c r="K392" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -7116,6 +14184,24 @@
         <v>9</v>
       </c>
       <c r="E393" t="n">
+        <v>0</v>
+      </c>
+      <c r="F393" t="n">
+        <v>0</v>
+      </c>
+      <c r="G393" t="n">
+        <v>0</v>
+      </c>
+      <c r="H393" t="n">
+        <v>0</v>
+      </c>
+      <c r="I393" t="n">
+        <v>0</v>
+      </c>
+      <c r="J393" t="n">
+        <v>0</v>
+      </c>
+      <c r="K393" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -7133,6 +14219,24 @@
         <v>7</v>
       </c>
       <c r="E394" t="n">
+        <v>3</v>
+      </c>
+      <c r="F394" t="n">
+        <v>2</v>
+      </c>
+      <c r="G394" t="n">
+        <v>0</v>
+      </c>
+      <c r="H394" t="n">
+        <v>0</v>
+      </c>
+      <c r="I394" t="n">
+        <v>5</v>
+      </c>
+      <c r="J394" t="n">
+        <v>0</v>
+      </c>
+      <c r="K394" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -7150,6 +14254,24 @@
         <v>7</v>
       </c>
       <c r="E395" t="n">
+        <v>2</v>
+      </c>
+      <c r="F395" t="n">
+        <v>0</v>
+      </c>
+      <c r="G395" t="n">
+        <v>0</v>
+      </c>
+      <c r="H395" t="n">
+        <v>0</v>
+      </c>
+      <c r="I395" t="n">
+        <v>2</v>
+      </c>
+      <c r="J395" t="n">
+        <v>0</v>
+      </c>
+      <c r="K395" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -7167,6 +14289,24 @@
         <v>7</v>
       </c>
       <c r="E396" t="n">
+        <v>11</v>
+      </c>
+      <c r="F396" t="n">
+        <v>2</v>
+      </c>
+      <c r="G396" t="n">
+        <v>0</v>
+      </c>
+      <c r="H396" t="n">
+        <v>0</v>
+      </c>
+      <c r="I396" t="n">
+        <v>0</v>
+      </c>
+      <c r="J396" t="n">
+        <v>5</v>
+      </c>
+      <c r="K396" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -7184,6 +14324,24 @@
         <v>9</v>
       </c>
       <c r="E397" t="n">
+        <v>20</v>
+      </c>
+      <c r="F397" t="n">
+        <v>4</v>
+      </c>
+      <c r="G397" t="n">
+        <v>0</v>
+      </c>
+      <c r="H397" t="n">
+        <v>1</v>
+      </c>
+      <c r="I397" t="n">
+        <v>0</v>
+      </c>
+      <c r="J397" t="n">
+        <v>11</v>
+      </c>
+      <c r="K397" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -7201,6 +14359,24 @@
         <v>7</v>
       </c>
       <c r="E398" t="n">
+        <v>12</v>
+      </c>
+      <c r="F398" t="n">
+        <v>6</v>
+      </c>
+      <c r="G398" t="n">
+        <v>0</v>
+      </c>
+      <c r="H398" t="n">
+        <v>0</v>
+      </c>
+      <c r="I398" t="n">
+        <v>0</v>
+      </c>
+      <c r="J398" t="n">
+        <v>6</v>
+      </c>
+      <c r="K398" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -7218,6 +14394,24 @@
         <v>9</v>
       </c>
       <c r="E399" t="n">
+        <v>8</v>
+      </c>
+      <c r="F399" t="n">
+        <v>4</v>
+      </c>
+      <c r="G399" t="n">
+        <v>0</v>
+      </c>
+      <c r="H399" t="n">
+        <v>0</v>
+      </c>
+      <c r="I399" t="n">
+        <v>0</v>
+      </c>
+      <c r="J399" t="n">
+        <v>3</v>
+      </c>
+      <c r="K399" t="n">
         <v>2006</v>
       </c>
     </row>

--- a/Excel Files IPEDS/Trimmed/c2006_trimmed_file.xlsx
+++ b/Excel Files IPEDS/Trimmed/c2006_trimmed_file.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K399"/>
+  <dimension ref="A1:M399"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -481,6 +481,16 @@
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
+          <t>CRACE17</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>CRACE19</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
           <t>Year</t>
         </is>
       </c>
@@ -517,6 +527,12 @@
         <v>0</v>
       </c>
       <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -552,6 +568,12 @@
         <v>5</v>
       </c>
       <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -587,6 +609,12 @@
         <v>2</v>
       </c>
       <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -622,6 +650,12 @@
         <v>5</v>
       </c>
       <c r="K5" t="n">
+        <v>3</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -657,6 +691,12 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
+        <v>3</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -692,6 +732,12 @@
         <v>1</v>
       </c>
       <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -727,6 +773,12 @@
         <v>2</v>
       </c>
       <c r="K8" t="n">
+        <v>1</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -762,6 +814,12 @@
         <v>2</v>
       </c>
       <c r="K9" t="n">
+        <v>3</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -797,6 +855,12 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
+        <v>1</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -832,6 +896,12 @@
         <v>1</v>
       </c>
       <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -867,6 +937,12 @@
         <v>1</v>
       </c>
       <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -902,6 +978,12 @@
         <v>1</v>
       </c>
       <c r="K13" t="n">
+        <v>3</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -937,6 +1019,12 @@
         <v>4</v>
       </c>
       <c r="K14" t="n">
+        <v>3</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -972,6 +1060,12 @@
         <v>11</v>
       </c>
       <c r="K15" t="n">
+        <v>6</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -1007,6 +1101,12 @@
         <v>1</v>
       </c>
       <c r="K16" t="n">
+        <v>1</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -1042,6 +1142,12 @@
         <v>5</v>
       </c>
       <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -1077,6 +1183,12 @@
         <v>5</v>
       </c>
       <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -1112,6 +1224,12 @@
         <v>1</v>
       </c>
       <c r="K19" t="n">
+        <v>5</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -1147,6 +1265,12 @@
         <v>2</v>
       </c>
       <c r="K20" t="n">
+        <v>1</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -1182,6 +1306,12 @@
         <v>7</v>
       </c>
       <c r="K21" t="n">
+        <v>14</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -1217,6 +1347,12 @@
         <v>0</v>
       </c>
       <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -1252,6 +1388,12 @@
         <v>2</v>
       </c>
       <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -1287,6 +1429,12 @@
         <v>1</v>
       </c>
       <c r="K24" t="n">
+        <v>1</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -1322,6 +1470,12 @@
         <v>1</v>
       </c>
       <c r="K25" t="n">
+        <v>3</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -1357,6 +1511,12 @@
         <v>3</v>
       </c>
       <c r="K26" t="n">
+        <v>1</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -1392,6 +1552,12 @@
         <v>1</v>
       </c>
       <c r="K27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -1427,6 +1593,12 @@
         <v>2</v>
       </c>
       <c r="K28" t="n">
+        <v>2</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -1462,6 +1634,12 @@
         <v>22</v>
       </c>
       <c r="K29" t="n">
+        <v>4</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -1497,6 +1675,12 @@
         <v>10</v>
       </c>
       <c r="K30" t="n">
+        <v>8</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -1532,6 +1716,12 @@
         <v>10</v>
       </c>
       <c r="K31" t="n">
+        <v>1</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -1567,6 +1757,12 @@
         <v>3</v>
       </c>
       <c r="K32" t="n">
+        <v>3</v>
+      </c>
+      <c r="L32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -1602,6 +1798,12 @@
         <v>5</v>
       </c>
       <c r="K33" t="n">
+        <v>3</v>
+      </c>
+      <c r="L33" t="n">
+        <v>0</v>
+      </c>
+      <c r="M33" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -1637,6 +1839,12 @@
         <v>1</v>
       </c>
       <c r="K34" t="n">
+        <v>3</v>
+      </c>
+      <c r="L34" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -1672,6 +1880,12 @@
         <v>13</v>
       </c>
       <c r="K35" t="n">
+        <v>1</v>
+      </c>
+      <c r="L35" t="n">
+        <v>0</v>
+      </c>
+      <c r="M35" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -1707,6 +1921,12 @@
         <v>12</v>
       </c>
       <c r="K36" t="n">
+        <v>6</v>
+      </c>
+      <c r="L36" t="n">
+        <v>0</v>
+      </c>
+      <c r="M36" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -1742,6 +1962,12 @@
         <v>2</v>
       </c>
       <c r="K37" t="n">
+        <v>2</v>
+      </c>
+      <c r="L37" t="n">
+        <v>0</v>
+      </c>
+      <c r="M37" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -1777,6 +2003,12 @@
         <v>2</v>
       </c>
       <c r="K38" t="n">
+        <v>1</v>
+      </c>
+      <c r="L38" t="n">
+        <v>0</v>
+      </c>
+      <c r="M38" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -1812,6 +2044,12 @@
         <v>11</v>
       </c>
       <c r="K39" t="n">
+        <v>1</v>
+      </c>
+      <c r="L39" t="n">
+        <v>0</v>
+      </c>
+      <c r="M39" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -1847,6 +2085,12 @@
         <v>10</v>
       </c>
       <c r="K40" t="n">
+        <v>2</v>
+      </c>
+      <c r="L40" t="n">
+        <v>0</v>
+      </c>
+      <c r="M40" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -1882,6 +2126,12 @@
         <v>2</v>
       </c>
       <c r="K41" t="n">
+        <v>3</v>
+      </c>
+      <c r="L41" t="n">
+        <v>0</v>
+      </c>
+      <c r="M41" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -1917,6 +2167,12 @@
         <v>16</v>
       </c>
       <c r="K42" t="n">
+        <v>2</v>
+      </c>
+      <c r="L42" t="n">
+        <v>0</v>
+      </c>
+      <c r="M42" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -1952,6 +2208,12 @@
         <v>9</v>
       </c>
       <c r="K43" t="n">
+        <v>1</v>
+      </c>
+      <c r="L43" t="n">
+        <v>0</v>
+      </c>
+      <c r="M43" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -1987,6 +2249,12 @@
         <v>5</v>
       </c>
       <c r="K44" t="n">
+        <v>1</v>
+      </c>
+      <c r="L44" t="n">
+        <v>0</v>
+      </c>
+      <c r="M44" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -2022,6 +2290,12 @@
         <v>17</v>
       </c>
       <c r="K45" t="n">
+        <v>4</v>
+      </c>
+      <c r="L45" t="n">
+        <v>0</v>
+      </c>
+      <c r="M45" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -2057,6 +2331,12 @@
         <v>1</v>
       </c>
       <c r="K46" t="n">
+        <v>0</v>
+      </c>
+      <c r="L46" t="n">
+        <v>0</v>
+      </c>
+      <c r="M46" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -2092,6 +2372,12 @@
         <v>1</v>
       </c>
       <c r="K47" t="n">
+        <v>3</v>
+      </c>
+      <c r="L47" t="n">
+        <v>1</v>
+      </c>
+      <c r="M47" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -2127,6 +2413,12 @@
         <v>1</v>
       </c>
       <c r="K48" t="n">
+        <v>3</v>
+      </c>
+      <c r="L48" t="n">
+        <v>0</v>
+      </c>
+      <c r="M48" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -2162,6 +2454,12 @@
         <v>2</v>
       </c>
       <c r="K49" t="n">
+        <v>4</v>
+      </c>
+      <c r="L49" t="n">
+        <v>0</v>
+      </c>
+      <c r="M49" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -2197,6 +2495,12 @@
         <v>0</v>
       </c>
       <c r="K50" t="n">
+        <v>7</v>
+      </c>
+      <c r="L50" t="n">
+        <v>0</v>
+      </c>
+      <c r="M50" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -2232,6 +2536,12 @@
         <v>5</v>
       </c>
       <c r="K51" t="n">
+        <v>1</v>
+      </c>
+      <c r="L51" t="n">
+        <v>0</v>
+      </c>
+      <c r="M51" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -2267,6 +2577,12 @@
         <v>10</v>
       </c>
       <c r="K52" t="n">
+        <v>5</v>
+      </c>
+      <c r="L52" t="n">
+        <v>0</v>
+      </c>
+      <c r="M52" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -2302,6 +2618,12 @@
         <v>4</v>
       </c>
       <c r="K53" t="n">
+        <v>1</v>
+      </c>
+      <c r="L53" t="n">
+        <v>0</v>
+      </c>
+      <c r="M53" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -2337,6 +2659,12 @@
         <v>7</v>
       </c>
       <c r="K54" t="n">
+        <v>2</v>
+      </c>
+      <c r="L54" t="n">
+        <v>0</v>
+      </c>
+      <c r="M54" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -2372,6 +2700,12 @@
         <v>0</v>
       </c>
       <c r="K55" t="n">
+        <v>4</v>
+      </c>
+      <c r="L55" t="n">
+        <v>0</v>
+      </c>
+      <c r="M55" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -2407,6 +2741,12 @@
         <v>1</v>
       </c>
       <c r="K56" t="n">
+        <v>1</v>
+      </c>
+      <c r="L56" t="n">
+        <v>0</v>
+      </c>
+      <c r="M56" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -2442,6 +2782,12 @@
         <v>1</v>
       </c>
       <c r="K57" t="n">
+        <v>0</v>
+      </c>
+      <c r="L57" t="n">
+        <v>0</v>
+      </c>
+      <c r="M57" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -2477,6 +2823,12 @@
         <v>0</v>
       </c>
       <c r="K58" t="n">
+        <v>4</v>
+      </c>
+      <c r="L58" t="n">
+        <v>0</v>
+      </c>
+      <c r="M58" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -2512,6 +2864,12 @@
         <v>2</v>
       </c>
       <c r="K59" t="n">
+        <v>4</v>
+      </c>
+      <c r="L59" t="n">
+        <v>0</v>
+      </c>
+      <c r="M59" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -2547,6 +2905,12 @@
         <v>0</v>
       </c>
       <c r="K60" t="n">
+        <v>3</v>
+      </c>
+      <c r="L60" t="n">
+        <v>0</v>
+      </c>
+      <c r="M60" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -2582,6 +2946,12 @@
         <v>1</v>
       </c>
       <c r="K61" t="n">
+        <v>1</v>
+      </c>
+      <c r="L61" t="n">
+        <v>0</v>
+      </c>
+      <c r="M61" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -2617,6 +2987,12 @@
         <v>12</v>
       </c>
       <c r="K62" t="n">
+        <v>15</v>
+      </c>
+      <c r="L62" t="n">
+        <v>0</v>
+      </c>
+      <c r="M62" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -2652,6 +3028,12 @@
         <v>3</v>
       </c>
       <c r="K63" t="n">
+        <v>8</v>
+      </c>
+      <c r="L63" t="n">
+        <v>0</v>
+      </c>
+      <c r="M63" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -2687,6 +3069,12 @@
         <v>1</v>
       </c>
       <c r="K64" t="n">
+        <v>0</v>
+      </c>
+      <c r="L64" t="n">
+        <v>0</v>
+      </c>
+      <c r="M64" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -2722,6 +3110,12 @@
         <v>1</v>
       </c>
       <c r="K65" t="n">
+        <v>1</v>
+      </c>
+      <c r="L65" t="n">
+        <v>0</v>
+      </c>
+      <c r="M65" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -2757,6 +3151,12 @@
         <v>1</v>
       </c>
       <c r="K66" t="n">
+        <v>1</v>
+      </c>
+      <c r="L66" t="n">
+        <v>0</v>
+      </c>
+      <c r="M66" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -2792,6 +3192,12 @@
         <v>5</v>
       </c>
       <c r="K67" t="n">
+        <v>2</v>
+      </c>
+      <c r="L67" t="n">
+        <v>0</v>
+      </c>
+      <c r="M67" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -2827,6 +3233,12 @@
         <v>2</v>
       </c>
       <c r="K68" t="n">
+        <v>0</v>
+      </c>
+      <c r="L68" t="n">
+        <v>0</v>
+      </c>
+      <c r="M68" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -2862,6 +3274,12 @@
         <v>1</v>
       </c>
       <c r="K69" t="n">
+        <v>0</v>
+      </c>
+      <c r="L69" t="n">
+        <v>0</v>
+      </c>
+      <c r="M69" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -2897,6 +3315,12 @@
         <v>0</v>
       </c>
       <c r="K70" t="n">
+        <v>1</v>
+      </c>
+      <c r="L70" t="n">
+        <v>0</v>
+      </c>
+      <c r="M70" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -2932,6 +3356,12 @@
         <v>1</v>
       </c>
       <c r="K71" t="n">
+        <v>2</v>
+      </c>
+      <c r="L71" t="n">
+        <v>0</v>
+      </c>
+      <c r="M71" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -2967,6 +3397,12 @@
         <v>0</v>
       </c>
       <c r="K72" t="n">
+        <v>1</v>
+      </c>
+      <c r="L72" t="n">
+        <v>0</v>
+      </c>
+      <c r="M72" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -3002,6 +3438,12 @@
         <v>0</v>
       </c>
       <c r="K73" t="n">
+        <v>1</v>
+      </c>
+      <c r="L73" t="n">
+        <v>0</v>
+      </c>
+      <c r="M73" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -3037,6 +3479,12 @@
         <v>1</v>
       </c>
       <c r="K74" t="n">
+        <v>2</v>
+      </c>
+      <c r="L74" t="n">
+        <v>0</v>
+      </c>
+      <c r="M74" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -3072,6 +3520,12 @@
         <v>2</v>
       </c>
       <c r="K75" t="n">
+        <v>1</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0</v>
+      </c>
+      <c r="M75" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -3107,6 +3561,12 @@
         <v>0</v>
       </c>
       <c r="K76" t="n">
+        <v>0</v>
+      </c>
+      <c r="L76" t="n">
+        <v>0</v>
+      </c>
+      <c r="M76" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -3142,6 +3602,12 @@
         <v>1</v>
       </c>
       <c r="K77" t="n">
+        <v>0</v>
+      </c>
+      <c r="L77" t="n">
+        <v>0</v>
+      </c>
+      <c r="M77" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -3177,6 +3643,12 @@
         <v>2</v>
       </c>
       <c r="K78" t="n">
+        <v>3</v>
+      </c>
+      <c r="L78" t="n">
+        <v>0</v>
+      </c>
+      <c r="M78" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -3212,6 +3684,12 @@
         <v>1</v>
       </c>
       <c r="K79" t="n">
+        <v>1</v>
+      </c>
+      <c r="L79" t="n">
+        <v>0</v>
+      </c>
+      <c r="M79" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -3247,6 +3725,12 @@
         <v>1</v>
       </c>
       <c r="K80" t="n">
+        <v>2</v>
+      </c>
+      <c r="L80" t="n">
+        <v>0</v>
+      </c>
+      <c r="M80" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -3282,6 +3766,12 @@
         <v>13</v>
       </c>
       <c r="K81" t="n">
+        <v>4</v>
+      </c>
+      <c r="L81" t="n">
+        <v>0</v>
+      </c>
+      <c r="M81" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -3317,6 +3807,12 @@
         <v>3</v>
       </c>
       <c r="K82" t="n">
+        <v>9</v>
+      </c>
+      <c r="L82" t="n">
+        <v>0</v>
+      </c>
+      <c r="M82" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -3352,6 +3848,12 @@
         <v>6</v>
       </c>
       <c r="K83" t="n">
+        <v>10</v>
+      </c>
+      <c r="L83" t="n">
+        <v>0</v>
+      </c>
+      <c r="M83" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -3387,6 +3889,12 @@
         <v>6</v>
       </c>
       <c r="K84" t="n">
+        <v>13</v>
+      </c>
+      <c r="L84" t="n">
+        <v>0</v>
+      </c>
+      <c r="M84" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -3422,6 +3930,12 @@
         <v>1</v>
       </c>
       <c r="K85" t="n">
+        <v>6</v>
+      </c>
+      <c r="L85" t="n">
+        <v>0</v>
+      </c>
+      <c r="M85" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -3457,6 +3971,12 @@
         <v>0</v>
       </c>
       <c r="K86" t="n">
+        <v>0</v>
+      </c>
+      <c r="L86" t="n">
+        <v>0</v>
+      </c>
+      <c r="M86" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -3492,6 +4012,12 @@
         <v>3</v>
       </c>
       <c r="K87" t="n">
+        <v>3</v>
+      </c>
+      <c r="L87" t="n">
+        <v>0</v>
+      </c>
+      <c r="M87" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -3527,6 +4053,12 @@
         <v>1</v>
       </c>
       <c r="K88" t="n">
+        <v>1</v>
+      </c>
+      <c r="L88" t="n">
+        <v>0</v>
+      </c>
+      <c r="M88" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -3562,6 +4094,12 @@
         <v>0</v>
       </c>
       <c r="K89" t="n">
+        <v>0</v>
+      </c>
+      <c r="L89" t="n">
+        <v>0</v>
+      </c>
+      <c r="M89" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -3597,6 +4135,12 @@
         <v>0</v>
       </c>
       <c r="K90" t="n">
+        <v>0</v>
+      </c>
+      <c r="L90" t="n">
+        <v>0</v>
+      </c>
+      <c r="M90" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -3632,6 +4176,12 @@
         <v>7</v>
       </c>
       <c r="K91" t="n">
+        <v>9</v>
+      </c>
+      <c r="L91" t="n">
+        <v>0</v>
+      </c>
+      <c r="M91" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -3667,6 +4217,12 @@
         <v>2</v>
       </c>
       <c r="K92" t="n">
+        <v>7</v>
+      </c>
+      <c r="L92" t="n">
+        <v>0</v>
+      </c>
+      <c r="M92" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -3702,6 +4258,12 @@
         <v>4</v>
       </c>
       <c r="K93" t="n">
+        <v>6</v>
+      </c>
+      <c r="L93" t="n">
+        <v>0</v>
+      </c>
+      <c r="M93" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -3737,6 +4299,12 @@
         <v>1</v>
       </c>
       <c r="K94" t="n">
+        <v>3</v>
+      </c>
+      <c r="L94" t="n">
+        <v>0</v>
+      </c>
+      <c r="M94" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -3772,6 +4340,12 @@
         <v>0</v>
       </c>
       <c r="K95" t="n">
+        <v>0</v>
+      </c>
+      <c r="L95" t="n">
+        <v>0</v>
+      </c>
+      <c r="M95" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -3807,6 +4381,12 @@
         <v>3</v>
       </c>
       <c r="K96" t="n">
+        <v>4</v>
+      </c>
+      <c r="L96" t="n">
+        <v>0</v>
+      </c>
+      <c r="M96" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -3842,6 +4422,12 @@
         <v>2</v>
       </c>
       <c r="K97" t="n">
+        <v>0</v>
+      </c>
+      <c r="L97" t="n">
+        <v>0</v>
+      </c>
+      <c r="M97" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -3877,6 +4463,12 @@
         <v>1</v>
       </c>
       <c r="K98" t="n">
+        <v>0</v>
+      </c>
+      <c r="L98" t="n">
+        <v>0</v>
+      </c>
+      <c r="M98" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -3912,6 +4504,12 @@
         <v>7</v>
       </c>
       <c r="K99" t="n">
+        <v>2</v>
+      </c>
+      <c r="L99" t="n">
+        <v>0</v>
+      </c>
+      <c r="M99" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -3947,6 +4545,12 @@
         <v>1</v>
       </c>
       <c r="K100" t="n">
+        <v>2</v>
+      </c>
+      <c r="L100" t="n">
+        <v>0</v>
+      </c>
+      <c r="M100" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -3982,6 +4586,12 @@
         <v>0</v>
       </c>
       <c r="K101" t="n">
+        <v>1</v>
+      </c>
+      <c r="L101" t="n">
+        <v>0</v>
+      </c>
+      <c r="M101" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -4017,6 +4627,12 @@
         <v>9</v>
       </c>
       <c r="K102" t="n">
+        <v>6</v>
+      </c>
+      <c r="L102" t="n">
+        <v>0</v>
+      </c>
+      <c r="M102" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -4052,6 +4668,12 @@
         <v>4</v>
       </c>
       <c r="K103" t="n">
+        <v>11</v>
+      </c>
+      <c r="L103" t="n">
+        <v>0</v>
+      </c>
+      <c r="M103" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -4087,6 +4709,12 @@
         <v>1</v>
       </c>
       <c r="K104" t="n">
+        <v>0</v>
+      </c>
+      <c r="L104" t="n">
+        <v>0</v>
+      </c>
+      <c r="M104" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -4122,6 +4750,12 @@
         <v>0</v>
       </c>
       <c r="K105" t="n">
+        <v>0</v>
+      </c>
+      <c r="L105" t="n">
+        <v>0</v>
+      </c>
+      <c r="M105" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -4157,6 +4791,12 @@
         <v>5</v>
       </c>
       <c r="K106" t="n">
+        <v>6</v>
+      </c>
+      <c r="L106" t="n">
+        <v>0</v>
+      </c>
+      <c r="M106" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -4192,6 +4832,12 @@
         <v>0</v>
       </c>
       <c r="K107" t="n">
+        <v>7</v>
+      </c>
+      <c r="L107" t="n">
+        <v>0</v>
+      </c>
+      <c r="M107" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -4227,6 +4873,12 @@
         <v>20</v>
       </c>
       <c r="K108" t="n">
+        <v>13</v>
+      </c>
+      <c r="L108" t="n">
+        <v>0</v>
+      </c>
+      <c r="M108" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -4262,6 +4914,12 @@
         <v>17</v>
       </c>
       <c r="K109" t="n">
+        <v>19</v>
+      </c>
+      <c r="L109" t="n">
+        <v>1</v>
+      </c>
+      <c r="M109" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -4297,6 +4955,12 @@
         <v>0</v>
       </c>
       <c r="K110" t="n">
+        <v>2</v>
+      </c>
+      <c r="L110" t="n">
+        <v>0</v>
+      </c>
+      <c r="M110" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -4332,6 +4996,12 @@
         <v>3</v>
       </c>
       <c r="K111" t="n">
+        <v>0</v>
+      </c>
+      <c r="L111" t="n">
+        <v>0</v>
+      </c>
+      <c r="M111" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -4367,6 +5037,12 @@
         <v>2</v>
       </c>
       <c r="K112" t="n">
+        <v>2</v>
+      </c>
+      <c r="L112" t="n">
+        <v>0</v>
+      </c>
+      <c r="M112" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -4402,6 +5078,12 @@
         <v>2</v>
       </c>
       <c r="K113" t="n">
+        <v>1</v>
+      </c>
+      <c r="L113" t="n">
+        <v>0</v>
+      </c>
+      <c r="M113" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -4437,6 +5119,12 @@
         <v>0</v>
       </c>
       <c r="K114" t="n">
+        <v>0</v>
+      </c>
+      <c r="L114" t="n">
+        <v>0</v>
+      </c>
+      <c r="M114" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -4472,6 +5160,12 @@
         <v>0</v>
       </c>
       <c r="K115" t="n">
+        <v>0</v>
+      </c>
+      <c r="L115" t="n">
+        <v>0</v>
+      </c>
+      <c r="M115" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -4507,6 +5201,12 @@
         <v>0</v>
       </c>
       <c r="K116" t="n">
+        <v>0</v>
+      </c>
+      <c r="L116" t="n">
+        <v>0</v>
+      </c>
+      <c r="M116" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -4542,6 +5242,12 @@
         <v>1</v>
       </c>
       <c r="K117" t="n">
+        <v>0</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0</v>
+      </c>
+      <c r="M117" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -4577,6 +5283,12 @@
         <v>1</v>
       </c>
       <c r="K118" t="n">
+        <v>1</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0</v>
+      </c>
+      <c r="M118" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -4612,6 +5324,12 @@
         <v>6</v>
       </c>
       <c r="K119" t="n">
+        <v>3</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0</v>
+      </c>
+      <c r="M119" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -4647,6 +5365,12 @@
         <v>0</v>
       </c>
       <c r="K120" t="n">
+        <v>1</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0</v>
+      </c>
+      <c r="M120" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -4682,6 +5406,12 @@
         <v>6</v>
       </c>
       <c r="K121" t="n">
+        <v>4</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0</v>
+      </c>
+      <c r="M121" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -4717,6 +5447,12 @@
         <v>1</v>
       </c>
       <c r="K122" t="n">
+        <v>4</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0</v>
+      </c>
+      <c r="M122" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -4752,6 +5488,12 @@
         <v>5</v>
       </c>
       <c r="K123" t="n">
+        <v>8</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0</v>
+      </c>
+      <c r="M123" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -4787,6 +5529,12 @@
         <v>2</v>
       </c>
       <c r="K124" t="n">
+        <v>3</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0</v>
+      </c>
+      <c r="M124" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -4822,6 +5570,12 @@
         <v>0</v>
       </c>
       <c r="K125" t="n">
+        <v>0</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0</v>
+      </c>
+      <c r="M125" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -4857,6 +5611,12 @@
         <v>0</v>
       </c>
       <c r="K126" t="n">
+        <v>0</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0</v>
+      </c>
+      <c r="M126" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -4892,6 +5652,12 @@
         <v>0</v>
       </c>
       <c r="K127" t="n">
+        <v>0</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0</v>
+      </c>
+      <c r="M127" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -4927,6 +5693,12 @@
         <v>0</v>
       </c>
       <c r="K128" t="n">
+        <v>0</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0</v>
+      </c>
+      <c r="M128" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -4962,6 +5734,12 @@
         <v>2</v>
       </c>
       <c r="K129" t="n">
+        <v>2</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0</v>
+      </c>
+      <c r="M129" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -4997,6 +5775,12 @@
         <v>1</v>
       </c>
       <c r="K130" t="n">
+        <v>6</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0</v>
+      </c>
+      <c r="M130" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -5032,6 +5816,12 @@
         <v>6</v>
       </c>
       <c r="K131" t="n">
+        <v>5</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0</v>
+      </c>
+      <c r="M131" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -5067,6 +5857,12 @@
         <v>2</v>
       </c>
       <c r="K132" t="n">
+        <v>1</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0</v>
+      </c>
+      <c r="M132" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -5102,6 +5898,12 @@
         <v>0</v>
       </c>
       <c r="K133" t="n">
+        <v>2</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0</v>
+      </c>
+      <c r="M133" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -5137,6 +5939,12 @@
         <v>0</v>
       </c>
       <c r="K134" t="n">
+        <v>3</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0</v>
+      </c>
+      <c r="M134" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -5172,6 +5980,12 @@
         <v>2</v>
       </c>
       <c r="K135" t="n">
+        <v>1</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0</v>
+      </c>
+      <c r="M135" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -5207,6 +6021,12 @@
         <v>1</v>
       </c>
       <c r="K136" t="n">
+        <v>1</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0</v>
+      </c>
+      <c r="M136" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -5242,6 +6062,12 @@
         <v>1</v>
       </c>
       <c r="K137" t="n">
+        <v>11</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0</v>
+      </c>
+      <c r="M137" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -5277,6 +6103,12 @@
         <v>2</v>
       </c>
       <c r="K138" t="n">
+        <v>1</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0</v>
+      </c>
+      <c r="M138" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -5312,6 +6144,12 @@
         <v>4</v>
       </c>
       <c r="K139" t="n">
+        <v>3</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0</v>
+      </c>
+      <c r="M139" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -5347,6 +6185,12 @@
         <v>1</v>
       </c>
       <c r="K140" t="n">
+        <v>0</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0</v>
+      </c>
+      <c r="M140" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -5382,6 +6226,12 @@
         <v>1</v>
       </c>
       <c r="K141" t="n">
+        <v>3</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0</v>
+      </c>
+      <c r="M141" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -5417,6 +6267,12 @@
         <v>0</v>
       </c>
       <c r="K142" t="n">
+        <v>2</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0</v>
+      </c>
+      <c r="M142" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -5452,6 +6308,12 @@
         <v>3</v>
       </c>
       <c r="K143" t="n">
+        <v>1</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0</v>
+      </c>
+      <c r="M143" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -5487,6 +6349,12 @@
         <v>0</v>
       </c>
       <c r="K144" t="n">
+        <v>0</v>
+      </c>
+      <c r="L144" t="n">
+        <v>0</v>
+      </c>
+      <c r="M144" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -5522,6 +6390,12 @@
         <v>1</v>
       </c>
       <c r="K145" t="n">
+        <v>0</v>
+      </c>
+      <c r="L145" t="n">
+        <v>0</v>
+      </c>
+      <c r="M145" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -5557,6 +6431,12 @@
         <v>2</v>
       </c>
       <c r="K146" t="n">
+        <v>2</v>
+      </c>
+      <c r="L146" t="n">
+        <v>0</v>
+      </c>
+      <c r="M146" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -5592,6 +6472,12 @@
         <v>0</v>
       </c>
       <c r="K147" t="n">
+        <v>1</v>
+      </c>
+      <c r="L147" t="n">
+        <v>0</v>
+      </c>
+      <c r="M147" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -5627,6 +6513,12 @@
         <v>2</v>
       </c>
       <c r="K148" t="n">
+        <v>0</v>
+      </c>
+      <c r="L148" t="n">
+        <v>0</v>
+      </c>
+      <c r="M148" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -5662,6 +6554,12 @@
         <v>1</v>
       </c>
       <c r="K149" t="n">
+        <v>0</v>
+      </c>
+      <c r="L149" t="n">
+        <v>0</v>
+      </c>
+      <c r="M149" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -5697,6 +6595,12 @@
         <v>12</v>
       </c>
       <c r="K150" t="n">
+        <v>13</v>
+      </c>
+      <c r="L150" t="n">
+        <v>0</v>
+      </c>
+      <c r="M150" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -5732,6 +6636,12 @@
         <v>5</v>
       </c>
       <c r="K151" t="n">
+        <v>7</v>
+      </c>
+      <c r="L151" t="n">
+        <v>0</v>
+      </c>
+      <c r="M151" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -5767,6 +6677,12 @@
         <v>3</v>
       </c>
       <c r="K152" t="n">
+        <v>0</v>
+      </c>
+      <c r="L152" t="n">
+        <v>0</v>
+      </c>
+      <c r="M152" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -5802,6 +6718,12 @@
         <v>1</v>
       </c>
       <c r="K153" t="n">
+        <v>3</v>
+      </c>
+      <c r="L153" t="n">
+        <v>0</v>
+      </c>
+      <c r="M153" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -5837,6 +6759,12 @@
         <v>7</v>
       </c>
       <c r="K154" t="n">
+        <v>4</v>
+      </c>
+      <c r="L154" t="n">
+        <v>0</v>
+      </c>
+      <c r="M154" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -5872,6 +6800,12 @@
         <v>11</v>
       </c>
       <c r="K155" t="n">
+        <v>19</v>
+      </c>
+      <c r="L155" t="n">
+        <v>0</v>
+      </c>
+      <c r="M155" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -5907,6 +6841,12 @@
         <v>0</v>
       </c>
       <c r="K156" t="n">
+        <v>1</v>
+      </c>
+      <c r="L156" t="n">
+        <v>0</v>
+      </c>
+      <c r="M156" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -5942,6 +6882,12 @@
         <v>1</v>
       </c>
       <c r="K157" t="n">
+        <v>3</v>
+      </c>
+      <c r="L157" t="n">
+        <v>0</v>
+      </c>
+      <c r="M157" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -5977,6 +6923,12 @@
         <v>1</v>
       </c>
       <c r="K158" t="n">
+        <v>2</v>
+      </c>
+      <c r="L158" t="n">
+        <v>0</v>
+      </c>
+      <c r="M158" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -6012,6 +6964,12 @@
         <v>0</v>
       </c>
       <c r="K159" t="n">
+        <v>6</v>
+      </c>
+      <c r="L159" t="n">
+        <v>0</v>
+      </c>
+      <c r="M159" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -6047,6 +7005,12 @@
         <v>3</v>
       </c>
       <c r="K160" t="n">
+        <v>1</v>
+      </c>
+      <c r="L160" t="n">
+        <v>0</v>
+      </c>
+      <c r="M160" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -6082,6 +7046,12 @@
         <v>1</v>
       </c>
       <c r="K161" t="n">
+        <v>2</v>
+      </c>
+      <c r="L161" t="n">
+        <v>0</v>
+      </c>
+      <c r="M161" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -6117,6 +7087,12 @@
         <v>0</v>
       </c>
       <c r="K162" t="n">
+        <v>1</v>
+      </c>
+      <c r="L162" t="n">
+        <v>0</v>
+      </c>
+      <c r="M162" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -6152,6 +7128,12 @@
         <v>0</v>
       </c>
       <c r="K163" t="n">
+        <v>1</v>
+      </c>
+      <c r="L163" t="n">
+        <v>0</v>
+      </c>
+      <c r="M163" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -6187,6 +7169,12 @@
         <v>17</v>
       </c>
       <c r="K164" t="n">
+        <v>8</v>
+      </c>
+      <c r="L164" t="n">
+        <v>0</v>
+      </c>
+      <c r="M164" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -6222,6 +7210,12 @@
         <v>17</v>
       </c>
       <c r="K165" t="n">
+        <v>10</v>
+      </c>
+      <c r="L165" t="n">
+        <v>0</v>
+      </c>
+      <c r="M165" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -6257,6 +7251,12 @@
         <v>1</v>
       </c>
       <c r="K166" t="n">
+        <v>4</v>
+      </c>
+      <c r="L166" t="n">
+        <v>0</v>
+      </c>
+      <c r="M166" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -6292,6 +7292,12 @@
         <v>2</v>
       </c>
       <c r="K167" t="n">
+        <v>1</v>
+      </c>
+      <c r="L167" t="n">
+        <v>0</v>
+      </c>
+      <c r="M167" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -6327,6 +7333,12 @@
         <v>3</v>
       </c>
       <c r="K168" t="n">
+        <v>4</v>
+      </c>
+      <c r="L168" t="n">
+        <v>0</v>
+      </c>
+      <c r="M168" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -6362,6 +7374,12 @@
         <v>1</v>
       </c>
       <c r="K169" t="n">
+        <v>3</v>
+      </c>
+      <c r="L169" t="n">
+        <v>0</v>
+      </c>
+      <c r="M169" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -6397,6 +7415,12 @@
         <v>3</v>
       </c>
       <c r="K170" t="n">
+        <v>0</v>
+      </c>
+      <c r="L170" t="n">
+        <v>0</v>
+      </c>
+      <c r="M170" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -6432,6 +7456,12 @@
         <v>15</v>
       </c>
       <c r="K171" t="n">
+        <v>23</v>
+      </c>
+      <c r="L171" t="n">
+        <v>0</v>
+      </c>
+      <c r="M171" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -6467,6 +7497,12 @@
         <v>0</v>
       </c>
       <c r="K172" t="n">
+        <v>3</v>
+      </c>
+      <c r="L172" t="n">
+        <v>0</v>
+      </c>
+      <c r="M172" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -6502,6 +7538,12 @@
         <v>0</v>
       </c>
       <c r="K173" t="n">
+        <v>5</v>
+      </c>
+      <c r="L173" t="n">
+        <v>0</v>
+      </c>
+      <c r="M173" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -6537,6 +7579,12 @@
         <v>2</v>
       </c>
       <c r="K174" t="n">
+        <v>0</v>
+      </c>
+      <c r="L174" t="n">
+        <v>0</v>
+      </c>
+      <c r="M174" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -6572,6 +7620,12 @@
         <v>2</v>
       </c>
       <c r="K175" t="n">
+        <v>5</v>
+      </c>
+      <c r="L175" t="n">
+        <v>0</v>
+      </c>
+      <c r="M175" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -6607,6 +7661,12 @@
         <v>0</v>
       </c>
       <c r="K176" t="n">
+        <v>3</v>
+      </c>
+      <c r="L176" t="n">
+        <v>0</v>
+      </c>
+      <c r="M176" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -6642,6 +7702,12 @@
         <v>1</v>
       </c>
       <c r="K177" t="n">
+        <v>0</v>
+      </c>
+      <c r="L177" t="n">
+        <v>0</v>
+      </c>
+      <c r="M177" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -6677,6 +7743,12 @@
         <v>2</v>
       </c>
       <c r="K178" t="n">
+        <v>1</v>
+      </c>
+      <c r="L178" t="n">
+        <v>0</v>
+      </c>
+      <c r="M178" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -6712,6 +7784,12 @@
         <v>1</v>
       </c>
       <c r="K179" t="n">
+        <v>2</v>
+      </c>
+      <c r="L179" t="n">
+        <v>0</v>
+      </c>
+      <c r="M179" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -6747,6 +7825,12 @@
         <v>1</v>
       </c>
       <c r="K180" t="n">
+        <v>2</v>
+      </c>
+      <c r="L180" t="n">
+        <v>0</v>
+      </c>
+      <c r="M180" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -6782,6 +7866,12 @@
         <v>16</v>
       </c>
       <c r="K181" t="n">
+        <v>1</v>
+      </c>
+      <c r="L181" t="n">
+        <v>0</v>
+      </c>
+      <c r="M181" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -6817,6 +7907,12 @@
         <v>9</v>
       </c>
       <c r="K182" t="n">
+        <v>8</v>
+      </c>
+      <c r="L182" t="n">
+        <v>0</v>
+      </c>
+      <c r="M182" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -6852,6 +7948,12 @@
         <v>7</v>
       </c>
       <c r="K183" t="n">
+        <v>8</v>
+      </c>
+      <c r="L183" t="n">
+        <v>0</v>
+      </c>
+      <c r="M183" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -6887,6 +7989,12 @@
         <v>8</v>
       </c>
       <c r="K184" t="n">
+        <v>9</v>
+      </c>
+      <c r="L184" t="n">
+        <v>0</v>
+      </c>
+      <c r="M184" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -6922,6 +8030,12 @@
         <v>1</v>
       </c>
       <c r="K185" t="n">
+        <v>2</v>
+      </c>
+      <c r="L185" t="n">
+        <v>0</v>
+      </c>
+      <c r="M185" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -6957,6 +8071,12 @@
         <v>0</v>
       </c>
       <c r="K186" t="n">
+        <v>0</v>
+      </c>
+      <c r="L186" t="n">
+        <v>0</v>
+      </c>
+      <c r="M186" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -6992,6 +8112,12 @@
         <v>0</v>
       </c>
       <c r="K187" t="n">
+        <v>0</v>
+      </c>
+      <c r="L187" t="n">
+        <v>0</v>
+      </c>
+      <c r="M187" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -7027,6 +8153,12 @@
         <v>1</v>
       </c>
       <c r="K188" t="n">
+        <v>0</v>
+      </c>
+      <c r="L188" t="n">
+        <v>0</v>
+      </c>
+      <c r="M188" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -7062,6 +8194,12 @@
         <v>1</v>
       </c>
       <c r="K189" t="n">
+        <v>0</v>
+      </c>
+      <c r="L189" t="n">
+        <v>0</v>
+      </c>
+      <c r="M189" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -7097,6 +8235,12 @@
         <v>1</v>
       </c>
       <c r="K190" t="n">
+        <v>1</v>
+      </c>
+      <c r="L190" t="n">
+        <v>0</v>
+      </c>
+      <c r="M190" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -7132,6 +8276,12 @@
         <v>0</v>
       </c>
       <c r="K191" t="n">
+        <v>2</v>
+      </c>
+      <c r="L191" t="n">
+        <v>0</v>
+      </c>
+      <c r="M191" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -7167,6 +8317,12 @@
         <v>0</v>
       </c>
       <c r="K192" t="n">
+        <v>5</v>
+      </c>
+      <c r="L192" t="n">
+        <v>0</v>
+      </c>
+      <c r="M192" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -7202,6 +8358,12 @@
         <v>2</v>
       </c>
       <c r="K193" t="n">
+        <v>3</v>
+      </c>
+      <c r="L193" t="n">
+        <v>0</v>
+      </c>
+      <c r="M193" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -7237,6 +8399,12 @@
         <v>9</v>
       </c>
       <c r="K194" t="n">
+        <v>7</v>
+      </c>
+      <c r="L194" t="n">
+        <v>0</v>
+      </c>
+      <c r="M194" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -7272,6 +8440,12 @@
         <v>1</v>
       </c>
       <c r="K195" t="n">
+        <v>0</v>
+      </c>
+      <c r="L195" t="n">
+        <v>0</v>
+      </c>
+      <c r="M195" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -7307,6 +8481,12 @@
         <v>1</v>
       </c>
       <c r="K196" t="n">
+        <v>0</v>
+      </c>
+      <c r="L196" t="n">
+        <v>0</v>
+      </c>
+      <c r="M196" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -7342,6 +8522,12 @@
         <v>1</v>
       </c>
       <c r="K197" t="n">
+        <v>0</v>
+      </c>
+      <c r="L197" t="n">
+        <v>0</v>
+      </c>
+      <c r="M197" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -7377,6 +8563,12 @@
         <v>0</v>
       </c>
       <c r="K198" t="n">
+        <v>5</v>
+      </c>
+      <c r="L198" t="n">
+        <v>0</v>
+      </c>
+      <c r="M198" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -7412,6 +8604,12 @@
         <v>0</v>
       </c>
       <c r="K199" t="n">
+        <v>0</v>
+      </c>
+      <c r="L199" t="n">
+        <v>0</v>
+      </c>
+      <c r="M199" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -7447,6 +8645,12 @@
         <v>3</v>
       </c>
       <c r="K200" t="n">
+        <v>4</v>
+      </c>
+      <c r="L200" t="n">
+        <v>0</v>
+      </c>
+      <c r="M200" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -7482,6 +8686,12 @@
         <v>2</v>
       </c>
       <c r="K201" t="n">
+        <v>6</v>
+      </c>
+      <c r="L201" t="n">
+        <v>0</v>
+      </c>
+      <c r="M201" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -7517,6 +8727,12 @@
         <v>1</v>
       </c>
       <c r="K202" t="n">
+        <v>4</v>
+      </c>
+      <c r="L202" t="n">
+        <v>0</v>
+      </c>
+      <c r="M202" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -7552,6 +8768,12 @@
         <v>2</v>
       </c>
       <c r="K203" t="n">
+        <v>2</v>
+      </c>
+      <c r="L203" t="n">
+        <v>0</v>
+      </c>
+      <c r="M203" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -7587,6 +8809,12 @@
         <v>3</v>
       </c>
       <c r="K204" t="n">
+        <v>5</v>
+      </c>
+      <c r="L204" t="n">
+        <v>0</v>
+      </c>
+      <c r="M204" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -7622,6 +8850,12 @@
         <v>3</v>
       </c>
       <c r="K205" t="n">
+        <v>1</v>
+      </c>
+      <c r="L205" t="n">
+        <v>0</v>
+      </c>
+      <c r="M205" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -7657,6 +8891,12 @@
         <v>1</v>
       </c>
       <c r="K206" t="n">
+        <v>1</v>
+      </c>
+      <c r="L206" t="n">
+        <v>0</v>
+      </c>
+      <c r="M206" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -7692,6 +8932,12 @@
         <v>12</v>
       </c>
       <c r="K207" t="n">
+        <v>5</v>
+      </c>
+      <c r="L207" t="n">
+        <v>0</v>
+      </c>
+      <c r="M207" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -7727,6 +8973,12 @@
         <v>5</v>
       </c>
       <c r="K208" t="n">
+        <v>8</v>
+      </c>
+      <c r="L208" t="n">
+        <v>0</v>
+      </c>
+      <c r="M208" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -7762,6 +9014,12 @@
         <v>6</v>
       </c>
       <c r="K209" t="n">
+        <v>1</v>
+      </c>
+      <c r="L209" t="n">
+        <v>0</v>
+      </c>
+      <c r="M209" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -7797,6 +9055,12 @@
         <v>2</v>
       </c>
       <c r="K210" t="n">
+        <v>1</v>
+      </c>
+      <c r="L210" t="n">
+        <v>0</v>
+      </c>
+      <c r="M210" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -7832,6 +9096,12 @@
         <v>0</v>
       </c>
       <c r="K211" t="n">
+        <v>0</v>
+      </c>
+      <c r="L211" t="n">
+        <v>0</v>
+      </c>
+      <c r="M211" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -7867,6 +9137,12 @@
         <v>2</v>
       </c>
       <c r="K212" t="n">
+        <v>0</v>
+      </c>
+      <c r="L212" t="n">
+        <v>0</v>
+      </c>
+      <c r="M212" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -7902,6 +9178,12 @@
         <v>3</v>
       </c>
       <c r="K213" t="n">
+        <v>3</v>
+      </c>
+      <c r="L213" t="n">
+        <v>0</v>
+      </c>
+      <c r="M213" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -7937,6 +9219,12 @@
         <v>1</v>
       </c>
       <c r="K214" t="n">
+        <v>2</v>
+      </c>
+      <c r="L214" t="n">
+        <v>0</v>
+      </c>
+      <c r="M214" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -7972,6 +9260,12 @@
         <v>0</v>
       </c>
       <c r="K215" t="n">
+        <v>1</v>
+      </c>
+      <c r="L215" t="n">
+        <v>0</v>
+      </c>
+      <c r="M215" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -8007,6 +9301,12 @@
         <v>0</v>
       </c>
       <c r="K216" t="n">
+        <v>6</v>
+      </c>
+      <c r="L216" t="n">
+        <v>0</v>
+      </c>
+      <c r="M216" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -8042,6 +9342,12 @@
         <v>1</v>
       </c>
       <c r="K217" t="n">
+        <v>0</v>
+      </c>
+      <c r="L217" t="n">
+        <v>0</v>
+      </c>
+      <c r="M217" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -8077,6 +9383,12 @@
         <v>4</v>
       </c>
       <c r="K218" t="n">
+        <v>2</v>
+      </c>
+      <c r="L218" t="n">
+        <v>0</v>
+      </c>
+      <c r="M218" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -8112,6 +9424,12 @@
         <v>1</v>
       </c>
       <c r="K219" t="n">
+        <v>0</v>
+      </c>
+      <c r="L219" t="n">
+        <v>0</v>
+      </c>
+      <c r="M219" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -8147,6 +9465,12 @@
         <v>2</v>
       </c>
       <c r="K220" t="n">
+        <v>2</v>
+      </c>
+      <c r="L220" t="n">
+        <v>0</v>
+      </c>
+      <c r="M220" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -8182,6 +9506,12 @@
         <v>3</v>
       </c>
       <c r="K221" t="n">
+        <v>1</v>
+      </c>
+      <c r="L221" t="n">
+        <v>0</v>
+      </c>
+      <c r="M221" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -8217,6 +9547,12 @@
         <v>3</v>
       </c>
       <c r="K222" t="n">
+        <v>2</v>
+      </c>
+      <c r="L222" t="n">
+        <v>0</v>
+      </c>
+      <c r="M222" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -8252,6 +9588,12 @@
         <v>13</v>
       </c>
       <c r="K223" t="n">
+        <v>9</v>
+      </c>
+      <c r="L223" t="n">
+        <v>0</v>
+      </c>
+      <c r="M223" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -8287,6 +9629,12 @@
         <v>1</v>
       </c>
       <c r="K224" t="n">
+        <v>0</v>
+      </c>
+      <c r="L224" t="n">
+        <v>0</v>
+      </c>
+      <c r="M224" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -8322,6 +9670,12 @@
         <v>0</v>
       </c>
       <c r="K225" t="n">
+        <v>2</v>
+      </c>
+      <c r="L225" t="n">
+        <v>0</v>
+      </c>
+      <c r="M225" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -8357,6 +9711,12 @@
         <v>1</v>
       </c>
       <c r="K226" t="n">
+        <v>0</v>
+      </c>
+      <c r="L226" t="n">
+        <v>0</v>
+      </c>
+      <c r="M226" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -8392,6 +9752,12 @@
         <v>1</v>
       </c>
       <c r="K227" t="n">
+        <v>1</v>
+      </c>
+      <c r="L227" t="n">
+        <v>0</v>
+      </c>
+      <c r="M227" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -8427,6 +9793,12 @@
         <v>0</v>
       </c>
       <c r="K228" t="n">
+        <v>1</v>
+      </c>
+      <c r="L228" t="n">
+        <v>0</v>
+      </c>
+      <c r="M228" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -8462,6 +9834,12 @@
         <v>4</v>
       </c>
       <c r="K229" t="n">
+        <v>1</v>
+      </c>
+      <c r="L229" t="n">
+        <v>0</v>
+      </c>
+      <c r="M229" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -8497,6 +9875,12 @@
         <v>2</v>
       </c>
       <c r="K230" t="n">
+        <v>2</v>
+      </c>
+      <c r="L230" t="n">
+        <v>0</v>
+      </c>
+      <c r="M230" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -8532,6 +9916,12 @@
         <v>0</v>
       </c>
       <c r="K231" t="n">
+        <v>1</v>
+      </c>
+      <c r="L231" t="n">
+        <v>0</v>
+      </c>
+      <c r="M231" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -8567,6 +9957,12 @@
         <v>3</v>
       </c>
       <c r="K232" t="n">
+        <v>1</v>
+      </c>
+      <c r="L232" t="n">
+        <v>0</v>
+      </c>
+      <c r="M232" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -8602,6 +9998,12 @@
         <v>2</v>
       </c>
       <c r="K233" t="n">
+        <v>2</v>
+      </c>
+      <c r="L233" t="n">
+        <v>0</v>
+      </c>
+      <c r="M233" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -8637,6 +10039,12 @@
         <v>7</v>
       </c>
       <c r="K234" t="n">
+        <v>9</v>
+      </c>
+      <c r="L234" t="n">
+        <v>0</v>
+      </c>
+      <c r="M234" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -8672,6 +10080,12 @@
         <v>8</v>
       </c>
       <c r="K235" t="n">
+        <v>10</v>
+      </c>
+      <c r="L235" t="n">
+        <v>0</v>
+      </c>
+      <c r="M235" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -8707,6 +10121,12 @@
         <v>19</v>
       </c>
       <c r="K236" t="n">
+        <v>11</v>
+      </c>
+      <c r="L236" t="n">
+        <v>0</v>
+      </c>
+      <c r="M236" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -8742,6 +10162,12 @@
         <v>12</v>
       </c>
       <c r="K237" t="n">
+        <v>11</v>
+      </c>
+      <c r="L237" t="n">
+        <v>0</v>
+      </c>
+      <c r="M237" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -8777,6 +10203,12 @@
         <v>0</v>
       </c>
       <c r="K238" t="n">
+        <v>0</v>
+      </c>
+      <c r="L238" t="n">
+        <v>0</v>
+      </c>
+      <c r="M238" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -8812,6 +10244,12 @@
         <v>0</v>
       </c>
       <c r="K239" t="n">
+        <v>1</v>
+      </c>
+      <c r="L239" t="n">
+        <v>0</v>
+      </c>
+      <c r="M239" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -8847,6 +10285,12 @@
         <v>3</v>
       </c>
       <c r="K240" t="n">
+        <v>5</v>
+      </c>
+      <c r="L240" t="n">
+        <v>0</v>
+      </c>
+      <c r="M240" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -8882,6 +10326,12 @@
         <v>3</v>
       </c>
       <c r="K241" t="n">
+        <v>0</v>
+      </c>
+      <c r="L241" t="n">
+        <v>0</v>
+      </c>
+      <c r="M241" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -8917,6 +10367,12 @@
         <v>0</v>
       </c>
       <c r="K242" t="n">
+        <v>2</v>
+      </c>
+      <c r="L242" t="n">
+        <v>0</v>
+      </c>
+      <c r="M242" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -8952,6 +10408,12 @@
         <v>0</v>
       </c>
       <c r="K243" t="n">
+        <v>6</v>
+      </c>
+      <c r="L243" t="n">
+        <v>0</v>
+      </c>
+      <c r="M243" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -8987,6 +10449,12 @@
         <v>7</v>
       </c>
       <c r="K244" t="n">
+        <v>7</v>
+      </c>
+      <c r="L244" t="n">
+        <v>0</v>
+      </c>
+      <c r="M244" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -9022,6 +10490,12 @@
         <v>0</v>
       </c>
       <c r="K245" t="n">
+        <v>6</v>
+      </c>
+      <c r="L245" t="n">
+        <v>0</v>
+      </c>
+      <c r="M245" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -9057,6 +10531,12 @@
         <v>4</v>
       </c>
       <c r="K246" t="n">
+        <v>5</v>
+      </c>
+      <c r="L246" t="n">
+        <v>0</v>
+      </c>
+      <c r="M246" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -9092,6 +10572,12 @@
         <v>4</v>
       </c>
       <c r="K247" t="n">
+        <v>8</v>
+      </c>
+      <c r="L247" t="n">
+        <v>0</v>
+      </c>
+      <c r="M247" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -9127,6 +10613,12 @@
         <v>5</v>
       </c>
       <c r="K248" t="n">
+        <v>5</v>
+      </c>
+      <c r="L248" t="n">
+        <v>0</v>
+      </c>
+      <c r="M248" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -9162,6 +10654,12 @@
         <v>1</v>
       </c>
       <c r="K249" t="n">
+        <v>2</v>
+      </c>
+      <c r="L249" t="n">
+        <v>0</v>
+      </c>
+      <c r="M249" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -9197,6 +10695,12 @@
         <v>1</v>
       </c>
       <c r="K250" t="n">
+        <v>1</v>
+      </c>
+      <c r="L250" t="n">
+        <v>0</v>
+      </c>
+      <c r="M250" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -9232,6 +10736,12 @@
         <v>0</v>
       </c>
       <c r="K251" t="n">
+        <v>5</v>
+      </c>
+      <c r="L251" t="n">
+        <v>0</v>
+      </c>
+      <c r="M251" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -9267,6 +10777,12 @@
         <v>2</v>
       </c>
       <c r="K252" t="n">
+        <v>5</v>
+      </c>
+      <c r="L252" t="n">
+        <v>0</v>
+      </c>
+      <c r="M252" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -9302,6 +10818,12 @@
         <v>9</v>
       </c>
       <c r="K253" t="n">
+        <v>13</v>
+      </c>
+      <c r="L253" t="n">
+        <v>0</v>
+      </c>
+      <c r="M253" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -9337,6 +10859,12 @@
         <v>5</v>
       </c>
       <c r="K254" t="n">
+        <v>5</v>
+      </c>
+      <c r="L254" t="n">
+        <v>0</v>
+      </c>
+      <c r="M254" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -9372,6 +10900,12 @@
         <v>2</v>
       </c>
       <c r="K255" t="n">
+        <v>6</v>
+      </c>
+      <c r="L255" t="n">
+        <v>0</v>
+      </c>
+      <c r="M255" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -9407,6 +10941,12 @@
         <v>1</v>
       </c>
       <c r="K256" t="n">
+        <v>2</v>
+      </c>
+      <c r="L256" t="n">
+        <v>0</v>
+      </c>
+      <c r="M256" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -9442,6 +10982,12 @@
         <v>7</v>
       </c>
       <c r="K257" t="n">
+        <v>0</v>
+      </c>
+      <c r="L257" t="n">
+        <v>0</v>
+      </c>
+      <c r="M257" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -9477,6 +11023,12 @@
         <v>3</v>
       </c>
       <c r="K258" t="n">
+        <v>0</v>
+      </c>
+      <c r="L258" t="n">
+        <v>0</v>
+      </c>
+      <c r="M258" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -9512,6 +11064,12 @@
         <v>7</v>
       </c>
       <c r="K259" t="n">
+        <v>0</v>
+      </c>
+      <c r="L259" t="n">
+        <v>0</v>
+      </c>
+      <c r="M259" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -9547,6 +11105,12 @@
         <v>6</v>
       </c>
       <c r="K260" t="n">
+        <v>1</v>
+      </c>
+      <c r="L260" t="n">
+        <v>0</v>
+      </c>
+      <c r="M260" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -9582,6 +11146,12 @@
         <v>0</v>
       </c>
       <c r="K261" t="n">
+        <v>1</v>
+      </c>
+      <c r="L261" t="n">
+        <v>0</v>
+      </c>
+      <c r="M261" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -9617,6 +11187,12 @@
         <v>7</v>
       </c>
       <c r="K262" t="n">
+        <v>2</v>
+      </c>
+      <c r="L262" t="n">
+        <v>0</v>
+      </c>
+      <c r="M262" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -9652,6 +11228,12 @@
         <v>3</v>
       </c>
       <c r="K263" t="n">
+        <v>4</v>
+      </c>
+      <c r="L263" t="n">
+        <v>0</v>
+      </c>
+      <c r="M263" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -9687,6 +11269,12 @@
         <v>3</v>
       </c>
       <c r="K264" t="n">
+        <v>1</v>
+      </c>
+      <c r="L264" t="n">
+        <v>0</v>
+      </c>
+      <c r="M264" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -9722,6 +11310,12 @@
         <v>3</v>
       </c>
       <c r="K265" t="n">
+        <v>0</v>
+      </c>
+      <c r="L265" t="n">
+        <v>0</v>
+      </c>
+      <c r="M265" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -9757,6 +11351,12 @@
         <v>4</v>
       </c>
       <c r="K266" t="n">
+        <v>2</v>
+      </c>
+      <c r="L266" t="n">
+        <v>0</v>
+      </c>
+      <c r="M266" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -9792,6 +11392,12 @@
         <v>1</v>
       </c>
       <c r="K267" t="n">
+        <v>0</v>
+      </c>
+      <c r="L267" t="n">
+        <v>0</v>
+      </c>
+      <c r="M267" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -9827,6 +11433,12 @@
         <v>0</v>
       </c>
       <c r="K268" t="n">
+        <v>0</v>
+      </c>
+      <c r="L268" t="n">
+        <v>0</v>
+      </c>
+      <c r="M268" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -9862,6 +11474,12 @@
         <v>2</v>
       </c>
       <c r="K269" t="n">
+        <v>2</v>
+      </c>
+      <c r="L269" t="n">
+        <v>0</v>
+      </c>
+      <c r="M269" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -9897,6 +11515,12 @@
         <v>0</v>
       </c>
       <c r="K270" t="n">
+        <v>0</v>
+      </c>
+      <c r="L270" t="n">
+        <v>0</v>
+      </c>
+      <c r="M270" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -9932,6 +11556,12 @@
         <v>0</v>
       </c>
       <c r="K271" t="n">
+        <v>0</v>
+      </c>
+      <c r="L271" t="n">
+        <v>0</v>
+      </c>
+      <c r="M271" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -9967,6 +11597,12 @@
         <v>2</v>
       </c>
       <c r="K272" t="n">
+        <v>0</v>
+      </c>
+      <c r="L272" t="n">
+        <v>0</v>
+      </c>
+      <c r="M272" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -10002,6 +11638,12 @@
         <v>2</v>
       </c>
       <c r="K273" t="n">
+        <v>4</v>
+      </c>
+      <c r="L273" t="n">
+        <v>0</v>
+      </c>
+      <c r="M273" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -10037,6 +11679,12 @@
         <v>4</v>
       </c>
       <c r="K274" t="n">
+        <v>1</v>
+      </c>
+      <c r="L274" t="n">
+        <v>0</v>
+      </c>
+      <c r="M274" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -10072,6 +11720,12 @@
         <v>0</v>
       </c>
       <c r="K275" t="n">
+        <v>5</v>
+      </c>
+      <c r="L275" t="n">
+        <v>0</v>
+      </c>
+      <c r="M275" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -10107,6 +11761,12 @@
         <v>0</v>
       </c>
       <c r="K276" t="n">
+        <v>2</v>
+      </c>
+      <c r="L276" t="n">
+        <v>0</v>
+      </c>
+      <c r="M276" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -10142,6 +11802,12 @@
         <v>0</v>
       </c>
       <c r="K277" t="n">
+        <v>5</v>
+      </c>
+      <c r="L277" t="n">
+        <v>0</v>
+      </c>
+      <c r="M277" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -10177,6 +11843,12 @@
         <v>3</v>
       </c>
       <c r="K278" t="n">
+        <v>1</v>
+      </c>
+      <c r="L278" t="n">
+        <v>0</v>
+      </c>
+      <c r="M278" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -10212,6 +11884,12 @@
         <v>1</v>
       </c>
       <c r="K279" t="n">
+        <v>0</v>
+      </c>
+      <c r="L279" t="n">
+        <v>0</v>
+      </c>
+      <c r="M279" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -10247,6 +11925,12 @@
         <v>0</v>
       </c>
       <c r="K280" t="n">
+        <v>2</v>
+      </c>
+      <c r="L280" t="n">
+        <v>0</v>
+      </c>
+      <c r="M280" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -10282,6 +11966,12 @@
         <v>0</v>
       </c>
       <c r="K281" t="n">
+        <v>3</v>
+      </c>
+      <c r="L281" t="n">
+        <v>0</v>
+      </c>
+      <c r="M281" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -10317,6 +12007,12 @@
         <v>7</v>
       </c>
       <c r="K282" t="n">
+        <v>4</v>
+      </c>
+      <c r="L282" t="n">
+        <v>0</v>
+      </c>
+      <c r="M282" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -10352,6 +12048,12 @@
         <v>6</v>
       </c>
       <c r="K283" t="n">
+        <v>2</v>
+      </c>
+      <c r="L283" t="n">
+        <v>0</v>
+      </c>
+      <c r="M283" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -10387,6 +12089,12 @@
         <v>4</v>
       </c>
       <c r="K284" t="n">
+        <v>15</v>
+      </c>
+      <c r="L284" t="n">
+        <v>0</v>
+      </c>
+      <c r="M284" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -10422,6 +12130,12 @@
         <v>0</v>
       </c>
       <c r="K285" t="n">
+        <v>11</v>
+      </c>
+      <c r="L285" t="n">
+        <v>0</v>
+      </c>
+      <c r="M285" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -10457,6 +12171,12 @@
         <v>1</v>
       </c>
       <c r="K286" t="n">
+        <v>9</v>
+      </c>
+      <c r="L286" t="n">
+        <v>0</v>
+      </c>
+      <c r="M286" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -10492,6 +12212,12 @@
         <v>2</v>
       </c>
       <c r="K287" t="n">
+        <v>1</v>
+      </c>
+      <c r="L287" t="n">
+        <v>0</v>
+      </c>
+      <c r="M287" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -10527,6 +12253,12 @@
         <v>3</v>
       </c>
       <c r="K288" t="n">
+        <v>6</v>
+      </c>
+      <c r="L288" t="n">
+        <v>0</v>
+      </c>
+      <c r="M288" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -10562,6 +12294,12 @@
         <v>0</v>
       </c>
       <c r="K289" t="n">
+        <v>0</v>
+      </c>
+      <c r="L289" t="n">
+        <v>0</v>
+      </c>
+      <c r="M289" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -10597,6 +12335,12 @@
         <v>2</v>
       </c>
       <c r="K290" t="n">
+        <v>0</v>
+      </c>
+      <c r="L290" t="n">
+        <v>0</v>
+      </c>
+      <c r="M290" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -10632,6 +12376,12 @@
         <v>0</v>
       </c>
       <c r="K291" t="n">
+        <v>0</v>
+      </c>
+      <c r="L291" t="n">
+        <v>0</v>
+      </c>
+      <c r="M291" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -10667,6 +12417,12 @@
         <v>2</v>
       </c>
       <c r="K292" t="n">
+        <v>3</v>
+      </c>
+      <c r="L292" t="n">
+        <v>0</v>
+      </c>
+      <c r="M292" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -10702,6 +12458,12 @@
         <v>2</v>
       </c>
       <c r="K293" t="n">
+        <v>2</v>
+      </c>
+      <c r="L293" t="n">
+        <v>0</v>
+      </c>
+      <c r="M293" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -10737,6 +12499,12 @@
         <v>0</v>
       </c>
       <c r="K294" t="n">
+        <v>0</v>
+      </c>
+      <c r="L294" t="n">
+        <v>0</v>
+      </c>
+      <c r="M294" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -10772,6 +12540,12 @@
         <v>0</v>
       </c>
       <c r="K295" t="n">
+        <v>0</v>
+      </c>
+      <c r="L295" t="n">
+        <v>0</v>
+      </c>
+      <c r="M295" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -10807,6 +12581,12 @@
         <v>2</v>
       </c>
       <c r="K296" t="n">
+        <v>4</v>
+      </c>
+      <c r="L296" t="n">
+        <v>0</v>
+      </c>
+      <c r="M296" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -10842,6 +12622,12 @@
         <v>1</v>
       </c>
       <c r="K297" t="n">
+        <v>3</v>
+      </c>
+      <c r="L297" t="n">
+        <v>1</v>
+      </c>
+      <c r="M297" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -10877,6 +12663,12 @@
         <v>0</v>
       </c>
       <c r="K298" t="n">
+        <v>0</v>
+      </c>
+      <c r="L298" t="n">
+        <v>0</v>
+      </c>
+      <c r="M298" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -10912,6 +12704,12 @@
         <v>0</v>
       </c>
       <c r="K299" t="n">
+        <v>0</v>
+      </c>
+      <c r="L299" t="n">
+        <v>0</v>
+      </c>
+      <c r="M299" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -10947,6 +12745,12 @@
         <v>2</v>
       </c>
       <c r="K300" t="n">
+        <v>2</v>
+      </c>
+      <c r="L300" t="n">
+        <v>0</v>
+      </c>
+      <c r="M300" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -10982,6 +12786,12 @@
         <v>1</v>
       </c>
       <c r="K301" t="n">
+        <v>0</v>
+      </c>
+      <c r="L301" t="n">
+        <v>0</v>
+      </c>
+      <c r="M301" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -11017,6 +12827,12 @@
         <v>2</v>
       </c>
       <c r="K302" t="n">
+        <v>9</v>
+      </c>
+      <c r="L302" t="n">
+        <v>0</v>
+      </c>
+      <c r="M302" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -11052,6 +12868,12 @@
         <v>5</v>
       </c>
       <c r="K303" t="n">
+        <v>2</v>
+      </c>
+      <c r="L303" t="n">
+        <v>0</v>
+      </c>
+      <c r="M303" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -11087,6 +12909,12 @@
         <v>3</v>
       </c>
       <c r="K304" t="n">
+        <v>3</v>
+      </c>
+      <c r="L304" t="n">
+        <v>0</v>
+      </c>
+      <c r="M304" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -11122,6 +12950,12 @@
         <v>2</v>
       </c>
       <c r="K305" t="n">
+        <v>0</v>
+      </c>
+      <c r="L305" t="n">
+        <v>0</v>
+      </c>
+      <c r="M305" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -11157,6 +12991,12 @@
         <v>4</v>
       </c>
       <c r="K306" t="n">
+        <v>7</v>
+      </c>
+      <c r="L306" t="n">
+        <v>0</v>
+      </c>
+      <c r="M306" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -11192,6 +13032,12 @@
         <v>1</v>
       </c>
       <c r="K307" t="n">
+        <v>8</v>
+      </c>
+      <c r="L307" t="n">
+        <v>0</v>
+      </c>
+      <c r="M307" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -11227,6 +13073,12 @@
         <v>1</v>
       </c>
       <c r="K308" t="n">
+        <v>3</v>
+      </c>
+      <c r="L308" t="n">
+        <v>0</v>
+      </c>
+      <c r="M308" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -11262,6 +13114,12 @@
         <v>1</v>
       </c>
       <c r="K309" t="n">
+        <v>3</v>
+      </c>
+      <c r="L309" t="n">
+        <v>0</v>
+      </c>
+      <c r="M309" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -11297,6 +13155,12 @@
         <v>3</v>
       </c>
       <c r="K310" t="n">
+        <v>3</v>
+      </c>
+      <c r="L310" t="n">
+        <v>0</v>
+      </c>
+      <c r="M310" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -11332,6 +13196,12 @@
         <v>2</v>
       </c>
       <c r="K311" t="n">
+        <v>2</v>
+      </c>
+      <c r="L311" t="n">
+        <v>0</v>
+      </c>
+      <c r="M311" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -11367,6 +13237,12 @@
         <v>7</v>
       </c>
       <c r="K312" t="n">
+        <v>5</v>
+      </c>
+      <c r="L312" t="n">
+        <v>0</v>
+      </c>
+      <c r="M312" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -11402,6 +13278,12 @@
         <v>2</v>
       </c>
       <c r="K313" t="n">
+        <v>1</v>
+      </c>
+      <c r="L313" t="n">
+        <v>0</v>
+      </c>
+      <c r="M313" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -11437,6 +13319,12 @@
         <v>6</v>
       </c>
       <c r="K314" t="n">
+        <v>5</v>
+      </c>
+      <c r="L314" t="n">
+        <v>0</v>
+      </c>
+      <c r="M314" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -11472,6 +13360,12 @@
         <v>3</v>
       </c>
       <c r="K315" t="n">
+        <v>10</v>
+      </c>
+      <c r="L315" t="n">
+        <v>0</v>
+      </c>
+      <c r="M315" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -11507,6 +13401,12 @@
         <v>0</v>
       </c>
       <c r="K316" t="n">
+        <v>5</v>
+      </c>
+      <c r="L316" t="n">
+        <v>0</v>
+      </c>
+      <c r="M316" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -11542,6 +13442,12 @@
         <v>24</v>
       </c>
       <c r="K317" t="n">
+        <v>0</v>
+      </c>
+      <c r="L317" t="n">
+        <v>0</v>
+      </c>
+      <c r="M317" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -11577,6 +13483,12 @@
         <v>1</v>
       </c>
       <c r="K318" t="n">
+        <v>0</v>
+      </c>
+      <c r="L318" t="n">
+        <v>0</v>
+      </c>
+      <c r="M318" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -11612,6 +13524,12 @@
         <v>2</v>
       </c>
       <c r="K319" t="n">
+        <v>0</v>
+      </c>
+      <c r="L319" t="n">
+        <v>0</v>
+      </c>
+      <c r="M319" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -11647,6 +13565,12 @@
         <v>0</v>
       </c>
       <c r="K320" t="n">
+        <v>0</v>
+      </c>
+      <c r="L320" t="n">
+        <v>0</v>
+      </c>
+      <c r="M320" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -11682,6 +13606,12 @@
         <v>1</v>
       </c>
       <c r="K321" t="n">
+        <v>14</v>
+      </c>
+      <c r="L321" t="n">
+        <v>0</v>
+      </c>
+      <c r="M321" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -11717,6 +13647,12 @@
         <v>2</v>
       </c>
       <c r="K322" t="n">
+        <v>14</v>
+      </c>
+      <c r="L322" t="n">
+        <v>0</v>
+      </c>
+      <c r="M322" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -11752,6 +13688,12 @@
         <v>0</v>
       </c>
       <c r="K323" t="n">
+        <v>0</v>
+      </c>
+      <c r="L323" t="n">
+        <v>0</v>
+      </c>
+      <c r="M323" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -11787,6 +13729,12 @@
         <v>0</v>
       </c>
       <c r="K324" t="n">
+        <v>0</v>
+      </c>
+      <c r="L324" t="n">
+        <v>0</v>
+      </c>
+      <c r="M324" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -11822,6 +13770,12 @@
         <v>7</v>
       </c>
       <c r="K325" t="n">
+        <v>6</v>
+      </c>
+      <c r="L325" t="n">
+        <v>0</v>
+      </c>
+      <c r="M325" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -11857,6 +13811,12 @@
         <v>2</v>
       </c>
       <c r="K326" t="n">
+        <v>2</v>
+      </c>
+      <c r="L326" t="n">
+        <v>0</v>
+      </c>
+      <c r="M326" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -11892,6 +13852,12 @@
         <v>2</v>
       </c>
       <c r="K327" t="n">
+        <v>1</v>
+      </c>
+      <c r="L327" t="n">
+        <v>0</v>
+      </c>
+      <c r="M327" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -11927,6 +13893,12 @@
         <v>0</v>
       </c>
       <c r="K328" t="n">
+        <v>2</v>
+      </c>
+      <c r="L328" t="n">
+        <v>0</v>
+      </c>
+      <c r="M328" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -11962,6 +13934,12 @@
         <v>1</v>
       </c>
       <c r="K329" t="n">
+        <v>1</v>
+      </c>
+      <c r="L329" t="n">
+        <v>0</v>
+      </c>
+      <c r="M329" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -11997,6 +13975,12 @@
         <v>3</v>
       </c>
       <c r="K330" t="n">
+        <v>1</v>
+      </c>
+      <c r="L330" t="n">
+        <v>0</v>
+      </c>
+      <c r="M330" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -12032,6 +14016,12 @@
         <v>4</v>
       </c>
       <c r="K331" t="n">
+        <v>1</v>
+      </c>
+      <c r="L331" t="n">
+        <v>0</v>
+      </c>
+      <c r="M331" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -12067,6 +14057,12 @@
         <v>5</v>
       </c>
       <c r="K332" t="n">
+        <v>5</v>
+      </c>
+      <c r="L332" t="n">
+        <v>0</v>
+      </c>
+      <c r="M332" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -12102,6 +14098,12 @@
         <v>2</v>
       </c>
       <c r="K333" t="n">
+        <v>3</v>
+      </c>
+      <c r="L333" t="n">
+        <v>0</v>
+      </c>
+      <c r="M333" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -12137,6 +14139,12 @@
         <v>0</v>
       </c>
       <c r="K334" t="n">
+        <v>3</v>
+      </c>
+      <c r="L334" t="n">
+        <v>0</v>
+      </c>
+      <c r="M334" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -12172,6 +14180,12 @@
         <v>0</v>
       </c>
       <c r="K335" t="n">
+        <v>0</v>
+      </c>
+      <c r="L335" t="n">
+        <v>0</v>
+      </c>
+      <c r="M335" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -12207,6 +14221,12 @@
         <v>0</v>
       </c>
       <c r="K336" t="n">
+        <v>0</v>
+      </c>
+      <c r="L336" t="n">
+        <v>0</v>
+      </c>
+      <c r="M336" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -12242,6 +14262,12 @@
         <v>2</v>
       </c>
       <c r="K337" t="n">
+        <v>3</v>
+      </c>
+      <c r="L337" t="n">
+        <v>0</v>
+      </c>
+      <c r="M337" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -12277,6 +14303,12 @@
         <v>3</v>
       </c>
       <c r="K338" t="n">
+        <v>0</v>
+      </c>
+      <c r="L338" t="n">
+        <v>0</v>
+      </c>
+      <c r="M338" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -12312,6 +14344,12 @@
         <v>2</v>
       </c>
       <c r="K339" t="n">
+        <v>0</v>
+      </c>
+      <c r="L339" t="n">
+        <v>0</v>
+      </c>
+      <c r="M339" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -12347,6 +14385,12 @@
         <v>6</v>
       </c>
       <c r="K340" t="n">
+        <v>0</v>
+      </c>
+      <c r="L340" t="n">
+        <v>0</v>
+      </c>
+      <c r="M340" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -12382,6 +14426,12 @@
         <v>2</v>
       </c>
       <c r="K341" t="n">
+        <v>11</v>
+      </c>
+      <c r="L341" t="n">
+        <v>0</v>
+      </c>
+      <c r="M341" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -12417,6 +14467,12 @@
         <v>1</v>
       </c>
       <c r="K342" t="n">
+        <v>10</v>
+      </c>
+      <c r="L342" t="n">
+        <v>0</v>
+      </c>
+      <c r="M342" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -12452,6 +14508,12 @@
         <v>3</v>
       </c>
       <c r="K343" t="n">
+        <v>1</v>
+      </c>
+      <c r="L343" t="n">
+        <v>0</v>
+      </c>
+      <c r="M343" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -12487,6 +14549,12 @@
         <v>2</v>
       </c>
       <c r="K344" t="n">
+        <v>3</v>
+      </c>
+      <c r="L344" t="n">
+        <v>0</v>
+      </c>
+      <c r="M344" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -12522,6 +14590,12 @@
         <v>1</v>
       </c>
       <c r="K345" t="n">
+        <v>1</v>
+      </c>
+      <c r="L345" t="n">
+        <v>0</v>
+      </c>
+      <c r="M345" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -12557,6 +14631,12 @@
         <v>6</v>
       </c>
       <c r="K346" t="n">
+        <v>7</v>
+      </c>
+      <c r="L346" t="n">
+        <v>0</v>
+      </c>
+      <c r="M346" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -12592,6 +14672,12 @@
         <v>1</v>
       </c>
       <c r="K347" t="n">
+        <v>1</v>
+      </c>
+      <c r="L347" t="n">
+        <v>0</v>
+      </c>
+      <c r="M347" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -12627,6 +14713,12 @@
         <v>0</v>
       </c>
       <c r="K348" t="n">
+        <v>0</v>
+      </c>
+      <c r="L348" t="n">
+        <v>0</v>
+      </c>
+      <c r="M348" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -12662,6 +14754,12 @@
         <v>1</v>
       </c>
       <c r="K349" t="n">
+        <v>1</v>
+      </c>
+      <c r="L349" t="n">
+        <v>0</v>
+      </c>
+      <c r="M349" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -12697,6 +14795,12 @@
         <v>0</v>
       </c>
       <c r="K350" t="n">
+        <v>1</v>
+      </c>
+      <c r="L350" t="n">
+        <v>0</v>
+      </c>
+      <c r="M350" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -12732,6 +14836,12 @@
         <v>4</v>
       </c>
       <c r="K351" t="n">
+        <v>0</v>
+      </c>
+      <c r="L351" t="n">
+        <v>0</v>
+      </c>
+      <c r="M351" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -12767,6 +14877,12 @@
         <v>2</v>
       </c>
       <c r="K352" t="n">
+        <v>0</v>
+      </c>
+      <c r="L352" t="n">
+        <v>0</v>
+      </c>
+      <c r="M352" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -12802,6 +14918,12 @@
         <v>2</v>
       </c>
       <c r="K353" t="n">
+        <v>10</v>
+      </c>
+      <c r="L353" t="n">
+        <v>0</v>
+      </c>
+      <c r="M353" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -12837,6 +14959,12 @@
         <v>1</v>
       </c>
       <c r="K354" t="n">
+        <v>14</v>
+      </c>
+      <c r="L354" t="n">
+        <v>0</v>
+      </c>
+      <c r="M354" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -12872,6 +15000,12 @@
         <v>0</v>
       </c>
       <c r="K355" t="n">
+        <v>9</v>
+      </c>
+      <c r="L355" t="n">
+        <v>0</v>
+      </c>
+      <c r="M355" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -12907,6 +15041,12 @@
         <v>3</v>
       </c>
       <c r="K356" t="n">
+        <v>9</v>
+      </c>
+      <c r="L356" t="n">
+        <v>0</v>
+      </c>
+      <c r="M356" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -12942,6 +15082,12 @@
         <v>9</v>
       </c>
       <c r="K357" t="n">
+        <v>12</v>
+      </c>
+      <c r="L357" t="n">
+        <v>0</v>
+      </c>
+      <c r="M357" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -12977,6 +15123,12 @@
         <v>7</v>
       </c>
       <c r="K358" t="n">
+        <v>1</v>
+      </c>
+      <c r="L358" t="n">
+        <v>0</v>
+      </c>
+      <c r="M358" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -13012,6 +15164,12 @@
         <v>5</v>
       </c>
       <c r="K359" t="n">
+        <v>3</v>
+      </c>
+      <c r="L359" t="n">
+        <v>0</v>
+      </c>
+      <c r="M359" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -13047,6 +15205,12 @@
         <v>0</v>
       </c>
       <c r="K360" t="n">
+        <v>10</v>
+      </c>
+      <c r="L360" t="n">
+        <v>0</v>
+      </c>
+      <c r="M360" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -13082,6 +15246,12 @@
         <v>1</v>
       </c>
       <c r="K361" t="n">
+        <v>4</v>
+      </c>
+      <c r="L361" t="n">
+        <v>0</v>
+      </c>
+      <c r="M361" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -13117,6 +15287,12 @@
         <v>0</v>
       </c>
       <c r="K362" t="n">
+        <v>0</v>
+      </c>
+      <c r="L362" t="n">
+        <v>0</v>
+      </c>
+      <c r="M362" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -13152,6 +15328,12 @@
         <v>6</v>
       </c>
       <c r="K363" t="n">
+        <v>0</v>
+      </c>
+      <c r="L363" t="n">
+        <v>0</v>
+      </c>
+      <c r="M363" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -13187,6 +15369,12 @@
         <v>0</v>
       </c>
       <c r="K364" t="n">
+        <v>0</v>
+      </c>
+      <c r="L364" t="n">
+        <v>0</v>
+      </c>
+      <c r="M364" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -13222,6 +15410,12 @@
         <v>2</v>
       </c>
       <c r="K365" t="n">
+        <v>1</v>
+      </c>
+      <c r="L365" t="n">
+        <v>0</v>
+      </c>
+      <c r="M365" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -13257,6 +15451,12 @@
         <v>10</v>
       </c>
       <c r="K366" t="n">
+        <v>11</v>
+      </c>
+      <c r="L366" t="n">
+        <v>0</v>
+      </c>
+      <c r="M366" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -13292,6 +15492,12 @@
         <v>2</v>
       </c>
       <c r="K367" t="n">
+        <v>3</v>
+      </c>
+      <c r="L367" t="n">
+        <v>0</v>
+      </c>
+      <c r="M367" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -13327,6 +15533,12 @@
         <v>1</v>
       </c>
       <c r="K368" t="n">
+        <v>0</v>
+      </c>
+      <c r="L368" t="n">
+        <v>0</v>
+      </c>
+      <c r="M368" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -13362,6 +15574,12 @@
         <v>7</v>
       </c>
       <c r="K369" t="n">
+        <v>4</v>
+      </c>
+      <c r="L369" t="n">
+        <v>0</v>
+      </c>
+      <c r="M369" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -13397,6 +15615,12 @@
         <v>4</v>
       </c>
       <c r="K370" t="n">
+        <v>4</v>
+      </c>
+      <c r="L370" t="n">
+        <v>0</v>
+      </c>
+      <c r="M370" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -13432,6 +15656,12 @@
         <v>0</v>
       </c>
       <c r="K371" t="n">
+        <v>0</v>
+      </c>
+      <c r="L371" t="n">
+        <v>0</v>
+      </c>
+      <c r="M371" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -13467,6 +15697,12 @@
         <v>0</v>
       </c>
       <c r="K372" t="n">
+        <v>0</v>
+      </c>
+      <c r="L372" t="n">
+        <v>0</v>
+      </c>
+      <c r="M372" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -13502,6 +15738,12 @@
         <v>2</v>
       </c>
       <c r="K373" t="n">
+        <v>8</v>
+      </c>
+      <c r="L373" t="n">
+        <v>0</v>
+      </c>
+      <c r="M373" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -13537,6 +15779,12 @@
         <v>0</v>
       </c>
       <c r="K374" t="n">
+        <v>3</v>
+      </c>
+      <c r="L374" t="n">
+        <v>0</v>
+      </c>
+      <c r="M374" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -13572,6 +15820,12 @@
         <v>4</v>
       </c>
       <c r="K375" t="n">
+        <v>3</v>
+      </c>
+      <c r="L375" t="n">
+        <v>0</v>
+      </c>
+      <c r="M375" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -13607,6 +15861,12 @@
         <v>0</v>
       </c>
       <c r="K376" t="n">
+        <v>0</v>
+      </c>
+      <c r="L376" t="n">
+        <v>0</v>
+      </c>
+      <c r="M376" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -13642,6 +15902,12 @@
         <v>3</v>
       </c>
       <c r="K377" t="n">
+        <v>0</v>
+      </c>
+      <c r="L377" t="n">
+        <v>0</v>
+      </c>
+      <c r="M377" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -13677,6 +15943,12 @@
         <v>8</v>
       </c>
       <c r="K378" t="n">
+        <v>2</v>
+      </c>
+      <c r="L378" t="n">
+        <v>0</v>
+      </c>
+      <c r="M378" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -13712,6 +15984,12 @@
         <v>4</v>
       </c>
       <c r="K379" t="n">
+        <v>4</v>
+      </c>
+      <c r="L379" t="n">
+        <v>0</v>
+      </c>
+      <c r="M379" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -13747,6 +16025,12 @@
         <v>0</v>
       </c>
       <c r="K380" t="n">
+        <v>0</v>
+      </c>
+      <c r="L380" t="n">
+        <v>0</v>
+      </c>
+      <c r="M380" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -13782,6 +16066,12 @@
         <v>1</v>
       </c>
       <c r="K381" t="n">
+        <v>2</v>
+      </c>
+      <c r="L381" t="n">
+        <v>0</v>
+      </c>
+      <c r="M381" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -13817,6 +16107,12 @@
         <v>0</v>
       </c>
       <c r="K382" t="n">
+        <v>1</v>
+      </c>
+      <c r="L382" t="n">
+        <v>0</v>
+      </c>
+      <c r="M382" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -13852,6 +16148,12 @@
         <v>14</v>
       </c>
       <c r="K383" t="n">
+        <v>3</v>
+      </c>
+      <c r="L383" t="n">
+        <v>0</v>
+      </c>
+      <c r="M383" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -13887,6 +16189,12 @@
         <v>18</v>
       </c>
       <c r="K384" t="n">
+        <v>5</v>
+      </c>
+      <c r="L384" t="n">
+        <v>0</v>
+      </c>
+      <c r="M384" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -13922,6 +16230,12 @@
         <v>2</v>
       </c>
       <c r="K385" t="n">
+        <v>5</v>
+      </c>
+      <c r="L385" t="n">
+        <v>0</v>
+      </c>
+      <c r="M385" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -13957,6 +16271,12 @@
         <v>3</v>
       </c>
       <c r="K386" t="n">
+        <v>2</v>
+      </c>
+      <c r="L386" t="n">
+        <v>0</v>
+      </c>
+      <c r="M386" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -13992,6 +16312,12 @@
         <v>1</v>
       </c>
       <c r="K387" t="n">
+        <v>0</v>
+      </c>
+      <c r="L387" t="n">
+        <v>0</v>
+      </c>
+      <c r="M387" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -14027,6 +16353,12 @@
         <v>12</v>
       </c>
       <c r="K388" t="n">
+        <v>0</v>
+      </c>
+      <c r="L388" t="n">
+        <v>0</v>
+      </c>
+      <c r="M388" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -14062,6 +16394,12 @@
         <v>10</v>
       </c>
       <c r="K389" t="n">
+        <v>13</v>
+      </c>
+      <c r="L389" t="n">
+        <v>1</v>
+      </c>
+      <c r="M389" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -14097,6 +16435,12 @@
         <v>2</v>
       </c>
       <c r="K390" t="n">
+        <v>0</v>
+      </c>
+      <c r="L390" t="n">
+        <v>0</v>
+      </c>
+      <c r="M390" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -14132,6 +16476,12 @@
         <v>1</v>
       </c>
       <c r="K391" t="n">
+        <v>3</v>
+      </c>
+      <c r="L391" t="n">
+        <v>0</v>
+      </c>
+      <c r="M391" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -14167,6 +16517,12 @@
         <v>2</v>
       </c>
       <c r="K392" t="n">
+        <v>0</v>
+      </c>
+      <c r="L392" t="n">
+        <v>0</v>
+      </c>
+      <c r="M392" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -14202,6 +16558,12 @@
         <v>0</v>
       </c>
       <c r="K393" t="n">
+        <v>0</v>
+      </c>
+      <c r="L393" t="n">
+        <v>0</v>
+      </c>
+      <c r="M393" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -14237,6 +16599,12 @@
         <v>0</v>
       </c>
       <c r="K394" t="n">
+        <v>0</v>
+      </c>
+      <c r="L394" t="n">
+        <v>0</v>
+      </c>
+      <c r="M394" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -14272,6 +16640,12 @@
         <v>0</v>
       </c>
       <c r="K395" t="n">
+        <v>0</v>
+      </c>
+      <c r="L395" t="n">
+        <v>0</v>
+      </c>
+      <c r="M395" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -14307,6 +16681,12 @@
         <v>5</v>
       </c>
       <c r="K396" t="n">
+        <v>5</v>
+      </c>
+      <c r="L396" t="n">
+        <v>0</v>
+      </c>
+      <c r="M396" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -14342,6 +16722,12 @@
         <v>11</v>
       </c>
       <c r="K397" t="n">
+        <v>11</v>
+      </c>
+      <c r="L397" t="n">
+        <v>0</v>
+      </c>
+      <c r="M397" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -14377,6 +16763,12 @@
         <v>6</v>
       </c>
       <c r="K398" t="n">
+        <v>10</v>
+      </c>
+      <c r="L398" t="n">
+        <v>0</v>
+      </c>
+      <c r="M398" t="n">
         <v>2006</v>
       </c>
     </row>
@@ -14412,6 +16804,12 @@
         <v>3</v>
       </c>
       <c r="K399" t="n">
+        <v>8</v>
+      </c>
+      <c r="L399" t="n">
+        <v>0</v>
+      </c>
+      <c r="M399" t="n">
         <v>2006</v>
       </c>
     </row>

--- a/Excel Files IPEDS/Trimmed/c2006_trimmed_file.xlsx
+++ b/Excel Files IPEDS/Trimmed/c2006_trimmed_file.xlsx
@@ -14,45 +14,48 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
   <si>
-    <t>UNITID</t>
+    <t>unitid</t>
   </si>
   <si>
-    <t>CIPCODE</t>
+    <t>cipcode</t>
   </si>
   <si>
-    <t>CTOTALT</t>
+    <t>ctotalt</t>
   </si>
   <si>
-    <t>AWLEVEL</t>
+    <t>awlevel</t>
   </si>
   <si>
-    <t>CRACE15</t>
+    <t>crace15</t>
   </si>
   <si>
-    <t>CRACE16</t>
+    <t>crace16</t>
   </si>
   <si>
-    <t>CRACE18</t>
+    <t>crace18</t>
   </si>
   <si>
-    <t>CRACE20</t>
+    <t>crace20</t>
   </si>
   <si>
-    <t>CRACE21</t>
+    <t>crace21</t>
   </si>
   <si>
-    <t>CRACE22</t>
+    <t>crace22</t>
   </si>
   <si>
-    <t>CRACE17</t>
+    <t>crace17</t>
   </si>
   <si>
-    <t>CRACE19</t>
+    <t>crace19</t>
   </si>
   <si>
-    <t>Year</t>
+    <t>majornum</t>
+  </si>
+  <si>
+    <t>year</t>
   </si>
 </sst>
 </file>
@@ -410,10 +413,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M399"/>
+  <dimension ref="A1:N399"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:14">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -453,8 +456,11 @@
       <c r="M1" s="1" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="2" spans="1:13">
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
       <c r="A2">
         <v>100654</v>
       </c>
@@ -492,10 +498,13 @@
         <v>0</v>
       </c>
       <c r="M2">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N2">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
       <c r="A3">
         <v>100663</v>
       </c>
@@ -533,10 +542,13 @@
         <v>0</v>
       </c>
       <c r="M3">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N3">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
       <c r="A4">
         <v>100663</v>
       </c>
@@ -574,10 +586,13 @@
         <v>0</v>
       </c>
       <c r="M4">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N4">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
       <c r="A5">
         <v>100706</v>
       </c>
@@ -615,10 +630,13 @@
         <v>0</v>
       </c>
       <c r="M5">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N5">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
       <c r="A6">
         <v>100706</v>
       </c>
@@ -656,10 +674,13 @@
         <v>0</v>
       </c>
       <c r="M6">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N6">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
       <c r="A7">
         <v>100751</v>
       </c>
@@ -697,10 +718,13 @@
         <v>0</v>
       </c>
       <c r="M7">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N7">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
       <c r="A8">
         <v>100751</v>
       </c>
@@ -738,10 +762,13 @@
         <v>0</v>
       </c>
       <c r="M8">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N8">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
       <c r="A9">
         <v>100858</v>
       </c>
@@ -779,10 +806,13 @@
         <v>0</v>
       </c>
       <c r="M9">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N9">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
       <c r="A10">
         <v>100858</v>
       </c>
@@ -820,10 +850,13 @@
         <v>0</v>
       </c>
       <c r="M10">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N10">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
       <c r="A11">
         <v>102614</v>
       </c>
@@ -861,10 +894,13 @@
         <v>0</v>
       </c>
       <c r="M11">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N11">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
       <c r="A12">
         <v>102614</v>
       </c>
@@ -902,10 +938,13 @@
         <v>0</v>
       </c>
       <c r="M12">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N12">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14">
       <c r="A13">
         <v>104151</v>
       </c>
@@ -943,10 +982,13 @@
         <v>0</v>
       </c>
       <c r="M13">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N13">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14">
       <c r="A14">
         <v>104151</v>
       </c>
@@ -984,10 +1026,13 @@
         <v>0</v>
       </c>
       <c r="M14">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N14">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14">
       <c r="A15">
         <v>104179</v>
       </c>
@@ -1025,10 +1070,13 @@
         <v>0</v>
       </c>
       <c r="M15">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N15">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14">
       <c r="A16">
         <v>104179</v>
       </c>
@@ -1066,10 +1114,13 @@
         <v>0</v>
       </c>
       <c r="M16">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="17" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N16">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14">
       <c r="A17">
         <v>105330</v>
       </c>
@@ -1107,10 +1158,13 @@
         <v>0</v>
       </c>
       <c r="M17">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="18" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N17">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14">
       <c r="A18">
         <v>106397</v>
       </c>
@@ -1148,10 +1202,13 @@
         <v>0</v>
       </c>
       <c r="M18">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="19" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N18">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14">
       <c r="A19">
         <v>106397</v>
       </c>
@@ -1189,10 +1246,13 @@
         <v>0</v>
       </c>
       <c r="M19">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="20" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N19">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14">
       <c r="A20">
         <v>110404</v>
       </c>
@@ -1230,10 +1290,13 @@
         <v>0</v>
       </c>
       <c r="M20">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="21" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N20">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14">
       <c r="A21">
         <v>110404</v>
       </c>
@@ -1271,10 +1334,13 @@
         <v>0</v>
       </c>
       <c r="M21">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="22" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N21">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14">
       <c r="A22">
         <v>110422</v>
       </c>
@@ -1312,10 +1378,13 @@
         <v>0</v>
       </c>
       <c r="M22">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="23" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N22">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14">
       <c r="A23">
         <v>110422</v>
       </c>
@@ -1353,10 +1422,13 @@
         <v>0</v>
       </c>
       <c r="M23">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="24" spans="1:13">
+        <v>2</v>
+      </c>
+      <c r="N23">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14">
       <c r="A24">
         <v>110556</v>
       </c>
@@ -1394,10 +1466,13 @@
         <v>0</v>
       </c>
       <c r="M24">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="25" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N24">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14">
       <c r="A25">
         <v>110565</v>
       </c>
@@ -1435,10 +1510,13 @@
         <v>0</v>
       </c>
       <c r="M25">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="26" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N25">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14">
       <c r="A26">
         <v>110583</v>
       </c>
@@ -1476,10 +1554,13 @@
         <v>0</v>
       </c>
       <c r="M26">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="27" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N26">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14">
       <c r="A27">
         <v>110592</v>
       </c>
@@ -1517,10 +1598,13 @@
         <v>0</v>
       </c>
       <c r="M27">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="28" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N27">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14">
       <c r="A28">
         <v>110608</v>
       </c>
@@ -1558,10 +1642,13 @@
         <v>0</v>
       </c>
       <c r="M28">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="29" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N28">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14">
       <c r="A29">
         <v>110635</v>
       </c>
@@ -1599,10 +1686,13 @@
         <v>0</v>
       </c>
       <c r="M29">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="30" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N29">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14">
       <c r="A30">
         <v>110635</v>
       </c>
@@ -1640,10 +1730,13 @@
         <v>0</v>
       </c>
       <c r="M30">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="31" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N30">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14">
       <c r="A31">
         <v>110644</v>
       </c>
@@ -1681,10 +1774,13 @@
         <v>0</v>
       </c>
       <c r="M31">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="32" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N31">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14">
       <c r="A32">
         <v>110644</v>
       </c>
@@ -1722,10 +1818,13 @@
         <v>0</v>
       </c>
       <c r="M32">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="33" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N32">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="33" spans="1:14">
       <c r="A33">
         <v>110653</v>
       </c>
@@ -1763,10 +1862,13 @@
         <v>0</v>
       </c>
       <c r="M33">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="34" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N33">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="34" spans="1:14">
       <c r="A34">
         <v>110653</v>
       </c>
@@ -1804,10 +1906,13 @@
         <v>0</v>
       </c>
       <c r="M34">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="35" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N34">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="35" spans="1:14">
       <c r="A35">
         <v>110662</v>
       </c>
@@ -1845,10 +1950,13 @@
         <v>0</v>
       </c>
       <c r="M35">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="36" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N35">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="36" spans="1:14">
       <c r="A36">
         <v>110662</v>
       </c>
@@ -1886,10 +1994,13 @@
         <v>0</v>
       </c>
       <c r="M36">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="37" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N36">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="37" spans="1:14">
       <c r="A37">
         <v>110671</v>
       </c>
@@ -1927,10 +2038,13 @@
         <v>0</v>
       </c>
       <c r="M37">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="38" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N37">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="38" spans="1:14">
       <c r="A38">
         <v>110671</v>
       </c>
@@ -1968,10 +2082,13 @@
         <v>0</v>
       </c>
       <c r="M38">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="39" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N38">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="39" spans="1:14">
       <c r="A39">
         <v>110680</v>
       </c>
@@ -2009,10 +2126,13 @@
         <v>0</v>
       </c>
       <c r="M39">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="40" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N39">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="40" spans="1:14">
       <c r="A40">
         <v>110680</v>
       </c>
@@ -2050,10 +2170,13 @@
         <v>0</v>
       </c>
       <c r="M40">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="41" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N40">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="41" spans="1:14">
       <c r="A41">
         <v>110705</v>
       </c>
@@ -2091,10 +2214,13 @@
         <v>0</v>
       </c>
       <c r="M41">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="42" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N41">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="42" spans="1:14">
       <c r="A42">
         <v>110705</v>
       </c>
@@ -2132,10 +2258,13 @@
         <v>0</v>
       </c>
       <c r="M42">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="43" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N42">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="43" spans="1:14">
       <c r="A43">
         <v>110714</v>
       </c>
@@ -2173,10 +2302,13 @@
         <v>0</v>
       </c>
       <c r="M43">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="44" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N43">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="44" spans="1:14">
       <c r="A44">
         <v>110714</v>
       </c>
@@ -2214,10 +2346,13 @@
         <v>0</v>
       </c>
       <c r="M44">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="45" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N44">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="45" spans="1:14">
       <c r="A45">
         <v>119678</v>
       </c>
@@ -2255,10 +2390,13 @@
         <v>0</v>
       </c>
       <c r="M45">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="46" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N45">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="46" spans="1:14">
       <c r="A46">
         <v>122409</v>
       </c>
@@ -2296,10 +2434,13 @@
         <v>0</v>
       </c>
       <c r="M46">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="47" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N46">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="47" spans="1:14">
       <c r="A47">
         <v>122597</v>
       </c>
@@ -2337,10 +2478,13 @@
         <v>1</v>
       </c>
       <c r="M47">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="48" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N47">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="48" spans="1:14">
       <c r="A48">
         <v>122755</v>
       </c>
@@ -2378,10 +2522,13 @@
         <v>0</v>
       </c>
       <c r="M48">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="49" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N48">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="49" spans="1:14">
       <c r="A49">
         <v>123961</v>
       </c>
@@ -2419,10 +2566,13 @@
         <v>0</v>
       </c>
       <c r="M49">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="50" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N49">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="50" spans="1:14">
       <c r="A50">
         <v>123961</v>
       </c>
@@ -2460,10 +2610,13 @@
         <v>0</v>
       </c>
       <c r="M50">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="51" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N50">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="51" spans="1:14">
       <c r="A51">
         <v>126614</v>
       </c>
@@ -2501,10 +2654,13 @@
         <v>0</v>
       </c>
       <c r="M51">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="52" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N51">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="52" spans="1:14">
       <c r="A52">
         <v>126614</v>
       </c>
@@ -2542,10 +2698,13 @@
         <v>0</v>
       </c>
       <c r="M52">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="53" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N52">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="53" spans="1:14">
       <c r="A53">
         <v>126775</v>
       </c>
@@ -2583,10 +2742,13 @@
         <v>0</v>
       </c>
       <c r="M53">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="54" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N53">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="54" spans="1:14">
       <c r="A54">
         <v>126818</v>
       </c>
@@ -2624,10 +2786,13 @@
         <v>0</v>
       </c>
       <c r="M54">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="55" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N54">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="55" spans="1:14">
       <c r="A55">
         <v>126818</v>
       </c>
@@ -2665,10 +2830,13 @@
         <v>0</v>
       </c>
       <c r="M55">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="56" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N55">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="56" spans="1:14">
       <c r="A56">
         <v>127060</v>
       </c>
@@ -2706,10 +2874,13 @@
         <v>0</v>
       </c>
       <c r="M56">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="57" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N56">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="57" spans="1:14">
       <c r="A57">
         <v>127060</v>
       </c>
@@ -2747,10 +2918,13 @@
         <v>0</v>
       </c>
       <c r="M57">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="58" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N57">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="58" spans="1:14">
       <c r="A58">
         <v>129020</v>
       </c>
@@ -2788,10 +2962,13 @@
         <v>0</v>
       </c>
       <c r="M58">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="59" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N58">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="59" spans="1:14">
       <c r="A59">
         <v>129020</v>
       </c>
@@ -2829,10 +3006,13 @@
         <v>0</v>
       </c>
       <c r="M59">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="60" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N59">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="60" spans="1:14">
       <c r="A60">
         <v>130697</v>
       </c>
@@ -2870,10 +3050,13 @@
         <v>0</v>
       </c>
       <c r="M60">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="61" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N60">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="61" spans="1:14">
       <c r="A61">
         <v>130697</v>
       </c>
@@ -2911,10 +3094,13 @@
         <v>0</v>
       </c>
       <c r="M61">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="62" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N61">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="62" spans="1:14">
       <c r="A62">
         <v>130794</v>
       </c>
@@ -2952,10 +3138,13 @@
         <v>0</v>
       </c>
       <c r="M62">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="63" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N62">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="63" spans="1:14">
       <c r="A63">
         <v>130794</v>
       </c>
@@ -2993,10 +3182,13 @@
         <v>0</v>
       </c>
       <c r="M63">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="64" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N63">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="64" spans="1:14">
       <c r="A64">
         <v>130934</v>
       </c>
@@ -3034,10 +3226,13 @@
         <v>0</v>
       </c>
       <c r="M64">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="65" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N64">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="65" spans="1:14">
       <c r="A65">
         <v>130943</v>
       </c>
@@ -3075,10 +3270,13 @@
         <v>0</v>
       </c>
       <c r="M65">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="66" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N65">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="66" spans="1:14">
       <c r="A66">
         <v>130943</v>
       </c>
@@ -3116,10 +3314,13 @@
         <v>0</v>
       </c>
       <c r="M66">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="67" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N66">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="67" spans="1:14">
       <c r="A67">
         <v>131283</v>
       </c>
@@ -3157,10 +3358,13 @@
         <v>0</v>
       </c>
       <c r="M67">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="68" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N67">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="68" spans="1:14">
       <c r="A68">
         <v>131283</v>
       </c>
@@ -3198,10 +3402,13 @@
         <v>0</v>
       </c>
       <c r="M68">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="69" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N68">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="69" spans="1:14">
       <c r="A69">
         <v>131469</v>
       </c>
@@ -3239,10 +3446,13 @@
         <v>0</v>
       </c>
       <c r="M69">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="70" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N69">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="70" spans="1:14">
       <c r="A70">
         <v>131469</v>
       </c>
@@ -3280,10 +3490,13 @@
         <v>0</v>
       </c>
       <c r="M70">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="71" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N70">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="71" spans="1:14">
       <c r="A71">
         <v>131496</v>
       </c>
@@ -3321,10 +3534,13 @@
         <v>0</v>
       </c>
       <c r="M71">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="72" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N71">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="72" spans="1:14">
       <c r="A72">
         <v>131520</v>
       </c>
@@ -3362,10 +3578,13 @@
         <v>0</v>
       </c>
       <c r="M72">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="73" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N72">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="73" spans="1:14">
       <c r="A73">
         <v>131520</v>
       </c>
@@ -3403,10 +3622,13 @@
         <v>0</v>
       </c>
       <c r="M73">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="74" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N73">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="74" spans="1:14">
       <c r="A74">
         <v>132903</v>
       </c>
@@ -3444,10 +3666,13 @@
         <v>0</v>
       </c>
       <c r="M74">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="75" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N74">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="75" spans="1:14">
       <c r="A75">
         <v>132903</v>
       </c>
@@ -3485,10 +3710,13 @@
         <v>0</v>
       </c>
       <c r="M75">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="76" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N75">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="76" spans="1:14">
       <c r="A76">
         <v>133650</v>
       </c>
@@ -3526,10 +3754,13 @@
         <v>0</v>
       </c>
       <c r="M76">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="77" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N76">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="77" spans="1:14">
       <c r="A77">
         <v>133669</v>
       </c>
@@ -3567,10 +3798,13 @@
         <v>0</v>
       </c>
       <c r="M77">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="78" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N77">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="78" spans="1:14">
       <c r="A78">
         <v>133669</v>
       </c>
@@ -3608,10 +3842,13 @@
         <v>0</v>
       </c>
       <c r="M78">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="79" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N78">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="79" spans="1:14">
       <c r="A79">
         <v>133881</v>
       </c>
@@ -3649,10 +3886,13 @@
         <v>0</v>
       </c>
       <c r="M79">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="80" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N79">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="80" spans="1:14">
       <c r="A80">
         <v>133951</v>
       </c>
@@ -3690,10 +3930,13 @@
         <v>0</v>
       </c>
       <c r="M80">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="81" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N80">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="81" spans="1:14">
       <c r="A81">
         <v>134097</v>
       </c>
@@ -3731,10 +3974,13 @@
         <v>0</v>
       </c>
       <c r="M81">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="82" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N81">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="82" spans="1:14">
       <c r="A82">
         <v>134097</v>
       </c>
@@ -3772,10 +4018,13 @@
         <v>0</v>
       </c>
       <c r="M82">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="83" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N82">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="83" spans="1:14">
       <c r="A83">
         <v>134130</v>
       </c>
@@ -3813,10 +4062,13 @@
         <v>0</v>
       </c>
       <c r="M83">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="84" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N83">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="84" spans="1:14">
       <c r="A84">
         <v>134130</v>
       </c>
@@ -3854,10 +4106,13 @@
         <v>0</v>
       </c>
       <c r="M84">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="85" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N84">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="85" spans="1:14">
       <c r="A85">
         <v>135726</v>
       </c>
@@ -3895,10 +4150,13 @@
         <v>0</v>
       </c>
       <c r="M85">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="86" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N85">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="86" spans="1:14">
       <c r="A86">
         <v>135726</v>
       </c>
@@ -3936,10 +4194,13 @@
         <v>0</v>
       </c>
       <c r="M86">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="87" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N86">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="87" spans="1:14">
       <c r="A87">
         <v>137351</v>
       </c>
@@ -3977,10 +4238,13 @@
         <v>0</v>
       </c>
       <c r="M87">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="88" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N87">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="88" spans="1:14">
       <c r="A88">
         <v>137351</v>
       </c>
@@ -4018,10 +4282,13 @@
         <v>0</v>
       </c>
       <c r="M88">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="89" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N88">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="89" spans="1:14">
       <c r="A89">
         <v>138947</v>
       </c>
@@ -4059,10 +4326,13 @@
         <v>0</v>
       </c>
       <c r="M89">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="90" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N89">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="90" spans="1:14">
       <c r="A90">
         <v>139658</v>
       </c>
@@ -4100,10 +4370,13 @@
         <v>0</v>
       </c>
       <c r="M90">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="91" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N90">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="91" spans="1:14">
       <c r="A91">
         <v>139755</v>
       </c>
@@ -4141,10 +4414,13 @@
         <v>0</v>
       </c>
       <c r="M91">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="92" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N91">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="92" spans="1:14">
       <c r="A92">
         <v>139755</v>
       </c>
@@ -4182,10 +4458,13 @@
         <v>0</v>
       </c>
       <c r="M92">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="93" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N92">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="93" spans="1:14">
       <c r="A93">
         <v>139940</v>
       </c>
@@ -4223,10 +4502,13 @@
         <v>0</v>
       </c>
       <c r="M93">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="94" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N93">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="94" spans="1:14">
       <c r="A94">
         <v>139940</v>
       </c>
@@ -4264,10 +4546,13 @@
         <v>0</v>
       </c>
       <c r="M94">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="95" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N94">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="95" spans="1:14">
       <c r="A95">
         <v>139959</v>
       </c>
@@ -4305,10 +4590,13 @@
         <v>0</v>
       </c>
       <c r="M95">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="96" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N95">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="96" spans="1:14">
       <c r="A96">
         <v>139959</v>
       </c>
@@ -4346,10 +4634,13 @@
         <v>0</v>
       </c>
       <c r="M96">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="97" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N96">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="97" spans="1:14">
       <c r="A97">
         <v>141574</v>
       </c>
@@ -4387,10 +4678,13 @@
         <v>0</v>
       </c>
       <c r="M97">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="98" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N97">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="98" spans="1:14">
       <c r="A98">
         <v>141574</v>
       </c>
@@ -4428,10 +4722,13 @@
         <v>0</v>
       </c>
       <c r="M98">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="99" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N98">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="99" spans="1:14">
       <c r="A99">
         <v>142276</v>
       </c>
@@ -4469,10 +4766,13 @@
         <v>0</v>
       </c>
       <c r="M99">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="100" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N99">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="100" spans="1:14">
       <c r="A100">
         <v>142285</v>
       </c>
@@ -4510,10 +4810,13 @@
         <v>0</v>
       </c>
       <c r="M100">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="101" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N100">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="101" spans="1:14">
       <c r="A101">
         <v>142285</v>
       </c>
@@ -4551,10 +4854,13 @@
         <v>0</v>
       </c>
       <c r="M101">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="102" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N101">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="102" spans="1:14">
       <c r="A102">
         <v>144050</v>
       </c>
@@ -4592,10 +4898,13 @@
         <v>0</v>
       </c>
       <c r="M102">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="103" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N102">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="103" spans="1:14">
       <c r="A103">
         <v>144050</v>
       </c>
@@ -4633,10 +4942,13 @@
         <v>0</v>
       </c>
       <c r="M103">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="104" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N103">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="104" spans="1:14">
       <c r="A104">
         <v>144740</v>
       </c>
@@ -4674,10 +4986,13 @@
         <v>0</v>
       </c>
       <c r="M104">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="105" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N104">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="105" spans="1:14">
       <c r="A105">
         <v>144740</v>
       </c>
@@ -4715,10 +5030,13 @@
         <v>0</v>
       </c>
       <c r="M105">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="106" spans="1:13">
+        <v>2</v>
+      </c>
+      <c r="N105">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="106" spans="1:14">
       <c r="A106">
         <v>145600</v>
       </c>
@@ -4756,10 +5074,13 @@
         <v>0</v>
       </c>
       <c r="M106">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="107" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N106">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="107" spans="1:14">
       <c r="A107">
         <v>145600</v>
       </c>
@@ -4797,10 +5118,13 @@
         <v>0</v>
       </c>
       <c r="M107">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="108" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N107">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="108" spans="1:14">
       <c r="A108">
         <v>145637</v>
       </c>
@@ -4838,10 +5162,13 @@
         <v>0</v>
       </c>
       <c r="M108">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="109" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N108">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="109" spans="1:14">
       <c r="A109">
         <v>145637</v>
       </c>
@@ -4879,10 +5206,13 @@
         <v>1</v>
       </c>
       <c r="M109">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="110" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N109">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="110" spans="1:14">
       <c r="A110">
         <v>145725</v>
       </c>
@@ -4920,10 +5250,13 @@
         <v>0</v>
       </c>
       <c r="M110">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="111" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N110">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="111" spans="1:14">
       <c r="A111">
         <v>147703</v>
       </c>
@@ -4961,10 +5294,13 @@
         <v>0</v>
       </c>
       <c r="M111">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="112" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N111">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="112" spans="1:14">
       <c r="A112">
         <v>147703</v>
       </c>
@@ -5002,10 +5338,13 @@
         <v>0</v>
       </c>
       <c r="M112">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="113" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N112">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="113" spans="1:14">
       <c r="A113">
         <v>149222</v>
       </c>
@@ -5043,10 +5382,13 @@
         <v>0</v>
       </c>
       <c r="M113">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="114" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N113">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="114" spans="1:14">
       <c r="A114">
         <v>149222</v>
       </c>
@@ -5084,10 +5426,13 @@
         <v>0</v>
       </c>
       <c r="M114">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="115" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N114">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="115" spans="1:14">
       <c r="A115">
         <v>149222</v>
       </c>
@@ -5125,10 +5470,13 @@
         <v>0</v>
       </c>
       <c r="M115">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="116" spans="1:13">
+        <v>2</v>
+      </c>
+      <c r="N115">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="116" spans="1:14">
       <c r="A116">
         <v>149222</v>
       </c>
@@ -5166,10 +5514,13 @@
         <v>0</v>
       </c>
       <c r="M116">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="117" spans="1:13">
+        <v>2</v>
+      </c>
+      <c r="N116">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="117" spans="1:14">
       <c r="A117">
         <v>149231</v>
       </c>
@@ -5207,10 +5558,13 @@
         <v>0</v>
       </c>
       <c r="M117">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="118" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N117">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="118" spans="1:14">
       <c r="A118">
         <v>149772</v>
       </c>
@@ -5248,10 +5602,13 @@
         <v>0</v>
       </c>
       <c r="M118">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="119" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N118">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="119" spans="1:14">
       <c r="A119">
         <v>150136</v>
       </c>
@@ -5289,10 +5646,13 @@
         <v>0</v>
       </c>
       <c r="M119">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="120" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N119">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="120" spans="1:14">
       <c r="A120">
         <v>151111</v>
       </c>
@@ -5330,10 +5690,13 @@
         <v>0</v>
       </c>
       <c r="M120">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="121" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N120">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="121" spans="1:14">
       <c r="A121">
         <v>151351</v>
       </c>
@@ -5371,10 +5734,13 @@
         <v>0</v>
       </c>
       <c r="M121">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="122" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N121">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="122" spans="1:14">
       <c r="A122">
         <v>151351</v>
       </c>
@@ -5412,10 +5778,13 @@
         <v>0</v>
       </c>
       <c r="M122">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="123" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N122">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="123" spans="1:14">
       <c r="A123">
         <v>152080</v>
       </c>
@@ -5453,10 +5822,13 @@
         <v>0</v>
       </c>
       <c r="M123">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="124" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N123">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="124" spans="1:14">
       <c r="A124">
         <v>152080</v>
       </c>
@@ -5494,10 +5866,13 @@
         <v>0</v>
       </c>
       <c r="M124">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="125" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N124">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="125" spans="1:14">
       <c r="A125">
         <v>153603</v>
       </c>
@@ -5535,10 +5910,13 @@
         <v>0</v>
       </c>
       <c r="M125">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="126" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N125">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="126" spans="1:14">
       <c r="A126">
         <v>153603</v>
       </c>
@@ -5576,10 +5954,13 @@
         <v>0</v>
       </c>
       <c r="M126">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="127" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N126">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="127" spans="1:14">
       <c r="A127">
         <v>153603</v>
       </c>
@@ -5617,10 +5998,13 @@
         <v>0</v>
       </c>
       <c r="M127">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="128" spans="1:13">
+        <v>2</v>
+      </c>
+      <c r="N127">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="128" spans="1:14">
       <c r="A128">
         <v>153603</v>
       </c>
@@ -5658,10 +6042,13 @@
         <v>0</v>
       </c>
       <c r="M128">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="129" spans="1:13">
+        <v>2</v>
+      </c>
+      <c r="N128">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="129" spans="1:14">
       <c r="A129">
         <v>153658</v>
       </c>
@@ -5699,10 +6086,13 @@
         <v>0</v>
       </c>
       <c r="M129">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="130" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N129">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="130" spans="1:14">
       <c r="A130">
         <v>153658</v>
       </c>
@@ -5740,10 +6130,13 @@
         <v>0</v>
       </c>
       <c r="M130">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="131" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N130">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="131" spans="1:14">
       <c r="A131">
         <v>155317</v>
       </c>
@@ -5781,10 +6174,13 @@
         <v>0</v>
       </c>
       <c r="M131">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="132" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N131">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="132" spans="1:14">
       <c r="A132">
         <v>155317</v>
       </c>
@@ -5822,10 +6218,13 @@
         <v>0</v>
       </c>
       <c r="M132">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="133" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N132">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="133" spans="1:14">
       <c r="A133">
         <v>155399</v>
       </c>
@@ -5863,10 +6262,13 @@
         <v>0</v>
       </c>
       <c r="M133">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="134" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N133">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="134" spans="1:14">
       <c r="A134">
         <v>155399</v>
       </c>
@@ -5904,10 +6306,13 @@
         <v>0</v>
       </c>
       <c r="M134">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="135" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N134">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="135" spans="1:14">
       <c r="A135">
         <v>155681</v>
       </c>
@@ -5945,10 +6350,13 @@
         <v>0</v>
       </c>
       <c r="M135">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="136" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N135">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="136" spans="1:14">
       <c r="A136">
         <v>156125</v>
       </c>
@@ -5986,10 +6394,13 @@
         <v>0</v>
       </c>
       <c r="M136">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="137" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N136">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="137" spans="1:14">
       <c r="A137">
         <v>157085</v>
       </c>
@@ -6027,10 +6438,13 @@
         <v>0</v>
       </c>
       <c r="M137">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="138" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N137">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="138" spans="1:14">
       <c r="A138">
         <v>157085</v>
       </c>
@@ -6068,10 +6482,13 @@
         <v>0</v>
       </c>
       <c r="M138">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="139" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N138">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="139" spans="1:14">
       <c r="A139">
         <v>157289</v>
       </c>
@@ -6109,10 +6526,13 @@
         <v>0</v>
       </c>
       <c r="M139">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="140" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N139">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="140" spans="1:14">
       <c r="A140">
         <v>159391</v>
       </c>
@@ -6150,10 +6570,13 @@
         <v>0</v>
       </c>
       <c r="M140">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="141" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N140">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="141" spans="1:14">
       <c r="A141">
         <v>159391</v>
       </c>
@@ -6191,10 +6614,13 @@
         <v>0</v>
       </c>
       <c r="M141">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="142" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N141">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="142" spans="1:14">
       <c r="A142">
         <v>159647</v>
       </c>
@@ -6232,10 +6658,13 @@
         <v>0</v>
       </c>
       <c r="M142">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="143" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N142">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="143" spans="1:14">
       <c r="A143">
         <v>159939</v>
       </c>
@@ -6273,10 +6702,13 @@
         <v>0</v>
       </c>
       <c r="M143">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="144" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N143">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="144" spans="1:14">
       <c r="A144">
         <v>160621</v>
       </c>
@@ -6314,10 +6746,13 @@
         <v>0</v>
       </c>
       <c r="M144">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="145" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N144">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="145" spans="1:14">
       <c r="A145">
         <v>160658</v>
       </c>
@@ -6355,10 +6790,13 @@
         <v>0</v>
       </c>
       <c r="M145">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="146" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N145">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="146" spans="1:14">
       <c r="A146">
         <v>160755</v>
       </c>
@@ -6396,10 +6834,13 @@
         <v>0</v>
       </c>
       <c r="M146">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="147" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N146">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="147" spans="1:14">
       <c r="A147">
         <v>160755</v>
       </c>
@@ -6437,10 +6878,13 @@
         <v>0</v>
       </c>
       <c r="M147">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="148" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N147">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="148" spans="1:14">
       <c r="A148">
         <v>161253</v>
       </c>
@@ -6478,10 +6922,13 @@
         <v>0</v>
       </c>
       <c r="M148">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="149" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N148">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="149" spans="1:14">
       <c r="A149">
         <v>161253</v>
       </c>
@@ -6519,10 +6966,13 @@
         <v>0</v>
       </c>
       <c r="M149">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="150" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N149">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="150" spans="1:14">
       <c r="A150">
         <v>162928</v>
       </c>
@@ -6560,10 +7010,13 @@
         <v>0</v>
       </c>
       <c r="M150">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="151" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N150">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="151" spans="1:14">
       <c r="A151">
         <v>162928</v>
       </c>
@@ -6601,10 +7054,13 @@
         <v>0</v>
       </c>
       <c r="M151">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="152" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N151">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="152" spans="1:14">
       <c r="A152">
         <v>163268</v>
       </c>
@@ -6642,10 +7098,13 @@
         <v>0</v>
       </c>
       <c r="M152">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="153" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N152">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="153" spans="1:14">
       <c r="A153">
         <v>163268</v>
       </c>
@@ -6683,10 +7142,13 @@
         <v>0</v>
       </c>
       <c r="M153">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="154" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N153">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="154" spans="1:14">
       <c r="A154">
         <v>163286</v>
       </c>
@@ -6724,10 +7186,13 @@
         <v>0</v>
       </c>
       <c r="M154">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="155" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N154">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="155" spans="1:14">
       <c r="A155">
         <v>163286</v>
       </c>
@@ -6765,10 +7230,13 @@
         <v>0</v>
       </c>
       <c r="M155">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="156" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N155">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="156" spans="1:14">
       <c r="A156">
         <v>164924</v>
       </c>
@@ -6806,10 +7274,13 @@
         <v>0</v>
       </c>
       <c r="M156">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="157" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N156">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="157" spans="1:14">
       <c r="A157">
         <v>164924</v>
       </c>
@@ -6847,10 +7318,13 @@
         <v>0</v>
       </c>
       <c r="M157">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="158" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N157">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="158" spans="1:14">
       <c r="A158">
         <v>164988</v>
       </c>
@@ -6888,10 +7362,13 @@
         <v>0</v>
       </c>
       <c r="M158">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="159" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N158">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="159" spans="1:14">
       <c r="A159">
         <v>164988</v>
       </c>
@@ -6929,10 +7406,13 @@
         <v>0</v>
       </c>
       <c r="M159">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="160" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N159">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="160" spans="1:14">
       <c r="A160">
         <v>165015</v>
       </c>
@@ -6970,10 +7450,13 @@
         <v>0</v>
       </c>
       <c r="M160">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="161" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N160">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="161" spans="1:14">
       <c r="A161">
         <v>165015</v>
       </c>
@@ -7011,10 +7494,13 @@
         <v>0</v>
       </c>
       <c r="M161">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="162" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N161">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="162" spans="1:14">
       <c r="A162">
         <v>165334</v>
       </c>
@@ -7052,10 +7538,13 @@
         <v>0</v>
       </c>
       <c r="M162">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="163" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N162">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="163" spans="1:14">
       <c r="A163">
         <v>165334</v>
       </c>
@@ -7093,10 +7582,13 @@
         <v>0</v>
       </c>
       <c r="M163">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="164" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N163">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="164" spans="1:14">
       <c r="A164">
         <v>166027</v>
       </c>
@@ -7134,10 +7626,13 @@
         <v>0</v>
       </c>
       <c r="M164">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="165" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N164">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="165" spans="1:14">
       <c r="A165">
         <v>166027</v>
       </c>
@@ -7175,10 +7670,13 @@
         <v>0</v>
       </c>
       <c r="M165">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="166" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N165">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="166" spans="1:14">
       <c r="A166">
         <v>166513</v>
       </c>
@@ -7216,10 +7714,13 @@
         <v>0</v>
       </c>
       <c r="M166">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="167" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N166">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="167" spans="1:14">
       <c r="A167">
         <v>166513</v>
       </c>
@@ -7257,10 +7758,13 @@
         <v>0</v>
       </c>
       <c r="M167">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="168" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N167">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="168" spans="1:14">
       <c r="A168">
         <v>166629</v>
       </c>
@@ -7298,10 +7802,13 @@
         <v>0</v>
       </c>
       <c r="M168">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="169" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N168">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="169" spans="1:14">
       <c r="A169">
         <v>166629</v>
       </c>
@@ -7339,10 +7846,13 @@
         <v>0</v>
       </c>
       <c r="M169">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="170" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N169">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="170" spans="1:14">
       <c r="A170">
         <v>166683</v>
       </c>
@@ -7380,10 +7890,13 @@
         <v>0</v>
       </c>
       <c r="M170">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="171" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N170">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="171" spans="1:14">
       <c r="A171">
         <v>166683</v>
       </c>
@@ -7421,10 +7934,13 @@
         <v>0</v>
       </c>
       <c r="M171">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="172" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N171">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="172" spans="1:14">
       <c r="A172">
         <v>167358</v>
       </c>
@@ -7462,10 +7978,13 @@
         <v>0</v>
       </c>
       <c r="M172">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="173" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N172">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="173" spans="1:14">
       <c r="A173">
         <v>167358</v>
       </c>
@@ -7503,10 +8022,13 @@
         <v>0</v>
       </c>
       <c r="M173">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="174" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N173">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="174" spans="1:14">
       <c r="A174">
         <v>167987</v>
       </c>
@@ -7544,10 +8066,13 @@
         <v>0</v>
       </c>
       <c r="M174">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="175" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N174">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="175" spans="1:14">
       <c r="A175">
         <v>168148</v>
       </c>
@@ -7585,10 +8110,13 @@
         <v>0</v>
       </c>
       <c r="M175">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="176" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N175">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="176" spans="1:14">
       <c r="A176">
         <v>168148</v>
       </c>
@@ -7626,10 +8154,13 @@
         <v>0</v>
       </c>
       <c r="M176">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="177" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N176">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="177" spans="1:14">
       <c r="A177">
         <v>168421</v>
       </c>
@@ -7667,10 +8198,13 @@
         <v>0</v>
       </c>
       <c r="M177">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="178" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N177">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="178" spans="1:14">
       <c r="A178">
         <v>168421</v>
       </c>
@@ -7708,10 +8242,13 @@
         <v>0</v>
       </c>
       <c r="M178">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="179" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N178">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="179" spans="1:14">
       <c r="A179">
         <v>169248</v>
       </c>
@@ -7749,10 +8286,13 @@
         <v>0</v>
       </c>
       <c r="M179">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="180" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N179">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="180" spans="1:14">
       <c r="A180">
         <v>169798</v>
       </c>
@@ -7790,10 +8330,13 @@
         <v>0</v>
       </c>
       <c r="M180">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="181" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N180">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="181" spans="1:14">
       <c r="A181">
         <v>170976</v>
       </c>
@@ -7831,10 +8374,13 @@
         <v>0</v>
       </c>
       <c r="M181">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="182" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N181">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="182" spans="1:14">
       <c r="A182">
         <v>170976</v>
       </c>
@@ -7872,10 +8418,13 @@
         <v>0</v>
       </c>
       <c r="M182">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="183" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N182">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="183" spans="1:14">
       <c r="A183">
         <v>171100</v>
       </c>
@@ -7913,10 +8462,13 @@
         <v>0</v>
       </c>
       <c r="M183">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="184" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N183">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="184" spans="1:14">
       <c r="A184">
         <v>171100</v>
       </c>
@@ -7954,10 +8506,13 @@
         <v>0</v>
       </c>
       <c r="M184">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="185" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N184">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="185" spans="1:14">
       <c r="A185">
         <v>171128</v>
       </c>
@@ -7995,10 +8550,13 @@
         <v>0</v>
       </c>
       <c r="M185">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="186" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N185">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="186" spans="1:14">
       <c r="A186">
         <v>171128</v>
       </c>
@@ -8036,10 +8594,13 @@
         <v>0</v>
       </c>
       <c r="M186">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="187" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N186">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="187" spans="1:14">
       <c r="A187">
         <v>171571</v>
       </c>
@@ -8077,10 +8638,13 @@
         <v>0</v>
       </c>
       <c r="M187">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="188" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N187">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="188" spans="1:14">
       <c r="A188">
         <v>172644</v>
       </c>
@@ -8118,10 +8682,13 @@
         <v>0</v>
       </c>
       <c r="M188">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="189" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N188">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="189" spans="1:14">
       <c r="A189">
         <v>172644</v>
       </c>
@@ -8159,10 +8726,13 @@
         <v>0</v>
       </c>
       <c r="M189">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="190" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N189">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="190" spans="1:14">
       <c r="A190">
         <v>172699</v>
       </c>
@@ -8200,10 +8770,13 @@
         <v>0</v>
       </c>
       <c r="M190">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="191" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N190">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="191" spans="1:14">
       <c r="A191">
         <v>172699</v>
       </c>
@@ -8241,10 +8814,13 @@
         <v>0</v>
       </c>
       <c r="M191">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="192" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N191">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="192" spans="1:14">
       <c r="A192">
         <v>173920</v>
       </c>
@@ -8282,10 +8858,13 @@
         <v>0</v>
       </c>
       <c r="M192">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="193" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N192">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="193" spans="1:14">
       <c r="A193">
         <v>174066</v>
       </c>
@@ -8323,10 +8902,13 @@
         <v>0</v>
       </c>
       <c r="M193">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="194" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N193">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="194" spans="1:14">
       <c r="A194">
         <v>174066</v>
       </c>
@@ -8364,10 +8946,13 @@
         <v>0</v>
       </c>
       <c r="M194">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="195" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N194">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="195" spans="1:14">
       <c r="A195">
         <v>174233</v>
       </c>
@@ -8405,10 +8990,13 @@
         <v>0</v>
       </c>
       <c r="M195">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="196" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N195">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="196" spans="1:14">
       <c r="A196">
         <v>176017</v>
       </c>
@@ -8446,10 +9034,13 @@
         <v>0</v>
       </c>
       <c r="M196">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="197" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N196">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="197" spans="1:14">
       <c r="A197">
         <v>176017</v>
       </c>
@@ -8487,10 +9078,13 @@
         <v>0</v>
       </c>
       <c r="M197">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="198" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N197">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="198" spans="1:14">
       <c r="A198">
         <v>176080</v>
       </c>
@@ -8528,10 +9122,13 @@
         <v>0</v>
       </c>
       <c r="M198">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="199" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N198">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="199" spans="1:14">
       <c r="A199">
         <v>176372</v>
       </c>
@@ -8569,10 +9166,13 @@
         <v>0</v>
       </c>
       <c r="M199">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="200" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N199">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="200" spans="1:14">
       <c r="A200">
         <v>178396</v>
       </c>
@@ -8610,10 +9210,13 @@
         <v>0</v>
       </c>
       <c r="M200">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="201" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N200">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="201" spans="1:14">
       <c r="A201">
         <v>178396</v>
       </c>
@@ -8651,10 +9254,13 @@
         <v>0</v>
       </c>
       <c r="M201">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="202" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N201">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="202" spans="1:14">
       <c r="A202">
         <v>178402</v>
       </c>
@@ -8692,10 +9298,13 @@
         <v>0</v>
       </c>
       <c r="M202">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="203" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N202">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="203" spans="1:14">
       <c r="A203">
         <v>178411</v>
       </c>
@@ -8733,10 +9342,13 @@
         <v>0</v>
       </c>
       <c r="M203">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="204" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N203">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="204" spans="1:14">
       <c r="A204">
         <v>178411</v>
       </c>
@@ -8774,10 +9386,13 @@
         <v>0</v>
       </c>
       <c r="M204">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="205" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N204">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="205" spans="1:14">
       <c r="A205">
         <v>178420</v>
       </c>
@@ -8815,10 +9430,13 @@
         <v>0</v>
       </c>
       <c r="M205">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="206" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N205">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="206" spans="1:14">
       <c r="A206">
         <v>178420</v>
       </c>
@@ -8856,10 +9474,13 @@
         <v>0</v>
       </c>
       <c r="M206">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="207" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N206">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="207" spans="1:14">
       <c r="A207">
         <v>179867</v>
       </c>
@@ -8897,10 +9518,13 @@
         <v>0</v>
       </c>
       <c r="M207">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="208" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N207">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="208" spans="1:14">
       <c r="A208">
         <v>179867</v>
       </c>
@@ -8938,10 +9562,13 @@
         <v>0</v>
       </c>
       <c r="M208">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="209" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N208">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="209" spans="1:14">
       <c r="A209">
         <v>180461</v>
       </c>
@@ -8979,10 +9606,13 @@
         <v>0</v>
       </c>
       <c r="M209">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="210" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N209">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="210" spans="1:14">
       <c r="A210">
         <v>180461</v>
       </c>
@@ -9020,10 +9650,13 @@
         <v>0</v>
       </c>
       <c r="M210">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="211" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N210">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="211" spans="1:14">
       <c r="A211">
         <v>180489</v>
       </c>
@@ -9061,10 +9694,13 @@
         <v>0</v>
       </c>
       <c r="M211">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="212" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N211">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="212" spans="1:14">
       <c r="A212">
         <v>181002</v>
       </c>
@@ -9102,10 +9738,13 @@
         <v>0</v>
       </c>
       <c r="M212">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="213" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N212">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="213" spans="1:14">
       <c r="A213">
         <v>181464</v>
       </c>
@@ -9143,10 +9782,13 @@
         <v>0</v>
       </c>
       <c r="M213">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="214" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N213">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="214" spans="1:14">
       <c r="A214">
         <v>181464</v>
       </c>
@@ -9184,10 +9826,13 @@
         <v>0</v>
       </c>
       <c r="M214">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="215" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N214">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="215" spans="1:14">
       <c r="A215">
         <v>182281</v>
       </c>
@@ -9225,10 +9870,13 @@
         <v>0</v>
       </c>
       <c r="M215">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="216" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N215">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="216" spans="1:14">
       <c r="A216">
         <v>182290</v>
       </c>
@@ -9266,10 +9914,13 @@
         <v>0</v>
       </c>
       <c r="M216">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="217" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N216">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="217" spans="1:14">
       <c r="A217">
         <v>182290</v>
       </c>
@@ -9307,10 +9958,13 @@
         <v>0</v>
       </c>
       <c r="M217">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="218" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N217">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="218" spans="1:14">
       <c r="A218">
         <v>182670</v>
       </c>
@@ -9348,10 +10002,13 @@
         <v>0</v>
       </c>
       <c r="M218">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="219" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N218">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="219" spans="1:14">
       <c r="A219">
         <v>182670</v>
       </c>
@@ -9389,10 +10046,13 @@
         <v>0</v>
       </c>
       <c r="M219">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="220" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N219">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="220" spans="1:14">
       <c r="A220">
         <v>183044</v>
       </c>
@@ -9430,10 +10090,13 @@
         <v>0</v>
       </c>
       <c r="M220">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="221" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N220">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="221" spans="1:14">
       <c r="A221">
         <v>183044</v>
       </c>
@@ -9471,10 +10134,13 @@
         <v>0</v>
       </c>
       <c r="M221">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="222" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N221">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="222" spans="1:14">
       <c r="A222">
         <v>186131</v>
       </c>
@@ -9512,10 +10178,13 @@
         <v>0</v>
       </c>
       <c r="M222">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="223" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N222">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="223" spans="1:14">
       <c r="A223">
         <v>186131</v>
       </c>
@@ -9553,10 +10222,13 @@
         <v>0</v>
       </c>
       <c r="M223">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="224" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N223">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="224" spans="1:14">
       <c r="A224">
         <v>186867</v>
       </c>
@@ -9594,10 +10266,13 @@
         <v>0</v>
       </c>
       <c r="M224">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="225" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N224">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="225" spans="1:14">
       <c r="A225">
         <v>186867</v>
       </c>
@@ -9635,10 +10310,13 @@
         <v>0</v>
       </c>
       <c r="M225">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="226" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N225">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="226" spans="1:14">
       <c r="A226">
         <v>187967</v>
       </c>
@@ -9676,10 +10354,13 @@
         <v>0</v>
       </c>
       <c r="M226">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="227" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N226">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="227" spans="1:14">
       <c r="A227">
         <v>187967</v>
       </c>
@@ -9717,10 +10398,13 @@
         <v>0</v>
       </c>
       <c r="M227">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="228" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N227">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="228" spans="1:14">
       <c r="A228">
         <v>187985</v>
       </c>
@@ -9758,10 +10442,13 @@
         <v>0</v>
       </c>
       <c r="M228">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="229" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N228">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="229" spans="1:14">
       <c r="A229">
         <v>187985</v>
       </c>
@@ -9799,10 +10486,13 @@
         <v>0</v>
       </c>
       <c r="M229">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="230" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N229">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="230" spans="1:14">
       <c r="A230">
         <v>188030</v>
       </c>
@@ -9840,10 +10530,13 @@
         <v>0</v>
       </c>
       <c r="M230">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="231" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N230">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="231" spans="1:14">
       <c r="A231">
         <v>188030</v>
       </c>
@@ -9881,10 +10574,13 @@
         <v>0</v>
       </c>
       <c r="M231">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="232" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N231">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="232" spans="1:14">
       <c r="A232">
         <v>190044</v>
       </c>
@@ -9922,10 +10618,13 @@
         <v>0</v>
       </c>
       <c r="M232">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="233" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N232">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="233" spans="1:14">
       <c r="A233">
         <v>190044</v>
       </c>
@@ -9963,10 +10662,13 @@
         <v>0</v>
       </c>
       <c r="M233">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="234" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N233">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="234" spans="1:14">
       <c r="A234">
         <v>190150</v>
       </c>
@@ -10004,10 +10706,13 @@
         <v>0</v>
       </c>
       <c r="M234">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="235" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N234">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="235" spans="1:14">
       <c r="A235">
         <v>190150</v>
       </c>
@@ -10045,10 +10750,13 @@
         <v>0</v>
       </c>
       <c r="M235">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="236" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N235">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="236" spans="1:14">
       <c r="A236">
         <v>190415</v>
       </c>
@@ -10086,10 +10794,13 @@
         <v>0</v>
       </c>
       <c r="M236">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="237" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N236">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="237" spans="1:14">
       <c r="A237">
         <v>190415</v>
       </c>
@@ -10127,10 +10838,13 @@
         <v>0</v>
       </c>
       <c r="M237">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="238" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N237">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="238" spans="1:14">
       <c r="A238">
         <v>190549</v>
       </c>
@@ -10168,10 +10882,13 @@
         <v>0</v>
       </c>
       <c r="M238">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="239" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N238">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="239" spans="1:14">
       <c r="A239">
         <v>190567</v>
       </c>
@@ -10209,10 +10926,13 @@
         <v>0</v>
       </c>
       <c r="M239">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="240" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N239">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="240" spans="1:14">
       <c r="A240">
         <v>190576</v>
       </c>
@@ -10250,10 +10970,13 @@
         <v>0</v>
       </c>
       <c r="M240">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="241" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N240">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="241" spans="1:14">
       <c r="A241">
         <v>190594</v>
       </c>
@@ -10291,10 +11014,13 @@
         <v>0</v>
       </c>
       <c r="M241">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="242" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N241">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="242" spans="1:14">
       <c r="A242">
         <v>193900</v>
       </c>
@@ -10332,10 +11058,13 @@
         <v>0</v>
       </c>
       <c r="M242">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="243" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N242">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="243" spans="1:14">
       <c r="A243">
         <v>193900</v>
       </c>
@@ -10373,10 +11102,13 @@
         <v>0</v>
       </c>
       <c r="M243">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="244" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N243">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="244" spans="1:14">
       <c r="A244">
         <v>194824</v>
       </c>
@@ -10414,10 +11146,13 @@
         <v>0</v>
       </c>
       <c r="M244">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="245" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N244">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="245" spans="1:14">
       <c r="A245">
         <v>194824</v>
       </c>
@@ -10455,10 +11190,13 @@
         <v>0</v>
       </c>
       <c r="M245">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="246" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N245">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="246" spans="1:14">
       <c r="A246">
         <v>195030</v>
       </c>
@@ -10496,10 +11234,13 @@
         <v>0</v>
       </c>
       <c r="M246">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="247" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N246">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="247" spans="1:14">
       <c r="A247">
         <v>195030</v>
       </c>
@@ -10537,10 +11278,13 @@
         <v>0</v>
       </c>
       <c r="M247">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="248" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N247">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="248" spans="1:14">
       <c r="A248">
         <v>196060</v>
       </c>
@@ -10578,10 +11322,13 @@
         <v>0</v>
       </c>
       <c r="M248">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="249" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N248">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="249" spans="1:14">
       <c r="A249">
         <v>196060</v>
       </c>
@@ -10619,10 +11366,13 @@
         <v>0</v>
       </c>
       <c r="M249">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="250" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N249">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="250" spans="1:14">
       <c r="A250">
         <v>196079</v>
       </c>
@@ -10660,10 +11410,13 @@
         <v>0</v>
       </c>
       <c r="M250">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="251" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N250">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="251" spans="1:14">
       <c r="A251">
         <v>196088</v>
       </c>
@@ -10701,10 +11454,13 @@
         <v>0</v>
       </c>
       <c r="M251">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="252" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N251">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="252" spans="1:14">
       <c r="A252">
         <v>196088</v>
       </c>
@@ -10742,10 +11498,13 @@
         <v>0</v>
       </c>
       <c r="M252">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="253" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N252">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="253" spans="1:14">
       <c r="A253">
         <v>196097</v>
       </c>
@@ -10783,10 +11542,13 @@
         <v>0</v>
       </c>
       <c r="M253">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="254" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N253">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="254" spans="1:14">
       <c r="A254">
         <v>196097</v>
       </c>
@@ -10824,10 +11586,13 @@
         <v>0</v>
       </c>
       <c r="M254">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="255" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N254">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="255" spans="1:14">
       <c r="A255">
         <v>196413</v>
       </c>
@@ -10865,10 +11630,13 @@
         <v>0</v>
       </c>
       <c r="M255">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="256" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N255">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="256" spans="1:14">
       <c r="A256">
         <v>196413</v>
       </c>
@@ -10906,10 +11674,13 @@
         <v>0</v>
       </c>
       <c r="M256">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="257" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N256">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="257" spans="1:14">
       <c r="A257">
         <v>197869</v>
       </c>
@@ -10947,10 +11718,13 @@
         <v>0</v>
       </c>
       <c r="M257">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="258" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N257">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="258" spans="1:14">
       <c r="A258">
         <v>198419</v>
       </c>
@@ -10988,10 +11762,13 @@
         <v>0</v>
       </c>
       <c r="M258">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="259" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N258">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="259" spans="1:14">
       <c r="A259">
         <v>198419</v>
       </c>
@@ -11029,10 +11806,13 @@
         <v>0</v>
       </c>
       <c r="M259">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="260" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N259">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="260" spans="1:14">
       <c r="A260">
         <v>198464</v>
       </c>
@@ -11070,10 +11850,13 @@
         <v>0</v>
       </c>
       <c r="M260">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="261" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N260">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="261" spans="1:14">
       <c r="A261">
         <v>199102</v>
       </c>
@@ -11111,10 +11894,13 @@
         <v>0</v>
       </c>
       <c r="M261">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="262" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N261">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="262" spans="1:14">
       <c r="A262">
         <v>199120</v>
       </c>
@@ -11152,10 +11938,13 @@
         <v>0</v>
       </c>
       <c r="M262">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="263" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N262">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="263" spans="1:14">
       <c r="A263">
         <v>199120</v>
       </c>
@@ -11193,10 +11982,13 @@
         <v>0</v>
       </c>
       <c r="M263">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="264" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N263">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="264" spans="1:14">
       <c r="A264">
         <v>199139</v>
       </c>
@@ -11234,10 +12026,13 @@
         <v>0</v>
       </c>
       <c r="M264">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="265" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N264">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="265" spans="1:14">
       <c r="A265">
         <v>199193</v>
       </c>
@@ -11275,10 +12070,13 @@
         <v>0</v>
       </c>
       <c r="M265">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="266" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N265">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="266" spans="1:14">
       <c r="A266">
         <v>199193</v>
       </c>
@@ -11316,10 +12114,13 @@
         <v>0</v>
       </c>
       <c r="M266">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="267" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N266">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="267" spans="1:14">
       <c r="A267">
         <v>199847</v>
       </c>
@@ -11357,10 +12158,13 @@
         <v>0</v>
       </c>
       <c r="M267">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="268" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N267">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="268" spans="1:14">
       <c r="A268">
         <v>199847</v>
       </c>
@@ -11398,10 +12202,13 @@
         <v>0</v>
       </c>
       <c r="M268">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="269" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N268">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="269" spans="1:14">
       <c r="A269">
         <v>200280</v>
       </c>
@@ -11439,10 +12246,13 @@
         <v>0</v>
       </c>
       <c r="M269">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="270" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N269">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="270" spans="1:14">
       <c r="A270">
         <v>200332</v>
       </c>
@@ -11480,10 +12290,13 @@
         <v>0</v>
       </c>
       <c r="M270">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="271" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N270">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="271" spans="1:14">
       <c r="A271">
         <v>200332</v>
       </c>
@@ -11521,10 +12334,13 @@
         <v>0</v>
       </c>
       <c r="M271">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="272" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N271">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="272" spans="1:14">
       <c r="A272">
         <v>200800</v>
       </c>
@@ -11562,10 +12378,13 @@
         <v>0</v>
       </c>
       <c r="M272">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="273" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N272">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="273" spans="1:14">
       <c r="A273">
         <v>201441</v>
       </c>
@@ -11603,10 +12422,13 @@
         <v>0</v>
       </c>
       <c r="M273">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="274" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N273">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="274" spans="1:14">
       <c r="A274">
         <v>201645</v>
       </c>
@@ -11644,10 +12466,13 @@
         <v>0</v>
       </c>
       <c r="M274">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="275" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N274">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="275" spans="1:14">
       <c r="A275">
         <v>201645</v>
       </c>
@@ -11685,10 +12510,13 @@
         <v>0</v>
       </c>
       <c r="M275">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="276" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N275">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="276" spans="1:14">
       <c r="A276">
         <v>201885</v>
       </c>
@@ -11726,10 +12554,13 @@
         <v>0</v>
       </c>
       <c r="M276">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="277" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N276">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="277" spans="1:14">
       <c r="A277">
         <v>201885</v>
       </c>
@@ -11767,10 +12598,13 @@
         <v>0</v>
       </c>
       <c r="M277">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="278" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N277">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="278" spans="1:14">
       <c r="A278">
         <v>202134</v>
       </c>
@@ -11808,10 +12642,13 @@
         <v>0</v>
       </c>
       <c r="M278">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="279" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N278">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="279" spans="1:14">
       <c r="A279">
         <v>203368</v>
       </c>
@@ -11849,10 +12686,13 @@
         <v>0</v>
       </c>
       <c r="M279">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="280" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N279">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="280" spans="1:14">
       <c r="A280">
         <v>203517</v>
       </c>
@@ -11890,10 +12730,13 @@
         <v>0</v>
       </c>
       <c r="M280">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="281" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N280">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="281" spans="1:14">
       <c r="A281">
         <v>203517</v>
       </c>
@@ -11931,10 +12774,13 @@
         <v>0</v>
       </c>
       <c r="M281">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="282" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N281">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="282" spans="1:14">
       <c r="A282">
         <v>204024</v>
       </c>
@@ -11972,10 +12818,13 @@
         <v>0</v>
       </c>
       <c r="M282">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="283" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N282">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="283" spans="1:14">
       <c r="A283">
         <v>204796</v>
       </c>
@@ -12013,10 +12862,13 @@
         <v>0</v>
       </c>
       <c r="M283">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="284" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N283">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="284" spans="1:14">
       <c r="A284">
         <v>204796</v>
       </c>
@@ -12054,10 +12906,13 @@
         <v>0</v>
       </c>
       <c r="M284">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="285" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N284">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="285" spans="1:14">
       <c r="A285">
         <v>204857</v>
       </c>
@@ -12095,10 +12950,13 @@
         <v>0</v>
       </c>
       <c r="M285">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="286" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N285">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="286" spans="1:14">
       <c r="A286">
         <v>204857</v>
       </c>
@@ -12136,10 +12994,13 @@
         <v>0</v>
       </c>
       <c r="M286">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="287" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N286">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="287" spans="1:14">
       <c r="A287">
         <v>206084</v>
       </c>
@@ -12177,10 +13038,13 @@
         <v>0</v>
       </c>
       <c r="M287">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="288" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N287">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="288" spans="1:14">
       <c r="A288">
         <v>206084</v>
       </c>
@@ -12218,10 +13082,13 @@
         <v>0</v>
       </c>
       <c r="M288">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="289" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N288">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="289" spans="1:14">
       <c r="A289">
         <v>206604</v>
       </c>
@@ -12259,10 +13126,13 @@
         <v>0</v>
       </c>
       <c r="M289">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="290" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N289">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="290" spans="1:14">
       <c r="A290">
         <v>206941</v>
       </c>
@@ -12300,10 +13170,13 @@
         <v>0</v>
       </c>
       <c r="M290">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="291" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N290">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="291" spans="1:14">
       <c r="A291">
         <v>206941</v>
       </c>
@@ -12341,10 +13214,13 @@
         <v>0</v>
       </c>
       <c r="M291">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="292" spans="1:13">
+        <v>2</v>
+      </c>
+      <c r="N291">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="292" spans="1:14">
       <c r="A292">
         <v>207388</v>
       </c>
@@ -12382,10 +13258,13 @@
         <v>0</v>
       </c>
       <c r="M292">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="293" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N292">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="293" spans="1:14">
       <c r="A293">
         <v>207388</v>
       </c>
@@ -12423,10 +13302,13 @@
         <v>0</v>
       </c>
       <c r="M293">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="294" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N293">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="294" spans="1:14">
       <c r="A294">
         <v>207388</v>
       </c>
@@ -12464,10 +13346,13 @@
         <v>0</v>
       </c>
       <c r="M294">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="295" spans="1:13">
+        <v>2</v>
+      </c>
+      <c r="N294">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="295" spans="1:14">
       <c r="A295">
         <v>207388</v>
       </c>
@@ -12505,10 +13390,13 @@
         <v>0</v>
       </c>
       <c r="M295">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="296" spans="1:13">
+        <v>2</v>
+      </c>
+      <c r="N295">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="296" spans="1:14">
       <c r="A296">
         <v>207500</v>
       </c>
@@ -12546,10 +13434,13 @@
         <v>0</v>
       </c>
       <c r="M296">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="297" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N296">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="297" spans="1:14">
       <c r="A297">
         <v>207500</v>
       </c>
@@ -12587,10 +13478,13 @@
         <v>1</v>
       </c>
       <c r="M297">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="298" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N297">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="298" spans="1:14">
       <c r="A298">
         <v>207500</v>
       </c>
@@ -12628,10 +13522,13 @@
         <v>0</v>
       </c>
       <c r="M298">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="299" spans="1:13">
+        <v>2</v>
+      </c>
+      <c r="N298">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="299" spans="1:14">
       <c r="A299">
         <v>207500</v>
       </c>
@@ -12669,10 +13566,13 @@
         <v>0</v>
       </c>
       <c r="M299">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="300" spans="1:13">
+        <v>2</v>
+      </c>
+      <c r="N299">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="300" spans="1:14">
       <c r="A300">
         <v>209542</v>
       </c>
@@ -12710,10 +13610,13 @@
         <v>0</v>
       </c>
       <c r="M300">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="301" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N300">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="301" spans="1:14">
       <c r="A301">
         <v>209542</v>
       </c>
@@ -12751,10 +13654,13 @@
         <v>0</v>
       </c>
       <c r="M301">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="302" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N301">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="302" spans="1:14">
       <c r="A302">
         <v>209551</v>
       </c>
@@ -12792,10 +13698,13 @@
         <v>0</v>
       </c>
       <c r="M302">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="303" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N302">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="303" spans="1:14">
       <c r="A303">
         <v>209551</v>
       </c>
@@ -12833,10 +13742,13 @@
         <v>0</v>
       </c>
       <c r="M303">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="304" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N303">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="304" spans="1:14">
       <c r="A304">
         <v>209807</v>
       </c>
@@ -12874,10 +13786,13 @@
         <v>0</v>
       </c>
       <c r="M304">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="305" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N304">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="305" spans="1:14">
       <c r="A305">
         <v>211273</v>
       </c>
@@ -12915,10 +13830,13 @@
         <v>0</v>
       </c>
       <c r="M305">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="306" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N305">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="306" spans="1:14">
       <c r="A306">
         <v>211440</v>
       </c>
@@ -12956,10 +13874,13 @@
         <v>0</v>
       </c>
       <c r="M306">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="307" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N306">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="307" spans="1:14">
       <c r="A307">
         <v>211440</v>
       </c>
@@ -12997,10 +13918,13 @@
         <v>0</v>
       </c>
       <c r="M307">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="308" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N307">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="308" spans="1:14">
       <c r="A308">
         <v>213020</v>
       </c>
@@ -13038,10 +13962,13 @@
         <v>0</v>
       </c>
       <c r="M308">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="309" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N308">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="309" spans="1:14">
       <c r="A309">
         <v>213543</v>
       </c>
@@ -13079,10 +14006,13 @@
         <v>0</v>
       </c>
       <c r="M309">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="310" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N309">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="310" spans="1:14">
       <c r="A310">
         <v>213543</v>
       </c>
@@ -13120,10 +14050,13 @@
         <v>0</v>
       </c>
       <c r="M310">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="311" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N310">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="311" spans="1:14">
       <c r="A311">
         <v>214777</v>
       </c>
@@ -13161,10 +14094,13 @@
         <v>0</v>
       </c>
       <c r="M311">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="312" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N311">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="312" spans="1:14">
       <c r="A312">
         <v>214777</v>
       </c>
@@ -13202,10 +14138,13 @@
         <v>0</v>
       </c>
       <c r="M312">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="313" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N312">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="313" spans="1:14">
       <c r="A313">
         <v>215062</v>
       </c>
@@ -13243,10 +14182,13 @@
         <v>0</v>
       </c>
       <c r="M313">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="314" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N313">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="314" spans="1:14">
       <c r="A314">
         <v>215062</v>
       </c>
@@ -13284,10 +14226,13 @@
         <v>0</v>
       </c>
       <c r="M314">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="315" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N314">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="315" spans="1:14">
       <c r="A315">
         <v>215293</v>
       </c>
@@ -13325,10 +14270,13 @@
         <v>0</v>
       </c>
       <c r="M315">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="316" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N315">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="316" spans="1:14">
       <c r="A316">
         <v>215293</v>
       </c>
@@ -13366,10 +14314,13 @@
         <v>0</v>
       </c>
       <c r="M316">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="317" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N316">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="317" spans="1:14">
       <c r="A317">
         <v>216038</v>
       </c>
@@ -13407,10 +14358,13 @@
         <v>0</v>
       </c>
       <c r="M317">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="318" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N317">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="318" spans="1:14">
       <c r="A318">
         <v>216038</v>
       </c>
@@ -13448,10 +14402,13 @@
         <v>0</v>
       </c>
       <c r="M318">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="319" spans="1:13">
+        <v>2</v>
+      </c>
+      <c r="N318">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="319" spans="1:14">
       <c r="A319">
         <v>216339</v>
       </c>
@@ -13489,10 +14446,13 @@
         <v>0</v>
       </c>
       <c r="M319">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="320" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N319">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="320" spans="1:14">
       <c r="A320">
         <v>216339</v>
       </c>
@@ -13530,10 +14490,13 @@
         <v>0</v>
       </c>
       <c r="M320">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="321" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N320">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="321" spans="1:14">
       <c r="A321">
         <v>217156</v>
       </c>
@@ -13571,10 +14534,13 @@
         <v>0</v>
       </c>
       <c r="M321">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="322" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N321">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="322" spans="1:14">
       <c r="A322">
         <v>217156</v>
       </c>
@@ -13612,10 +14578,13 @@
         <v>0</v>
       </c>
       <c r="M322">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="323" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N322">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="323" spans="1:14">
       <c r="A323">
         <v>217484</v>
       </c>
@@ -13653,10 +14622,13 @@
         <v>0</v>
       </c>
       <c r="M323">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="324" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N323">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="324" spans="1:14">
       <c r="A324">
         <v>217484</v>
       </c>
@@ -13694,10 +14666,13 @@
         <v>0</v>
       </c>
       <c r="M324">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="325" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N324">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="325" spans="1:14">
       <c r="A325">
         <v>217882</v>
       </c>
@@ -13735,10 +14710,13 @@
         <v>0</v>
       </c>
       <c r="M325">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="326" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N325">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="326" spans="1:14">
       <c r="A326">
         <v>217882</v>
       </c>
@@ -13776,10 +14754,13 @@
         <v>0</v>
       </c>
       <c r="M326">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="327" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N326">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="327" spans="1:14">
       <c r="A327">
         <v>218663</v>
       </c>
@@ -13817,10 +14798,13 @@
         <v>0</v>
       </c>
       <c r="M327">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="328" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N327">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="328" spans="1:14">
       <c r="A328">
         <v>218663</v>
       </c>
@@ -13858,10 +14842,13 @@
         <v>0</v>
       </c>
       <c r="M328">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="329" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N328">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="329" spans="1:14">
       <c r="A329">
         <v>220181</v>
       </c>
@@ -13899,10 +14886,13 @@
         <v>0</v>
       </c>
       <c r="M329">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="330" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N329">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="330" spans="1:14">
       <c r="A330">
         <v>220862</v>
       </c>
@@ -13940,10 +14930,13 @@
         <v>0</v>
       </c>
       <c r="M330">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="331" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N330">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="331" spans="1:14">
       <c r="A331">
         <v>221759</v>
       </c>
@@ -13981,10 +14974,13 @@
         <v>0</v>
       </c>
       <c r="M331">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="332" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N331">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="332" spans="1:14">
       <c r="A332">
         <v>221759</v>
       </c>
@@ -14022,10 +15018,13 @@
         <v>0</v>
       </c>
       <c r="M332">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="333" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N332">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="333" spans="1:14">
       <c r="A333">
         <v>221999</v>
       </c>
@@ -14063,10 +15062,13 @@
         <v>0</v>
       </c>
       <c r="M333">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="334" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N333">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="334" spans="1:14">
       <c r="A334">
         <v>221999</v>
       </c>
@@ -14104,10 +15106,13 @@
         <v>0</v>
       </c>
       <c r="M334">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="335" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N334">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="335" spans="1:14">
       <c r="A335">
         <v>221999</v>
       </c>
@@ -14145,10 +15150,13 @@
         <v>0</v>
       </c>
       <c r="M335">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="336" spans="1:13">
+        <v>2</v>
+      </c>
+      <c r="N335">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="336" spans="1:14">
       <c r="A336">
         <v>221999</v>
       </c>
@@ -14186,10 +15194,13 @@
         <v>0</v>
       </c>
       <c r="M336">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="337" spans="1:13">
+        <v>2</v>
+      </c>
+      <c r="N336">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="337" spans="1:14">
       <c r="A337">
         <v>223232</v>
       </c>
@@ -14227,10 +15238,13 @@
         <v>0</v>
       </c>
       <c r="M337">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="338" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N337">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="338" spans="1:14">
       <c r="A338">
         <v>223232</v>
       </c>
@@ -14268,10 +15282,13 @@
         <v>0</v>
       </c>
       <c r="M338">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="339" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N338">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="339" spans="1:14">
       <c r="A339">
         <v>224554</v>
       </c>
@@ -14309,10 +15326,13 @@
         <v>0</v>
       </c>
       <c r="M339">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="340" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N339">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="340" spans="1:14">
       <c r="A340">
         <v>225414</v>
       </c>
@@ -14350,10 +15370,13 @@
         <v>0</v>
       </c>
       <c r="M340">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="341" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N340">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="341" spans="1:14">
       <c r="A341">
         <v>225511</v>
       </c>
@@ -14391,10 +15414,13 @@
         <v>0</v>
       </c>
       <c r="M341">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="342" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N341">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="342" spans="1:14">
       <c r="A342">
         <v>225511</v>
       </c>
@@ -14432,10 +15458,13 @@
         <v>0</v>
       </c>
       <c r="M342">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="343" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N342">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="343" spans="1:14">
       <c r="A343">
         <v>227216</v>
       </c>
@@ -14473,10 +15502,13 @@
         <v>0</v>
       </c>
       <c r="M343">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="344" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N343">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="344" spans="1:14">
       <c r="A344">
         <v>227216</v>
       </c>
@@ -14514,10 +15546,13 @@
         <v>0</v>
       </c>
       <c r="M344">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="345" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N344">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="345" spans="1:14">
       <c r="A345">
         <v>227377</v>
       </c>
@@ -14555,10 +15590,13 @@
         <v>0</v>
       </c>
       <c r="M345">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="346" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N345">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="346" spans="1:14">
       <c r="A346">
         <v>227757</v>
       </c>
@@ -14596,10 +15634,13 @@
         <v>0</v>
       </c>
       <c r="M346">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="347" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N346">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="347" spans="1:14">
       <c r="A347">
         <v>227757</v>
       </c>
@@ -14637,10 +15678,13 @@
         <v>0</v>
       </c>
       <c r="M347">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="348" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N347">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="348" spans="1:14">
       <c r="A348">
         <v>227881</v>
       </c>
@@ -14678,10 +15722,13 @@
         <v>0</v>
       </c>
       <c r="M348">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="349" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N348">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="349" spans="1:14">
       <c r="A349">
         <v>228246</v>
       </c>
@@ -14719,10 +15766,13 @@
         <v>0</v>
       </c>
       <c r="M349">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="350" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N349">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="350" spans="1:14">
       <c r="A350">
         <v>228246</v>
       </c>
@@ -14760,10 +15810,13 @@
         <v>0</v>
       </c>
       <c r="M350">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="351" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N350">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="351" spans="1:14">
       <c r="A351">
         <v>228431</v>
       </c>
@@ -14801,10 +15854,13 @@
         <v>0</v>
       </c>
       <c r="M351">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="352" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N351">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="352" spans="1:14">
       <c r="A352">
         <v>228459</v>
       </c>
@@ -14842,10 +15898,13 @@
         <v>0</v>
       </c>
       <c r="M352">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="353" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N352">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="353" spans="1:14">
       <c r="A353">
         <v>228723</v>
       </c>
@@ -14883,10 +15942,13 @@
         <v>0</v>
       </c>
       <c r="M353">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="354" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N353">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="354" spans="1:14">
       <c r="A354">
         <v>228723</v>
       </c>
@@ -14924,10 +15986,13 @@
         <v>0</v>
       </c>
       <c r="M354">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="355" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N354">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="355" spans="1:14">
       <c r="A355">
         <v>228769</v>
       </c>
@@ -14965,10 +16030,13 @@
         <v>0</v>
       </c>
       <c r="M355">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="356" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N355">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="356" spans="1:14">
       <c r="A356">
         <v>228778</v>
       </c>
@@ -15006,10 +16074,13 @@
         <v>0</v>
       </c>
       <c r="M356">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="357" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N356">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="357" spans="1:14">
       <c r="A357">
         <v>228778</v>
       </c>
@@ -15047,10 +16118,13 @@
         <v>0</v>
       </c>
       <c r="M357">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="358" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N357">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="358" spans="1:14">
       <c r="A358">
         <v>228787</v>
       </c>
@@ -15088,10 +16162,13 @@
         <v>0</v>
       </c>
       <c r="M358">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="359" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N358">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="359" spans="1:14">
       <c r="A359">
         <v>228787</v>
       </c>
@@ -15129,10 +16206,13 @@
         <v>0</v>
       </c>
       <c r="M359">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="360" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N359">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="360" spans="1:14">
       <c r="A360">
         <v>228796</v>
       </c>
@@ -15170,10 +16250,13 @@
         <v>0</v>
       </c>
       <c r="M360">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="361" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N360">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="361" spans="1:14">
       <c r="A361">
         <v>229115</v>
       </c>
@@ -15211,10 +16294,13 @@
         <v>0</v>
       </c>
       <c r="M361">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="362" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N361">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="362" spans="1:14">
       <c r="A362">
         <v>229115</v>
       </c>
@@ -15252,10 +16338,13 @@
         <v>0</v>
       </c>
       <c r="M362">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="363" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N362">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="363" spans="1:14">
       <c r="A363">
         <v>230038</v>
       </c>
@@ -15293,10 +16382,13 @@
         <v>0</v>
       </c>
       <c r="M363">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="364" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N363">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="364" spans="1:14">
       <c r="A364">
         <v>230728</v>
       </c>
@@ -15334,10 +16426,13 @@
         <v>0</v>
       </c>
       <c r="M364">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="365" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N364">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="365" spans="1:14">
       <c r="A365">
         <v>230728</v>
       </c>
@@ -15375,10 +16470,13 @@
         <v>0</v>
       </c>
       <c r="M365">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="366" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N365">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="366" spans="1:14">
       <c r="A366">
         <v>230764</v>
       </c>
@@ -15416,10 +16514,13 @@
         <v>0</v>
       </c>
       <c r="M366">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="367" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N366">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="367" spans="1:14">
       <c r="A367">
         <v>230764</v>
       </c>
@@ -15457,10 +16558,13 @@
         <v>0</v>
       </c>
       <c r="M367">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="368" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N367">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="368" spans="1:14">
       <c r="A368">
         <v>231174</v>
       </c>
@@ -15498,10 +16602,13 @@
         <v>0</v>
       </c>
       <c r="M368">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="369" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N368">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="369" spans="1:14">
       <c r="A369">
         <v>231624</v>
       </c>
@@ -15539,10 +16646,13 @@
         <v>0</v>
       </c>
       <c r="M369">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="370" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N369">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="370" spans="1:14">
       <c r="A370">
         <v>231624</v>
       </c>
@@ -15580,10 +16690,13 @@
         <v>0</v>
       </c>
       <c r="M370">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="371" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N370">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="371" spans="1:14">
       <c r="A371">
         <v>232265</v>
       </c>
@@ -15621,10 +16734,13 @@
         <v>0</v>
       </c>
       <c r="M371">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="372" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N371">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="372" spans="1:14">
       <c r="A372">
         <v>232265</v>
       </c>
@@ -15662,10 +16778,13 @@
         <v>0</v>
       </c>
       <c r="M372">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="373" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N372">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="373" spans="1:14">
       <c r="A373">
         <v>232982</v>
       </c>
@@ -15703,10 +16822,13 @@
         <v>0</v>
       </c>
       <c r="M373">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="374" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N373">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="374" spans="1:14">
       <c r="A374">
         <v>232982</v>
       </c>
@@ -15744,10 +16866,13 @@
         <v>0</v>
       </c>
       <c r="M374">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="375" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N374">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="375" spans="1:14">
       <c r="A375">
         <v>233921</v>
       </c>
@@ -15785,10 +16910,13 @@
         <v>0</v>
       </c>
       <c r="M375">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="376" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N375">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="376" spans="1:14">
       <c r="A376">
         <v>233921</v>
       </c>
@@ -15826,10 +16954,13 @@
         <v>0</v>
       </c>
       <c r="M376">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="377" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N376">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="377" spans="1:14">
       <c r="A377">
         <v>234030</v>
       </c>
@@ -15867,10 +16998,13 @@
         <v>0</v>
       </c>
       <c r="M377">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="378" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N377">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="378" spans="1:14">
       <c r="A378">
         <v>234076</v>
       </c>
@@ -15908,10 +17042,13 @@
         <v>0</v>
       </c>
       <c r="M378">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="379" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N378">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="379" spans="1:14">
       <c r="A379">
         <v>234076</v>
       </c>
@@ -15949,10 +17086,13 @@
         <v>0</v>
       </c>
       <c r="M379">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="380" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N379">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="380" spans="1:14">
       <c r="A380">
         <v>234155</v>
       </c>
@@ -15990,10 +17130,13 @@
         <v>0</v>
       </c>
       <c r="M380">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="381" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N380">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="381" spans="1:14">
       <c r="A381">
         <v>236939</v>
       </c>
@@ -16031,10 +17174,13 @@
         <v>0</v>
       </c>
       <c r="M381">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="382" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N381">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="382" spans="1:14">
       <c r="A382">
         <v>236939</v>
       </c>
@@ -16072,10 +17218,13 @@
         <v>0</v>
       </c>
       <c r="M382">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="383" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N382">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="383" spans="1:14">
       <c r="A383">
         <v>236948</v>
       </c>
@@ -16113,10 +17262,13 @@
         <v>0</v>
       </c>
       <c r="M383">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="384" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N383">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="384" spans="1:14">
       <c r="A384">
         <v>236948</v>
       </c>
@@ -16154,10 +17306,13 @@
         <v>0</v>
       </c>
       <c r="M384">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="385" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N384">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="385" spans="1:14">
       <c r="A385">
         <v>238032</v>
       </c>
@@ -16195,10 +17350,13 @@
         <v>0</v>
       </c>
       <c r="M385">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="386" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N385">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="386" spans="1:14">
       <c r="A386">
         <v>238032</v>
       </c>
@@ -16236,10 +17394,13 @@
         <v>0</v>
       </c>
       <c r="M386">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="387" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N386">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="387" spans="1:14">
       <c r="A387">
         <v>240365</v>
       </c>
@@ -16277,10 +17438,13 @@
         <v>0</v>
       </c>
       <c r="M387">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="388" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N387">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="388" spans="1:14">
       <c r="A388">
         <v>240444</v>
       </c>
@@ -16318,10 +17482,13 @@
         <v>0</v>
       </c>
       <c r="M388">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="389" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N388">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="389" spans="1:14">
       <c r="A389">
         <v>240444</v>
       </c>
@@ -16359,10 +17526,13 @@
         <v>1</v>
       </c>
       <c r="M389">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="390" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N389">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="390" spans="1:14">
       <c r="A390">
         <v>240453</v>
       </c>
@@ -16400,10 +17570,13 @@
         <v>0</v>
       </c>
       <c r="M390">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="391" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N390">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="391" spans="1:14">
       <c r="A391">
         <v>240453</v>
       </c>
@@ -16441,10 +17614,13 @@
         <v>0</v>
       </c>
       <c r="M391">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="392" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N391">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="392" spans="1:14">
       <c r="A392">
         <v>240727</v>
       </c>
@@ -16482,10 +17658,13 @@
         <v>0</v>
       </c>
       <c r="M392">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="393" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N392">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="393" spans="1:14">
       <c r="A393">
         <v>240727</v>
       </c>
@@ -16523,10 +17702,13 @@
         <v>0</v>
       </c>
       <c r="M393">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="394" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N393">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="394" spans="1:14">
       <c r="A394">
         <v>243197</v>
       </c>
@@ -16564,10 +17746,13 @@
         <v>0</v>
       </c>
       <c r="M394">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="395" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N394">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="395" spans="1:14">
       <c r="A395">
         <v>243221</v>
       </c>
@@ -16605,10 +17790,13 @@
         <v>0</v>
       </c>
       <c r="M395">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="396" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N395">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="396" spans="1:14">
       <c r="A396">
         <v>243744</v>
       </c>
@@ -16646,10 +17834,13 @@
         <v>0</v>
       </c>
       <c r="M396">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="397" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N396">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="397" spans="1:14">
       <c r="A397">
         <v>243744</v>
       </c>
@@ -16687,10 +17878,13 @@
         <v>0</v>
       </c>
       <c r="M397">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="398" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N397">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="398" spans="1:14">
       <c r="A398">
         <v>243780</v>
       </c>
@@ -16728,10 +17922,13 @@
         <v>0</v>
       </c>
       <c r="M398">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="399" spans="1:13">
+        <v>1</v>
+      </c>
+      <c r="N398">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="399" spans="1:14">
       <c r="A399">
         <v>243780</v>
       </c>
@@ -16769,6 +17966,9 @@
         <v>0</v>
       </c>
       <c r="M399">
+        <v>1</v>
+      </c>
+      <c r="N399">
         <v>2006</v>
       </c>
     </row>
